--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{595341F3-CC78-4EDD-A32A-3B9CE51153A8}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9A8B274-BF14-452D-997F-D3F652653A3D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="objetos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="546">
   <si>
     <t>objeto</t>
   </si>
@@ -1627,6 +1627,57 @@
   </si>
   <si>
     <t>Construção de um Espaço de convivência - POC</t>
+  </si>
+  <si>
+    <t>0036.022430/2025-31</t>
+  </si>
+  <si>
+    <t>Monitor Multiparâmetro, equipamento permanente para atender as demandas das UTI 1 e UTI 2 do Hospital Regional de Cacoal - HRC.</t>
+  </si>
+  <si>
+    <t>Aquisição de Monitor Multiparâmetro, equipamento permanente para atender as demandas das UTI 1 e UTI 2 - HRC</t>
+  </si>
+  <si>
+    <t>0036.033047/2025-17</t>
+  </si>
+  <si>
+    <t>Contratação de curso II Fórum de Concessões e PPPs em Infraestrutura Social-Saúde, Educação, Segurança e Operações de transformação urbana, no dia 18 de setembro de 2025</t>
+  </si>
+  <si>
+    <t>0036.034011/2025-42</t>
+  </si>
+  <si>
+    <t>prestação de serviços técnicos de Engenharia Naval, visando à elaboração de Laudo Técnico e de Projeto Executivo de Recuperação Estrutural da embarcação Unidade de Saúde Social Fluvial Walter Bártolo, incluindo diagnóstico, especificações das intervenções necessárias, memorais descritivos, cronograma e demais documentos técnicos exigidos para a completa reabilitação e segurança operacional da embarcação.</t>
+  </si>
+  <si>
+    <t>0036.028208/2025-42</t>
+  </si>
+  <si>
+    <t>Emergencial - Limpeza, Conservação, Higienização e Desinfecção com Fornecimento de Materiais e Equipamentos (GRS4)</t>
+  </si>
+  <si>
+    <t>0035.001454/2025-67</t>
+  </si>
+  <si>
+    <t>Aquisição de ar condicionado com o objetivo de atender o Centro de Diálise de Ariquemes- CDA.</t>
+  </si>
+  <si>
+    <t>0046.000425/2025-59</t>
+  </si>
+  <si>
+    <t>Aquisição de condicionadores de ar (Central de Ar Condicionado), destinados ao atendimento das unidades de saúde (LABORATÓRIO CENTRAL DE SAÚDE PÚBLICA - LACEN/RO)</t>
+  </si>
+  <si>
+    <t>0050.007939/2025-76</t>
+  </si>
+  <si>
+    <t>JPII- Aquisição de Vídeo Laringoscópio Portátil.</t>
+  </si>
+  <si>
+    <t>0036.032294/2025-98</t>
+  </si>
+  <si>
+    <t>Aquisição de Materiais de Expediente - CLAP</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}">
-  <dimension ref="A1:C277"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -5026,6 +5077,87 @@
         <v>528</v>
       </c>
     </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>529</v>
+      </c>
+      <c r="B278" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>529</v>
+      </c>
+      <c r="B279" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>532</v>
+      </c>
+      <c r="B280" t="s">
+        <v>533</v>
+      </c>
+      <c r="C280" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>534</v>
+      </c>
+      <c r="B281" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>536</v>
+      </c>
+      <c r="B282" t="s">
+        <v>537</v>
+      </c>
+      <c r="C282" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>538</v>
+      </c>
+      <c r="B283" t="s">
+        <v>539</v>
+      </c>
+      <c r="C283" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>540</v>
+      </c>
+      <c r="B284" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>542</v>
+      </c>
+      <c r="B285" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>544</v>
+      </c>
+      <c r="B286" t="s">
+        <v>545</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C249" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBF222EC-9CE5-4C04-90D1-111313684F4A}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A3FCDA6-C36A-4F82-A114-FD6E820EE7E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="654">
   <si>
     <t>objeto</t>
   </si>
@@ -354,6 +354,1655 @@
   </si>
   <si>
     <t>Aquisição de ar condicionado com o objetivo de atender o Centro de Diálise de Ariquemes- CDA.</t>
+  </si>
+  <si>
+    <t>0036.059337/2023-11</t>
+  </si>
+  <si>
+    <t>Aquisição do livro “Manual do Servidor Público do Estado de Rondônia” para distribuição nas unidades da Secretaria de Estado da Saúde de Rondônia.</t>
+  </si>
+  <si>
+    <t>0036.031048/2023-57</t>
+  </si>
+  <si>
+    <t>Serviço De Engenharia Clínica, Incluindo Serviço De Gerenciamento De Equipamentos Manutenção Corretiva, Preventiva, Preditiva E Calibração Dos Equipamentos Com Reposição De Peças E Acessórios. Lepac E Cdi</t>
+  </si>
+  <si>
+    <t>0051.491179/2020-59</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de locação de sistema de Fornecimento e tratamento de água para hemodiálise com osmose reversa fixa duplo passo, visando atender a 26 pontos, incluíndo a rede de distribuição e os pontos de consumo, de forma contínua,​ visando atender ao Hospital Regional de Cacoal (HRC), por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.014359/2024-32</t>
+  </si>
+  <si>
+    <t>Registro de Preços para contratação de solução com fornecimento de equipamentos, licenças de softwares e serviços, para proteção e gerenciamento seguro da rede LAN/WAN da Secretaria de Estado da Saúde – SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0050.005171/2023-34</t>
+  </si>
+  <si>
+    <t>Locação prédio para acomodação do Serviço de Atendimento Multidisciplinar Domiciliar - SAMD e Subdiretoria Técnica em Saúde - SDTECS/SESAU, incluindo climatização e manutenção predial, localizado no Município de Porto Velho/RO.</t>
+  </si>
+  <si>
+    <t>0036.021529/2024-35</t>
+  </si>
+  <si>
+    <t>Prestação de Serviços de Limpeza/Desinfecção de Ambientes e Gerenciamento de Resíduos (interno) dos Serviços de Saúde - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento dos Resíduos Grupo D, de forma contínua, para atender a 2ª Gerência Regional de Saúde no município de Cacoal, em caráter contínuo</t>
+  </si>
+  <si>
+    <t>0036.000311/2025-28</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Locação de Módulo/Central de Compressores de Ar Medicinal, incluído providências para instalação completa dos sistemas respectivos, com construção civil, elétrica, mecânica e hidráulica, bem como outros insumos necessários para seu devido funcionamento, considerando na prestação do serviço a montagem e manutenção preventiva e corretiva dos equipamentos de acordo com os padrões e normas técnicas atualizadas, como RDC n.º 50, RDC n.º 307, NBR 12.188 entre outras, para atender as necessidades do Hospital Regional de Cacoal (HRC), conforme Documento de Oficialização de Demanda n.º 2/2025/HRC-SGM (0056295036).</t>
+  </si>
+  <si>
+    <t>0036.055698/2024-79</t>
+  </si>
+  <si>
+    <t>Contratação emergencial de empresa especializada na Prestação de Serviços de Engenharia Clínica, Incluindo Serviço de Gerenciamento de Equipamentos Manutenção Corretiva, Preventiva, Preditiva e Calibração dos Equipamentos com Reposição de Peças e Acessórios, visando atender às necessidades do Hospital Infantil Cosme e Damião - HICD (139 leitos), de forma contínua, conforme a Lei Federal 14.133/2021.</t>
+  </si>
+  <si>
+    <t>0036.007254/2025-16</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em prestação de serviços de manutenção preventiva e corretiva, de forma contínua, com fornecimento e reposição de peças, acessórios e componentes eletrônicos do Sistema de Climatização do (HICD), incluindo de expansão indireta CHILLER, conforme projeto O.S 1430 (0033753209), com capacidade de 162 TR e Centrais de Ar Condicionados instaladas nos setores que não contemplam o sistema de refrigeração chiller, para atender as necessidade do Hospital Infantil Cosme e Damião (HICD), por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.059843/2024-91</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa prestação de serviços de Manutenção Preventiva e Corretiva, com fornecimento e reposição de peças, acessórios e componentes eletrônicos do sistema climatização de expansão direta tipo VRF de 950 HP da marca Mitsubishi e demais equipamentos complementares e substitutos do sistema de climatização (VRF) de conforto térmico, de forma contínua, para atender ao Hospital Regional de Cacoal - HRC, por um período de 01 (um) ano, podendo ser prorrogado conforme previsto nos Art. 106 e 107 da lei nº 14.133, conforme Documento de Oficialização de Demanda nº 6/2025/COHREC-NEMP (0057374682).</t>
+  </si>
+  <si>
+    <t>0036.004257/2025-90</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa para presente instrumento é a prestação de serviços de translado terrestre de corpos, com assistência 24 (vinte e quatro) horas, a fim de atender os óbitos ocorridos no Hospital e Pronto Socorro João Paulo II-HPSJPII, Assistência Médica Intensiva-AMI 24h e Centro de Medicina Tropical de Rondônia-CEMETRON, por um período de 01 (um) ano, podendo ser prorrogado conforme previsto nos Art. 106 e 107 da lei n.º 14.133, conforme Documento de Oficialização de Demanda n.º 2/2025/CEMETRON-ASTEC, n.º 3/2025/AMI-COORD (0057366910, 0057594289).</t>
+  </si>
+  <si>
+    <t>0036.003493/2025-99</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada em Prestação de Serviços de Limpeza, Conservação, Higienização e Desinfecção com Fornecimento de Materiais e Equipamentos nas dependências do prédio onde funciona a III Gerência Regional de Saúde - Vilhena (GRS3), pelo período de 5 (cinco) anos de forma contínua.</t>
+  </si>
+  <si>
+    <t>0020.002635/2025-70</t>
+  </si>
+  <si>
+    <t>Contratação de empresa objetivando a participação de servidores no 1° Congresso Nacional de Contratações e Convênios na Saúde, de forma remota, nos dias 09, 10 e 11 de Abril de 2025, conforme Documento de Oficialização de Demanda nº 1/2025/PGE-SESAU (0057771461).</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em Locação de Módulo/Central de Compressores de Ar Medicinal, incluído providências para instalação completa dos sistemas respectivos, com construção civil, elétrica, mecânica e hidráulica, bem como outros insumos necessários para seu devido funcionamento, considerando na prestação do serviço a montagem e manutenção preventiva e corretiva dos equipamentos de acordo com os padrões e normas técnicas atualizadas, como RDC nº 50, RDC nº 307, NBR 12.188 entre outras, para atender as necessidades do Hospital Regional de Cacoal (HRC).</t>
+  </si>
+  <si>
+    <t>0036.013189/2025-50</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em Serviços de Engenharia Clínica, Incluindo Serviço de Gerenciamento de Equipamentos Manutenção Corretiva, Preventiva, Preditiva e Calibração dos Equipamentos com Reposição de Peças e Acessórios, visando atender às necessidades do Hospital Regional de Cacoal - HRC, Hospital de Urgência e Emergência Regional de Cacoal - HEURO e Hospital Regional de Extrema - HRE, por um período de 01 (um) ano, podendo ser prorrogado conforme previsto nos Art. 106 e 107 da lei nº 14.133, conforme Documento de Oficialização de Demanda nº 251/2024/SESAU-GECOMP (0052163179).</t>
+  </si>
+  <si>
+    <t>0049.006695/2023-81</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de manutenção preventiva e corretiva, com reposição integral de peças do Sistema de Tratamento de Água por osmose reversa passo simples para hemodiálise, na Central de Hemodiálise do Hospital de Base Dr. Ary Pinheiro - HBAP, com capacidade de abastecimento de até 15 máquinas de hemodiálise, por um período de 12 meses.</t>
+  </si>
+  <si>
+    <t>0036.103898/2022-83</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Limpeza, Desobstrução do Sistema de Tratamento de Esgoto (Tanque Séptico, Filtro Anaeróbio e Sumidouro), Caixas de Esgoto, Caixas de Gordura e Tubulações de Esgoto, bem como Limpeza e Desinfecção de Caixas D’água, de forma contínua, por um período de 12 (doze) meses</t>
+  </si>
+  <si>
+    <t>0036.042664/2024-14</t>
+  </si>
+  <si>
+    <t>Locação do imóvel localizado - Coordenadoria Estadual de Nutrição Enteral - CENE, Coordenadoria de Gestão e Assistência Farmacêutica - CGAF, atualmente vigente.</t>
+  </si>
+  <si>
+    <t>0049.010601/2024-50</t>
+  </si>
+  <si>
+    <t>INEXIGIBILIDADE - Contratação de empresa especializada em manutenção corretiva com fornecimento de peças do equipamento Autoclave de peróxido de hidrogênio BAUMMER - HBAP</t>
+  </si>
+  <si>
+    <t>0036.033145/2024-65</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada para a Prestação de Serviços de Higienização e Limpeza Hospitalar e assemelhadas, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento dos Resíduos do Grupo “D” para atuar de forma contínua no Laboratório de Fronteira - LAFRON, conforme Documento de Oficialização de Demanda nº 2/2024/LACEN-NLAFRON (0052710793).</t>
+  </si>
+  <si>
+    <t>0053.336440/2021-10</t>
+  </si>
+  <si>
+    <t>Serviços de limpeza de poços e manutenção preventiva e corretiva das bombas, para atendimento CEMETRON</t>
+  </si>
+  <si>
+    <t>0036.023187/2024-98</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual contratação de empresa especializada em serviço de nuvem na modalidade SaaS de uso de suíte de plataforma de colaboração, associada aos serviços de colaboração e produtividade de e-mail, agendas compartilhadas, ferramenta de videoconferência, pacote de Software de Escritório e Armazenamento, com o objetivo de atender as Coordenadorias que compõem esta Secretaria de Estado da Saúde, pelo período de 1 (um) ano, podendo ser prorrogado, por igual período, conforme previsto no art. 84º da Lei 14.133, de 1° de Abril e 2021.</t>
+  </si>
+  <si>
+    <t>0036.077686/2022-33</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual contratação de empresa especializada na confecção de crachás, visando atender as necessidades das Unidades da Secretaria de Estado da Saúde de Rondônia SESAU/RO por um período de 12 meses.</t>
+  </si>
+  <si>
+    <t>0036.006146/2025-18</t>
+  </si>
+  <si>
+    <t>Emergencial - Manutenção preventiva e corretiva de Grupo gerador HRC</t>
+  </si>
+  <si>
+    <t>0036.008076/2025-32</t>
+  </si>
+  <si>
+    <t>Licitatório - coleta interna e externa, transporte, tratamento (incineração ou autoclavagem e incineração e destinação final dos resíduos de serviços de saúde RSS (grupos A,B,E e eventualmente C) HBAP, HICD, CEMETRON, POC, HRB, HEPSJPII, AMI, LACEN, LEPAC, HEURO, HRC e HRSFG.</t>
+  </si>
+  <si>
+    <t>0036.007322/2023-77</t>
+  </si>
+  <si>
+    <t>sondagem para fabricação e Fornecimento de Reservatórios de água do Hospital de Urgência e Emergência Regional de Cacoal - HEURO</t>
+  </si>
+  <si>
+    <t>0036.030732/2024-01</t>
+  </si>
+  <si>
+    <t>Lavanderia Hospitalar com Fornecimento de Enxoval, a fim de atender às necessidades da Secretaria de Estado de Saúde de Rondônia - SESAU</t>
+  </si>
+  <si>
+    <t>0036.024208/2023-10</t>
+  </si>
+  <si>
+    <t>Contratação de empresa de serviços de soluções e tecnologia, visando modernização dos serviços de atenção à saúde pública, a fim de atender às necessidades da Secretaria de Estado da Saúde - SESAU, contemplando 25 (vinte e cinco) Unidades do estado de Rondônia, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.106428/2022-71</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em prestação de serviços de manutenção preventiva e corretiva, de forma contínua, com fornecimento e reposição de peças, acessórios e componentes eletrônicos do Sistema de Climatização do HICD, incluindo de expansão indireta CHILLER, conforme projeto O.S 1430 (0033753209), com capacidade de 162 TR e Centrais de Ar Condicionados instaladas nos setores que não contemplam o sistema de refrigeração chiller, para atender as necessidade do Hospital Infantil Cosme e Damião - HICD, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.008314/2024-29</t>
+  </si>
+  <si>
+    <t>Contratação de serviços dos Correios para a Operação de Logística de Suprimentos In House conforme disponibiliza a NLLC (Inciso IX, art. 75 da Lei 14.133/21) para o Setor de Controle de Estoque, Armazenamento e Distribuição de Suprimentos desta Setorial de Produtos Médicos da SESAU, por um período mínimo de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.109115/2022-75</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Avançado TIPO ”D” (UTI Móvel) e Suporte Básico TIPO "B", com mão de obra especializada, para atender as necessidades do Hospital Regional de Buritis - HRB, Hospital de Urgência e Emergência Regional de Cacoal - HEURO, Hospital Regional de Cacoal (HRC), Centro de Medicina Tropical - CEMETRON, Hospital e Pronto Socorro João Paulo II - HEPSJP/II, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.006073/2024-83</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em prestação de serviços de vigilância/segurança patrimonial ostensiva e armada/desarmada, visando atender a I Gerência Regional de Saúde de Vilhena, II Gerência Regional de Saúde de Ariquemes, III Gerência Regional de Saúde de Rolim de Moura, e o IV Hospital Regional de São Francisco do Guaporé - HRSFG, no âmbito da Secretaria de Estado da Saúde de Rondônia (SESAU/RO), de forma contínua, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.002598/2024-40</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de materiais periféricos de informática, com a finalidade de atender as necessidades desta Secretaria de Estado da Saúde.</t>
+  </si>
+  <si>
+    <t>0036.031949/2024-20</t>
+  </si>
+  <si>
+    <t>Aquisição e Instalação de Unidades de Tratamento de Ar - UTA´s das salas cirúrgicas para atender o Hospital de Urgência e Emergência Regional de Cacoal - HEURO, conforme Documento de Oficialização de Demanda nº 48/2024/HEURO-ASGAB (0050389844)</t>
+  </si>
+  <si>
+    <t>0036.003735/2024-63</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de vigilância/segurança patrimonial ostensiva e armada/desarmada, para atender as unidades administrativas da I Gerência Regional de Saúde de Ji-Paraná e II Gerência Regional de Saúde de Cacoal, vinculadas à Secretaria de Estado da Saúde, referente aos Lotes I e II</t>
+  </si>
+  <si>
+    <t>0036.012675/2025-51</t>
+  </si>
+  <si>
+    <t>Contratação Emergencial de Empresa Especializada na Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Avançado TIPO ”D” (UTI Móvel) e Suporte Básico TIPO "B", com mão de obra especializada, para atender as necessidades do Hospital Regional São Francisco do Guaporé-HRSF, Policlínica Oswaldo Cruz-POC, Hospital Regional de Buritis-HRB, Hospital de Urgência e Emergência Regional de Cacoal-HEURO, Hospital Regional de Cacoal-HRC, Centro de Medicina Tropical-CEMETRON, Hospital e Pronto Socorro João Paulo II-JPII, Hospital de Retaguarda de Rondônia-HRRO; Centro de Medicina Intensiva​ - AMI; Hospital Regional de Extrema - HRE e Serviço Assistencial Multidisciplinar e Domiciliar-SAMD, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.517278/2021-47</t>
+  </si>
+  <si>
+    <t>Manutenção Prev. e Corretiva Equipamentos da Lavanderia - Hospital de Base Dr. Ary Pinheiro - HB e Hospital Regional de Cacoal - HRC</t>
+  </si>
+  <si>
+    <t>0059.000422/2023-12</t>
+  </si>
+  <si>
+    <t>Manutenção Prev. e Corretiva da Estação de Tratamento de Esgoto - ETE - Hospital Regional de Extrema - HRE</t>
+  </si>
+  <si>
+    <t>0036.051061/2023-22</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de equipamentos de informática tendo como finalidade atender as necessidades das Unidades de Saúde da Secretária de Estado da Saúde - SESAU/RO, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.005911/2024-00</t>
+  </si>
+  <si>
+    <t>Serviços de fornecimento de alimentação e nutrição hospitalar padronizada</t>
+  </si>
+  <si>
+    <t>0036.013967/2024-20</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na Prestação de Serviço de Lavanderia Hospitalar Interna, com disponibilização de equipamentos e demais utensílios, materiais de consumo, realização de manutenção preventiva e corretiva com reposição de peças para atender de forma continuada as necessidades do Hospital Regional de Buritis - HRB, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.033609/2024-33</t>
+  </si>
+  <si>
+    <t>Eng. clinica HB, HRB e CDVJ</t>
+  </si>
+  <si>
+    <t>0036.036977/2024-33</t>
+  </si>
+  <si>
+    <t>Contratação de produtos e serviços por meio de Pacote de Serviços dos CORREIOS</t>
+  </si>
+  <si>
+    <t>0036.037711/2024-16</t>
+  </si>
+  <si>
+    <t>Aquisição de VOIP para atender a CTI.</t>
+  </si>
+  <si>
+    <t>0036.039245/2024-03</t>
+  </si>
+  <si>
+    <t>RP - Serviços de transporte de dados/interconexão (internet), através de cabeamento de fibra óptica e Rede privativa de comunicação. SESAU/CTI</t>
+  </si>
+  <si>
+    <t>0036.036691/2024-58</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada para prestação de serviços de gestão de acervo documental com guarda de documentos, tratamento técnico, Organização e Indexação, de forma contínua, assim como digitalização de documentos com fornecimento de Sistema Informatizado de Gestão Arquivística de Documentos - SIGAD, visando atender a Secretaria de Estado da Saúde - SESAU, por um período de 1 (um) ano, podendo ser prorrogado sucessivamente por igual período, até o limite de 10 (dez) anos, conforme previsto no art. 107 da Lei Federal nº 14.133/21.</t>
+  </si>
+  <si>
+    <t>0036.042679/2024-82</t>
+  </si>
+  <si>
+    <t>Locação de um Imóvel Comercial para instalação da Coordenadoria de Almoxarifado e Patrimônio - CAP</t>
+  </si>
+  <si>
+    <t>0036.274454/2021-41</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada em Serviços na Área de de manutenção preventiva e corretiva em Condicionadores de Ar, com fornecimento e reposição de peças, acessórios e componentes eletrônicos, para atender as seguintes unidades: Hospital Regional de Extrema - HRE, Hospital Regional de Buritis - HRB, Hospital de Base Dr. Ary Pinheiro - HBAP, Hospital e Pronto Socorro João Paulo II - HEPSJPII, Assistência Médica Intensiva - AMI, Hospital Infantil Cosme e Damião - HICD, Laboratório Central de Saúde Pública - LACEN, Laboratório de Fronteira - LAFRON, Centro de Medicina Tropical de Rondônia - CEMETRON e Policlínica Osvaldo Cruz - POC, Centro de Diálise Ariquemes - CDA, Laboratório Estadual de Patologia e Análise Clínicas - LEPAC Hospital de Urgência e Emergência Regional de Cacoal - HEURO.</t>
+  </si>
+  <si>
+    <t>0036.029876/2024-14</t>
+  </si>
+  <si>
+    <t>Aquisição de um imóvel para a 1° Gerência Regional de Saúde de Ji-Paraná</t>
+  </si>
+  <si>
+    <t>0036.007047/2025-53</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em Locação de Módulo/Central de Compressores de Ar Medicinal, incluído providências para instalação completa dos sistemas respectivos, com construção civil, elétrica, mecânica e hidráulica, bem como outros insumos necessários para seu devido funcionamento, considerando na prestação do serviço a montagem e manutenção preventiva e corretiva dos equipamentos de acordo com os padrões e normas técnicas atualizadas, como RDC nº 50, RDC nº 307, NBR 12.188 entre outras, para atender as necessidades do Hospital Regional de Cacoal (HRC), em caráter emergencial, pelo período até 01 (um) ano ou até a conclusão do processo nº 0036.000311/2025-28</t>
+  </si>
+  <si>
+    <t>0036.004517/2025-27</t>
+  </si>
+  <si>
+    <t>Contratação de empresa para prestação de serviços de Manutenção Preventiva e Corretiva em Condicionadores de Ar, com fornecimento e reposição de peças, acessórios e componentes eletrônicos de Sistema de expansão direta (Split), de forma emergencial, por um período de até um (01) ano ou até a conclusão do processo licitatório n° 0036.274454/2021-41, a fim de atender as necessidades do Hospital de Urgência e Emergência Regional de Cacoal - HEURO, Hospital Regional de Buritis - HRB, Hospital e Pronto Socorro João Paulo II - HEPSJPII e Assistência Médica Intensiva - AMI, Centro de Diálise Ariquemes - CDA, Policlínica Osvaldo Cruz - POC, Centro de Medicina Tropical de Rondônia - CEMETRON e Hospital Regional de Extrema - HRE</t>
+  </si>
+  <si>
+    <t>0036.052658/2023-94</t>
+  </si>
+  <si>
+    <t>Locação de Imóvel, visando atender as necessidades da Gerência de Regulação Estadual do SUS (CAIS-GERREG) em Coordenadoria de Regulação de Acesso ao Serviço de Saúde (SESAU-CREG), localizado no Município de Porto Velho/RO.</t>
+  </si>
+  <si>
+    <t>0036.011653/2025-73</t>
+  </si>
+  <si>
+    <t>Contratação de empresa objetivando a participação dos servidores desta Secretaria de Estado da Saúde no II Fórum Concessões e PPPs em Infraestrutura Social, a realizar-se no dia 02 de abril de 2025, na cidade de São Paulo-SP.</t>
+  </si>
+  <si>
+    <t>0036.008982/2025-37</t>
+  </si>
+  <si>
+    <t>Contratação de empresa objetivando a participação dos servidores desta Secretaria de Estado da Saúde no curso híbrido em emendas parlamentares, de forma presencial, nos dias 19, 20 a 21 de março de 2025 na cidade de Porto Velho/RO.</t>
+  </si>
+  <si>
+    <t>0036.013191/2025-29</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviço de engenharia clínica, incluindo serviço de gerenciamento de equipamentos manutenção corretiva, preventiva, preditiva e calibração dos equipamentos com reposição de peças e acessórios, para atender as necessidades do Hospital Regional de Cacoal - HRC, Hospital de Urgência e Emergência de Cacoal - HEURO e Hospital Regional de São Francisco do Guaporé - HRSFG, de forma emergencial por um período de 1 (um) ano conforme a Lei Federal 14.133/2021, ou até a finalização do processo licitatório 0036.013189/2025-50.</t>
+  </si>
+  <si>
+    <t>0036.010551/2025-31</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na Prestação de Serviços de manutenção preventiva e corretiva com fornecimento de peças, executada de forma contínua nos equipamentos da Lavanderia Central do Hospital de Base Dr. Ary Pinheiro - HB e Hospital Regional de Cacoal - HRC, de forma emergencial, por um período de até 1 (um) ano, ou até a finalização do processo licitatório nº 0036.517278/2021-47, conforme Documento de Oficialização de Demanda nº 2/2025/COHREC-NLAV (0058030036) e Documento de Oficialização de Demanda nº 2/2025/HB-NLAV (0058231441).</t>
+  </si>
+  <si>
+    <t>0036.014723/2025-45</t>
+  </si>
+  <si>
+    <t>Contratação de empresa objetivando a participação de 07 (sete) servidores desta Secretaria Estadual de Saúde de Rondônia no 6º Congresso Brasileiro de Compras Públicas, de forma presencial nos dias 25 a 28 de agosto de 2025, em Foz do Iguaçu/PR.</t>
+  </si>
+  <si>
+    <t>0036.037359/2024-19</t>
+  </si>
+  <si>
+    <t>Contratação de empresa(s) especializada(s) em estudos prévios, serviços técnicos, perfurações e instalação de poços tubulares profundos, com a finalidade de atender ao abastecimento público de água potável nas unidades de saúde vinculadas à SESAU.</t>
+  </si>
+  <si>
+    <t>0036.036175/2024-23</t>
+  </si>
+  <si>
+    <t>Registro de preço para eventual contratação de serviços comuns de engenharia e insumos para manutenção predial das unidades de saúde e prédios sob a tutela da Secretaria de Estado da Saúde de Rôndonia (SESAU-RO), conforme especificações técnicas estabelecidas no Sistema Nacional de Pesquisa de Custos e Índices da Construção Civil(SINAPI).</t>
+  </si>
+  <si>
+    <t>0036.369652/2020-19</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada em Serviços de manutenção preventiva e corretiva em Subestação Abaixadora e Grupos Geradores, com fornecimento de quaisquer componentes e/ou peças novas e originais, para atender o Hospital de Base Dr. Ary Pinheiro - HBAP, de forma contínua, por um período de 60 (sessenta) meses, conforme Art. 106 da Lei Federal nº 14.133 de 1° de abril de 2021.</t>
+  </si>
+  <si>
+    <t>0053.002493/2024-82</t>
+  </si>
+  <si>
+    <t>contratação de empresa especializada na prestação de serviços de vigilância e segurança patrimonial ostensiva (armada e desarmada).</t>
+  </si>
+  <si>
+    <t>0036.028242/2024-36</t>
+  </si>
+  <si>
+    <t>Registro de Preços para contratação de empresa para fornecimento, sob demanda, de solução de segurança para proteção de e-mail, Endpoint e proteção contra ataques avançados, incluindo instalação, configuração, repasse de conhecimento, suporte técnico e garantia, para atender às necessidades da Secretaria de Estado da Saúde de Rondônia, pelo período de 12 meses</t>
+  </si>
+  <si>
+    <t>0036.005756/2024-13</t>
+  </si>
+  <si>
+    <t>Registro de Preço para aquisição de servidor de Hiperconvergência - CTI</t>
+  </si>
+  <si>
+    <t>0036.001625/2024-67</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada para prestação de serviços de coleta externa, transporte e destinação final dos resíduos sólidos (grupo D)</t>
+  </si>
+  <si>
+    <t>0036.057526/2023-59</t>
+  </si>
+  <si>
+    <t>SRP - Aquisição de itens de hotelaria hospitalar</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual contratação de empresa de serviços de soluções e tecnologia, visando modernização dos serviços de atenção à saúde pública</t>
+  </si>
+  <si>
+    <t>0036.006890/2023-51</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em construção e reforma para realização de revitalização do bloco berçário do Hospital de Base Dr. Ary Pinheiro - HBAP.</t>
+  </si>
+  <si>
+    <t>0036.060058/2022-19</t>
+  </si>
+  <si>
+    <t>REFORMA DA COBERTURA DO ESTACIONAMENTO DE AMBULÂNCIAS DO HRC CACOAL</t>
+  </si>
+  <si>
+    <t>0036.018613/2020-48</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de manutenção por chamado, com fornecimento de peças, de forma contínua, aos equipamentos de empilhadeira, empilhadeira elétrica, empilhadeira manual, carrinho de carga horizontal, carrinho de carga vertical, carrinhos, paleteira e transpaleteira</t>
+  </si>
+  <si>
+    <t>0036.093613/2022-99</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada para realização de CONTROLE E MONITORAMENTO DE ÁGUA POTÁVEL, COM ANÁLISE PERIÓDICA DAS ÁGUAS, LIMPEZA E DESINFECÇÃO do Hospital de Emergência e Pronto Socorro João Paulo II - HEPSJP II, AMI, HBAP, HICD HRE e COHREC desta Secretaria de Estado da Saúde de Rondônia – SESAU/RO, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Locação de imóvel comercial para instalações da Coordenação Estadual de Nutrição Enteral - CENE, conforme requisitos mínimos exigidos, afim de atender a Secretaria Estado de Saúde de Rondônia - SESAU/RO, por um período de 12 (doze) meses, com possibilidade de prorrogação.</t>
+  </si>
+  <si>
+    <t>0036.494502/2021-15</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na Prestação de Serviços de Coleta Interna e Externa, Recolhimento, Transporte, Tratamento e Destinação Final dos Resíduos de Serviços de Saúde – RSS (Grupos A, B, E e eventualmente C), de forma contínua, visando atender as Unidades da SESAU, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.051069/2023-99</t>
+  </si>
+  <si>
+    <t>Registro de Preços para a Contratação de Empresa Especializada na Prestação de Serviços de festividades/homenagens, visando atender as necessidades da Secretaria do Estado da Saúde - SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0046.000875/2024-61</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na Prestação de Serviços de Coleta Interna e Externa, Recolhimento, Transporte, Tratamento e Destinação Final dos Resíduos de Serviços de Saúde – RSS (Grupos A, B e E), de forma Emergencial, visando atender o Laboratório de Fronteira de Rondônia (LAFRON) e Hospital Regional de Extrema (HRE), pelo período de 1 (Um) ano ou até que se conclua o processo licitatório 0036.494502/2021-15.</t>
+  </si>
+  <si>
+    <t>0054.001524/2024-78</t>
+  </si>
+  <si>
+    <t>Contratação da Empresa Especializada na Prestação de Serviços de Coleta Interna e Externa, Transporte, Tratamento (incineração ou autoclavagem e incineração) e Destinação Final dos Resíduos de Serviços de Saúde RSS (Grupos A, B, E e eventualmente C), de forma contínua, para atender o Centro de Reabilitação de Rondônia de forma contínua.</t>
+  </si>
+  <si>
+    <t>0053.002612/2024-05</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa especializada, no ramo de engenharia hospitalar, para prestação de serviços de manutenção preditiva, preventiva e corretiva, com fornecimento de peças, materiais de consumo, insumos e mão de obra, para os sistemas, equipamentos e instalações do Centro de Medicina Tropical de Rondônia (CEMETRON)</t>
+  </si>
+  <si>
+    <t>0036.032378/2024-41</t>
+  </si>
+  <si>
+    <t>Licitatório Manutenção de ar condicionado</t>
+  </si>
+  <si>
+    <t>0053.505372/2021-45</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviço de limpeza de caixa d'água, visando atender as necessidades do Centro de Medicina Tropical de Rondônia - CEMETRON, Hospital Regional de São Francisco do Guaporé - HRSFG e Centro de Reabilitação de Rondônia - CERO, por um período de 60 meses, prorrogaéveis por igual período.</t>
+  </si>
+  <si>
+    <t>0036.028372/2024-79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locação de imóvel com o objetivo comportar bens de patrimônio público, garantindo assim a segurança, organização e gestão apropriada dos materiais e bens sob a responsabilidade da Gerência de Transporte e Abastecimento (GAT), Coordenadoria de engenharia e Arquitetura em Saúde (CEAS) e Coordenadoria de Almoxarifado e Patrimônio (CAP), pelo período de 1 (um) ano, podendo ser prorrogado sucessivamente, respeitada a vigência máxima decenal, conforme previsto no art. 107 da Lei nº 14.133/2021. 
+</t>
+  </si>
+  <si>
+    <t>0036.006969/2025-43</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços contínuos de recepção, com emprego de mão-de-obra qualificada e habilitada, bem como fornecimento dos materiais necessários à execução do serviço, visando atender ao Hospital Infantil Cosme e Damião, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0049.000906/2023-72</t>
+  </si>
+  <si>
+    <t>Locação de Grupo Gerador para o HB - Licitatório</t>
+  </si>
+  <si>
+    <t>0036.013541/2025-57</t>
+  </si>
+  <si>
+    <t>Seminário- DOMINANDO AS CONTRATAÇÕES PÚBLICAS: Tendências e Novidades da Lei 14.133/2021, a ser realizado nos dias 23, 24 e 25 de abril de 2025 (curso)</t>
+  </si>
+  <si>
+    <t>0036.009983/2025-07</t>
+  </si>
+  <si>
+    <t>(curso) - 20º Congresso Brasileiro de Gestão, Projetos e Liderança realizado pelo Project Management Institute - PMI, sendo 5 (cinco) servidores de forma presencial, nos dias 22 e 23 de Abril de 2025 na cidade de Fortaleza/CE.</t>
+  </si>
+  <si>
+    <t>0036.058703/2024-03</t>
+  </si>
+  <si>
+    <t>Inexigibilidade - Contratação de empresa especializada em manutenção preventiva e corretiva com fornecimento de peças, executada de forma contínua em Ventiladores Pulmonares da marca MAGNAMED, para atender as necessidades Hospital Regional de Cacoal - HRC e Hospital Infantil Cosme e Damião-HICD/RO.</t>
+  </si>
+  <si>
+    <t>0063.002259/2023-55</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa para prestação do Serviço de alimentação para atender os pacientes das oficinas terapêuticas e grupo terapêuticos do Centro de Atenção Psicossocial Madeira Mamoré - CAPS II, de forma contínua, 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.057140/2024-28</t>
+  </si>
+  <si>
+    <t>Emergencial - Controle e monitoramento de água potável, com análise periódica das águas, limpeza e desinfecção visando atender as unidades hospitalares: Hospital de Emergência e Pronto Socorro João Paulo II - JP II</t>
+  </si>
+  <si>
+    <t>0036.017798/2025-88</t>
+  </si>
+  <si>
+    <t>curso "Contrato de Gestão: planejamento, celebração, execução e prestação de contas", realizado pelo Grupo Orzil, sendo 5 (cinco) servidores de forma presencial, nos dias 15 e 16 de maio de 2025, na cidade de Brasília/DF.</t>
+  </si>
+  <si>
+    <t>Emergencial - prestação de Serviço de Higienização e Limpeza Hospitalar, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento dos resíduos Grupo "D", visando atender as necessidades do Hospital Regional de Extrema HRE</t>
+  </si>
+  <si>
+    <t>0036.001619/2025-91</t>
+  </si>
+  <si>
+    <t>(curso) CAPACITAÇÃO E APERFEIÇOAMENTO, para participação de 04 (quatro) servidores no Curso de Como Elaborar Concurso Público e Processo Seletivo Simplificado, dos dias 28 a 30 de abril de 2025 em Brasília/DF</t>
+  </si>
+  <si>
+    <t>0049.070072/2022-81</t>
+  </si>
+  <si>
+    <t>Manutenção preventiva e corretiva com fornecimento de peças, executada de forma contínua em equipamentos médico hospitalares da marca Drager, visando atender às necessidades do Hospital de Base Dr. Ary Pinheiro - HBAP, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON e Hospital de Retaguarda de Rondônia-HRRO, desta Secretaria de Estado da Saúde de Rondônia – SESAU-RO, por um período de 12 (doze) meses​.</t>
+  </si>
+  <si>
+    <t>0036.021467/2023-81</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Fornecedora dos Serviços de Higienização e Limpeza Hospitalar, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Coleta interna dos resíduos dos Grupos A, D e E para atender o Centro de Diálise de Ariquemes, em caráter contínuo, por um período de 60 (sessenta) meses, conforme Art. 106 da Lei Federal nº 14.133 de 1° de abril de 2021.</t>
+  </si>
+  <si>
+    <t>0036.024410/2024-14</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Construção da base do reservatório em concreto armado (sobre o solo); fornecimento e instalação de cisterna pré-fabricada com capacidade de 10.000 litros, tipo Tanque, sobre a base (não aterrado), com extravasor, tubos, conexões, entrada e saída de água; conjunto motobomba para recalque tipo centrífuga de 1 CV para comprimento máximo de 25 metros; instalações de quadro elétrico com comprimento máximo de 15 metros, cabos elétricos, disjuntor e automação, conforme Decreto nº 29.252 de 04 de julho de 2024, pelo período de até 1 (um) ano.</t>
+  </si>
+  <si>
+    <t>0036.018638/2024-75</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada no fornecimento de gás especial HÉLIO LÍQUIDO, visando atender o Hospital Regional de Cacoal (HRC), com abastecimento conforme a necessidade pontual da unidade, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.042461/2023-47</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de Serviços de Manutenção Preventiva e Corretiva em Grupo Gerador, com fornecimento de quaisquer componentes e/ou troca de peças novas e originais, de forma contínua para atender ao Hospital Regional de Cacoal - HRC e Hospital de Urgencia e Emergência Regional de Cacoal - HEURO, por um período de 5 (cinco) anos, nos moldes do Art. 106º da Lei Federal n.º 14.133 de 1º Abril de 2021.</t>
+  </si>
+  <si>
+    <t>0036.017639/2024-01</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de desinsetização; desratização, descupinização e desalojamento de pombos e morcegos, como também o combate aos mosquitos e larvas em áreas internas e externas nas dependências da Coordenadoria de Gestão e Assistência Farmacêutica - CGAF, Coordenadoria Nutrição Enteral - CENE, Conselho Estadual de Saúde - CES, Comissão Intergestores Bipartite – CIB, Centro de Atenção Psicossocial - CAPS, Coordenadoria de Almoxarifado e Patrimônio - CAP, de forma contínua, por um período de 60 (sessenta) meses.</t>
+  </si>
+  <si>
+    <t>0036.027422/2023-10</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de Controle de Vetores e Pragas Urbanas, englobando: desinsetização, desratização, descupinização e desalojamento de pombos e morcegos, bem como o combate a mosquitos, lavras e carrapatos, para atender as necessidades das unidades pertencentes a esta Secretaria de Estado da Saúde - SESAU/RO, por um período de 5 (cinco) anos.</t>
+  </si>
+  <si>
+    <t>0036.033164/2024-91</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na prestação de Serviços de Engenharia Clínica, Incluindo Serviço de Gerenciamento de Equipamentos, Manutenção Corretiva, Preventiva, Preditiva e Calibração dos Equipamentos com Reposição de Peças, Acessórios e Insumos para atender ao Hospital Estadual e Pronto Socorro João Paulo II e Assistência Médica Intensiva - AMI, Centro de Dialise Vale do Jamari - CDVJ e Hospital Regional de Extrema HRE.</t>
+  </si>
+  <si>
+    <t>0062.000185/2023-22</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em Serviços de Higienização e Limpeza Hospitalar e assemelhadas, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento Interno dos Resíduos do Grupo “D”, visando à obtenção de adequadas condições de salubridade e higiene em dependências da Policlínica Oswaldo Cruz - POC, Laboratoriais e Ambulatoriais do Laboratório Estadual de Patologia e Análises Clínicas - LEPAC e Hospital Regional de Extrema - HRE, pelo período de 60 (sessenta) meses de forma contínua.</t>
+  </si>
+  <si>
+    <t>0036.045810/2024-63</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa para Prestação de Serviço de Levantamento Radiométrico, Controle de Qualidade e Teste de Radiação de Fuga, com Emissão de Laudos para atender o Hospital Regional de São Francisco do Guaporé-HRSFG e Hospital Regional de Buritis-HRB, por um período de 5 (cinco) anos.</t>
+  </si>
+  <si>
+    <t>0036.031073/2024-11</t>
+  </si>
+  <si>
+    <t>Contratação, por Registro de Preço, de empresa(s) especializada(s) na prestação de serviços de Estudo Prévio/Análise, Adequação, Manutenção, Limpeza e Desinfecção em poços tubulares para atender às necessidades das unidades Laboratório Central de Saúde Pública - LACEN, Centro de Reabilitação de Rondônia - CERO, Assistência Médica Intensiva - AMI, Centro de Medicina Tropical de Rondônia - CEMETRON, Hospital Retaguarda de Rondônia - HRRO, Hospital Regional Cacoal - HRC, Hospital São Francisco do Guaporé - HRSFG, Hospital Regional de Extrema - HRE e Laboratório de Fronteira de Rondônia - LAFRON, por um período de 1 (um) ano, nos moldes da Lei Federal n.º 14.133 de 1º Abril de 2021..</t>
+  </si>
+  <si>
+    <t>0036.003690/2024-27</t>
+  </si>
+  <si>
+    <t>Contratação empresa especializada em locação de Outdoor de 9m x 3m e impressão colorido em serigrafia, com instalação e exibição conforme campanhas definidas pela coordenadoria de doenças e condições crônicas - CDCC/SDTECS/SESAU, sendo de responsabilidade da contratante a criação e envio da arte da campanha para a empresa vencedora. Considerando sempre o período exibição de 2 BI-SEMANAS de forma continua, por cada campanha, sendo 5 campanhas a serem implementadas no decorrer do ano.</t>
+  </si>
+  <si>
+    <t>0036.037259/2023-01</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de locação do sistema de tratamento de água por osmose reversa duplo passo para serviços de terapia renal substitutiva com manutenção, operação e controle dos pacientes crônicos em tratamento de hemodiálise no Centro de Diálise do Vale do Jamari - CDVJ, com capacidade de abastecimento para 38 (trinta e oito) máquinas de hemodiálise em funcionamento, e locação da estação de tratamento de efluente de tratamento hemodiálitico para redução de DBO e DQO tornando-o apto a ser destinado a lançamento em coletor de rede pluvial e ou em corpo hídrico em conformidade a legislação vigente /Conama – Resolução nº 430, de 13 de Maio de 2011, por um período de 5 (cinco) anos.</t>
+  </si>
+  <si>
+    <t>0036.547611/2021-42</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de Rouparia Hospitalar (Enxoval), visando atender as Unidades de Saúde do Hospital Infantil Cosme e Damião - HICD; Hospital Regional São Francisco do Guaporé - HRSFG, Complexo Hospitalar Regional de Cacoal - COHREC, Hospital de Base Doutor Ary Pinheiro - HBAP, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON/ANEXO JBS, Hospital Regional de Buritis - HRB, Hospital e Pronto Socorro João Paulo II - JP II, Centro de Diagnóstico por Imagem de Rondônia - CDI; Hospital Regional de Extrema - HRE e Assistência Médica Intensiva - AMI-24h., por um Período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.061224/2024-66</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em prestação de serviços de manutenção preventiva e corretiva, de forma continua, com fornecimento e reposição de peças, acessórios e componentes eletrônicos dos Sistemas de Climatização, de expansão indireta CHILLER com capacidade de 150 TR e 9,92 TR e de expansão direta através Condicionador de Ar Tipo Self Contained com Condensador a Ar Remoto de 7,5 TR, conforme dados técnicos em anexo, para atender o Hospital de Base Dr. Ary Pinheiro, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.010175/2025-84</t>
+  </si>
+  <si>
+    <t>Contratação Emergencial de Empresa Especializada na Prestação de Serviços de coleta interna e externa, transporte, tratamento e destinação final dos resíduos de Serviços de Saúde - RSS (Grupos A, B e E) de forma contínua, para atender o Hospital de Retaguarda e Rondônia, por um período de 1 (um) ano, ou até que se conclua o Processo licitatório 0036.494502/2021-15 conforme estabelecido nos moldes da Lei nº 14.133/2021.</t>
+  </si>
+  <si>
+    <t>0036.004010/2025-73</t>
+  </si>
+  <si>
+    <t>Contratação emergencial de Empresa Especializada em serviços de Controle de Vetores e Pragas Urbanas englobando: desinsetização, desratização, descupinização e desalojamento de pombos e morcegos, bem como o combate a mosquitos e lavras em atendimento ao Hospital Infantil Cosme e Damião - HICD, Hospital Regional de São Francisco do Guaporé - HRSF, Hospital de Base Dr. Ary Pinheiro - HBAP, Hospital e Pronto Socorro João Paulo II - HPJPII, Assistência Médica Interdisciplinar - AMI, Hospital Regional de Cacoal - HRC, Policlínica Oswaldo Cruz - POC, Centro de Reabilitação de Rondônia - CERO, Laboratório de Fronteira- LAFRON, Laboratório Central de Saúde Pública de Rondônia - LACEN, Centro de Diagnóstico por Imagem de Rondônia - CDI, Centro de Medicina Tropical - CEMETRON, Hospital Regional de Extrema - HRE, Hospital de Retaguarda de Rondônia - HRRO e Hospital Regional de Buritis - HRB, por um período de 1 (um) ano, ou até que se conclua o processo licitatório 0036.027422/2023-10.</t>
+  </si>
+  <si>
+    <t>0036.017945/2025-10</t>
+  </si>
+  <si>
+    <t>Contratação de manutenção corretiva dos equipamentos Arco Cirúrgicos da marca VMI disponíveis na unidade Hospital de Base Dr. Ary Pinheiro</t>
+  </si>
+  <si>
+    <t>Contratação, por Registro de Preço, de empresa(s) especializada(s) na prestação de serviços de Estudo Prévio/Análise, Adequação, Manutenção, Limpeza e Desinfecção em poços tubulares para atender às necessidades das unidades Laboratório Central de Saúde Pública - LACEN, Centro de Reabilitação de Rondônia - CERO, Assistência Médica Intensiva - AMI, Centro de Medicina Tropical de Rondônia - CEMETRON, Hospital Retaguarda de Rondônia - HRRO, Hospital Regional Cacoal - HRC, Hospital São Francisco do Guaporé - HRSFG, Hospital Regional de Extrema - HRE e Laboratório de Fronteira de Rondônia - LAFRON, por um período de 1 (um) ano, nos moldes da Lei Federal n.º 14.133 de 1º Abril de 2021.</t>
+  </si>
+  <si>
+    <t>0049.004223/2024-75</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços médicos complementares especializados na área de Pediatria e Neonatologia, com a finalidade de atender a demanda de usuários da saúde pública recém-nascidos do setor de neonatologia nas dependências do Hospital de Base Dr. Ary Pinheiro, por um período de 12 meses</t>
+  </si>
+  <si>
+    <t>0036.003868/2024-30</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços médicos de anestesiologia, visando atender todas as unidades estaduais</t>
+  </si>
+  <si>
+    <t>0049.013605/2023-17</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços médicos complementares especializados na área de nefrologia, para atender as demandas dos usuários da saúde pública nas dependências do Hospital de Base Dr. Ary Pinheiro (HBAP), Assistência Médica Intensiva (AMI), e Centro de Medicina Tropical de Rondônia (CEMETRON), pertencentes a Secretaria de Estado da Saúde - SESAU, de forma contínua, pelo período de 12 meses.</t>
+  </si>
+  <si>
+    <t>0036.005381/2024-91</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em disponibilização de médicos intensivistas pediátricos em regime de plantão, com objetivo de atender a Unidade de Terapia Intensiva Pediátrica - UTIP do Hospital Infantil Cosme e Damião - HICD, por um período de 1 (um) ano .</t>
+  </si>
+  <si>
+    <t>0036.006652/2023-45</t>
+  </si>
+  <si>
+    <t>Contratação de serviços/procedimentos inseridos nos subgrupos de Diagnóstico em Laboratório Clínico, com a seguinte forma de organização: Exames Bioquímicos, Hematológicos e Hemostasia, Sorológicos e Imunológicos, Colprológicos, Uroanálise, Hormonais, Toxicológicos ou de Monitorização Terapêutica, Microbiológicos, Genética, Imunohistoquímica, Imunohematológicos e Citologia em outros Líquidos Biológicos e Anatomopatologia; inseridos na Tabela de Procedimentos do Sistema Único de Saúde (SIGTAP) editada pelo Ministério de Saúde, abrangendo as áreas respectivas descritas no edital, em âmbito ambulatorial e hospitalar 24 (vinte e quatro) horas por dia com suporte para as UTI’S, Leitos Clínicos e Ambulatoriais, de forma contínua, por um período de 12 (doze) meses. HRC, HEURO e HRE.</t>
+  </si>
+  <si>
+    <t>0036.100288/2022-28</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços médicos complementares especializados na área de cardiologia e neurologia com especialização em hemodinâmica, de forma contínua, com a finalidade de atender a demanda de usuários da saúde pública nas dependências do Hospital de Base Dr. Ary Pinheiro.</t>
+  </si>
+  <si>
+    <t>0036.024936/2024-02</t>
+  </si>
+  <si>
+    <t>Contratação de profissionais médicos para atendimento em Cirurgia Geral, bem como subespecilidades cirúrgicas, quando não disponível no Complexo de Cacoal, nas demandas dos usuários da saúde pública, nas dependências do Hospital de Urgência e Emergência Regional de Cacoal - HEURO, pertencente a Secretaria de Estado da Saúde - SESAU, pelo período de até 12 meses, a partir da primeira assinatura contratual, em conformidade com o disposto no Art. 107, da Lei 14.133 de 1º de abril de 2021.</t>
+  </si>
+  <si>
+    <t>0036.042116/2023-11</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de Neurologia Cirúrgica Hospitalar e Ambulatorial, Neurologia Clínica e Neurologia Pediátrica (atendimento inicial, evolução diária, cirurgias, alta hospitalar e atendimento ambulatorial, Exames complementares, neurofisiologia e neurointervecionismo ), sob sistema de comodato com fornecimento de insumos</t>
+  </si>
+  <si>
+    <t>0036.037319/2024-69</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços médicos complementares especializados na área de Pediatria e Neonatologia, com a finalidade de atender a demanda de usuários da saúde pública recém-nascidos do setor de neonatologia nas dependências do Hospital Regional de Cacoal (HRC) pelo período de 12 meses</t>
+  </si>
+  <si>
+    <t>0036.044438/2024-78</t>
+  </si>
+  <si>
+    <t>Contratação de estabelecimento de saúde especializado à realizar transplante renal de doador falecido e intervivo, devidamente credenciada na Central Estadual de Transplante e autorizada pelo Sistema Nacional de Transplante - Ministério da Saúde, para a realização de procedimentos relacionados a captação e ao transplante de rins em todas as suas fases (pré-transplante, transplante e pós-transplante incluindo internações de intercorrências no pós transplante renal seja de doadores vivos e/ou falecidos), a fim de atender a demanda de pacientes com falência renal crônica, com base na Constituição Federal, arts. 37, XXIII e 199, na Lei 8080/90, aplicando-se subsidiariamente na Lei nº 14.133 de 1º de abril de 2021 e suas alterações, conforme Documento de Oficialização de Demanda nº 87 (0052858164).</t>
+  </si>
+  <si>
+    <t>0036.058593/2024-71</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em prestação de Serviços Médicos na área de Ortopedia e Traumatologia, de Média e Alta Complexidade, de forma contínua, com a finalidade de atender demanda em ortopedia de usuários da saúde pública do Hospitalar Regional de Cacoal de usuários da saúde pública do Hospitalar Regional de Cacoal, que atende toda a população da MACRO II de Saúde de Rondônia, para atendimento pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.060770/2024-80</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de Serviços Médicos especializados na área de Ortopedia e Traumatologia, de Média e Alta Complexidade, de forma contínua, com a finalidade de atender demanda em ortopedia de usuários da saúde pública do Hospitalar Regional de Cacoal, que atende toda a população da MACRO II de Saúde de Rondônia, por um período de 01 (um) ano, podendo ser prorrogado conforme previsto nos Art. 106 e 107 da lei n.º 14.133</t>
+  </si>
+  <si>
+    <t>0046.000902/2024-03</t>
+  </si>
+  <si>
+    <t>Contratação de fornecimento de insumos laboratoriais, para realização de análise de águas envasadas (água mineral) para consumo humano atendendo o Setor de Produtos e Meio Ambiente do LACEN RO por um período de 12 meses conforme detalhamento do objeto apresentado abaixo.</t>
+  </si>
+  <si>
+    <t>0046.000720/2024-24</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada no fornecimento continuado de (Kits/Reagentes) com todo sistema/solução de automação laboratorial em regime de "COMODATO", para realização de exames de biologia molecular (PCR Multiplex) em testagem rápida silmutânea para multialvos ou painéis sindrômicos (vírus, bactérias, fungos, parasitas e genes de resistência), para atender ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO, pertencente ao quadro da Secretaria de Estado da Saúde – SESAU/RO, de forma continuada.</t>
+  </si>
+  <si>
+    <t>0036.014212/2024-42</t>
+  </si>
+  <si>
+    <t>Aquisição de Equipamentos Laboratoriais, para atendimento ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO e a sua rede de laboratórios (filiais), cujo recurso é proveniente e específico do Programa: NOVO PAC - ESTRUTURAÇÃO DA VIGILÂNCIA LABORATORIAL EM SAÚDE E AMBIENTES E RESPOSTA AS EMERGÊNCIAS EM SAÚDE, com o Componente: ESTRUTURAÇÃO DE LABORATÓRIOS DA REDE NACIONAL DE LABORATÓRIOS EM SAÚDE PÚBLICA</t>
+  </si>
+  <si>
+    <t>0046.000368/2024-27</t>
+  </si>
+  <si>
+    <t>Aquisição de insumos para realização de sequenciamento genético de amostras de vírus e bactérias para atender o laboratório de virologia do LACEN/RO.</t>
+  </si>
+  <si>
+    <t>0036.008654/2025-31</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada no Fornecimento de Sistema de Automação Laboratorial (equipamentos) e todos os materiais, reagentes e acessórios necessários à realização de TESTES BIOQUIMICA, com vistas no atendimento às necessidades da Secretaria de Estado da Saúde - SESAU.</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada no Fornecimento de Sistemas de Automação Laboratorial (equipamentos) e todos os materiais, reagentes e acessórios necessários à realização de TESTES de Gasometria, com vistas no atendimento às necessidades das unidades hospitalares, da Secretaria de Estado da Saúde - SESAU.</t>
+  </si>
+  <si>
+    <t>0050.010429/2024-03</t>
+  </si>
+  <si>
+    <t>Contratação de plantões de médico vascular para atendimentos de pacientes e realização de procedimentos cirúrgicos nas depêndencias do HEURO, HRC, JPII, HBAP, HICD, CEMETROM E POC</t>
+  </si>
+  <si>
+    <t>0036.010062/2025-89</t>
+  </si>
+  <si>
+    <t>0036.006167/2025-33</t>
+  </si>
+  <si>
+    <t>Contratação de serviços/procedimentos inseridos nos subgrupos de Diagnóstico em Laboratório Clínico, com a seguinte forma de organização: Exames Bioquímicos, Hematológicos e Hemostasia, Sorológicos e Imunológicos, Colprológicos, Uroanálise, Hormonais, Toxicológicos ou de Monitorização Terapêutica, Microbiológicos, Genética, Imunohistoquímica, Imunohematológicos e Citologia em outros Líquidos Biológicos e Anatomopatologia; inseridos na Tabela de Procedimentos do Sistema Único de Saúde (SIGTAP) editada pelo Ministério de Saúde, abrangendo as áreas respectivas descritas no edital, em âmbito ambulatorial e hospitalar 24 (vinte e quatro) horas por dia com suporte para as UTI’S, Leitos Clínicos e Ambulatoriais, de forma contínua, por um período de 12 (doze) meses. HRC, HEURO.</t>
+  </si>
+  <si>
+    <t>0036.061042/2024-95</t>
+  </si>
+  <si>
+    <t>Seleção Pública de Entidade Privada, sem fins lucrativos, previamente qualificada como Organização Social de Saúde – OSS no Estado de Rondônia, para a celebração de Contrato de Gestão, com o objetivo fomentar a absorção do gerenciamento, operacionalização e execução dos serviços de saúde do Hospital de Base Dr. Ary Pinheiro - HBAP, por meio da gestão compartilhada.</t>
+  </si>
+  <si>
+    <t>Organização Social</t>
+  </si>
+  <si>
+    <t>0036009792/2025-37</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada para o gerenciamento da estrutura física e de pessoal, bem como a execução de serviços profissionais na área médico-hospitalar, incluindo o fornecimento de bens e insumos necessários para o pleno funcionamento das unidades, visando assegurar o atendimento integral e contínuo à populaççao da região MACRO II, compreendidos pelos hospitais HEURO, HRC e HRSFG</t>
+  </si>
+  <si>
+    <t>0036.003630/2024-12</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de Balança Antropométrica e de Uso Geral, visando atender as Unidades de Saúde do Hospital de Base Dr. Ary Pinheiro, Hospital Regional de Buritis, Hospital Regional de São Francisco, Hospital de Urgência e Emergência Regional de Cacoal - HEURO, Hospital Regional de Cacoal - HRC, Hospital Regional de Extrema - HRE, Assistência Médica Intensiva - AMI, Hospital Infantil Cosme e Damião - HICD, Policlínica Oswaldo Cruz - POC, Hospital de Retaguarda de Rondônia - HRRO, Hospital Estadual e Pronto Socorro João Paulo II, por um Período de 1 (um) ano.</t>
+  </si>
+  <si>
+    <t>0036.001261/2025-04</t>
+  </si>
+  <si>
+    <t>REGISTRO DE PREÇO PARA FUTURA E EVENTUAL AQUISIÇÃO DE BRINQUEDOS, MATERIAIS EDUCATIVOS E PEDAGÓGICOS</t>
+  </si>
+  <si>
+    <t>0036.002097/2025-44</t>
+  </si>
+  <si>
+    <t>Registro de Preço para a futura e eventual aquisição de CABOS E ACESSÓRIOS PARA EQUIPAMENTOS MÉDICO-HOSPITALARES, a fim de atender as unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia"</t>
+  </si>
+  <si>
+    <t>0036.002590/2025-64</t>
+  </si>
+  <si>
+    <t>Registro de preços para aquisição de generos alimentícios (café e açucar) para suprir as necessidades das unidades de saúde vinculadas a Secretaria de Estado da Saúde - SESAU/RO, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0050.072218/2022-94</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de aparelhos de Cardioversor/Desfibrilador visando atender as necessidades das Unidades da Secretaria do Estado da Saúde de Rondônia - SESAU, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0049.073242/2022-80</t>
+  </si>
+  <si>
+    <t>Aquisição de carros coletores, visando atender as necessidades das Unidades da Secretaria de Estado da Saúde de Rondônia - SESAU/RO, por um período de 12 meses</t>
+  </si>
+  <si>
+    <t>0036.000381/2025-86</t>
+  </si>
+  <si>
+    <t>Registro de Preços para aquisição de Carros Coletores, Suporte para Hamper, Calandra, Coifa e Triturador de Tecidos, visando atender as necessidades das unidades da Secretaria de Estado da Saúde do Estado de Rondônia - SESAU/RO, por um período de 12 (doze) meses</t>
+  </si>
+  <si>
+    <t>0036.024493/2024-41</t>
+  </si>
+  <si>
+    <t>Registro de preços para aquisição de CENTRAL DE MONITORAMENTO COM MONITORES, GATEWAY E VENTILADORES, para atender às unidades de saúde da SESAU/RO</t>
+  </si>
+  <si>
+    <t>0036.000533/2025-41</t>
+  </si>
+  <si>
+    <t>Aquisição de coffe break</t>
+  </si>
+  <si>
+    <t>0036.041915/2024-43</t>
+  </si>
+  <si>
+    <t>Bens de consumo comum: Colchões Hospitalares, Travesseiros e Tolos de Posicionamento, destinados a atender as necessidades das unidades de saúde estaduais, tanto hospitalares quanto ambulatoriais, da Secretaria de Estado da Saúde (SESAU).</t>
+  </si>
+  <si>
+    <t>0066.210706/2021-56</t>
+  </si>
+  <si>
+    <t>Registro de preços para futura e eventual aquisição de ferramentas e materiais para manutenção predial de hidráulica, elétrica, pintura e outros, fora da tabela SINAPI, em atendimento as unidades de saúde vinculadas à SESAU/RO, pelo período de 01 (um) ano</t>
+  </si>
+  <si>
+    <t>0036.050120/2023-45</t>
+  </si>
+  <si>
+    <t>Aquisição de formulários de aplicação testes e protocolos diagnósticos especializados, destinados ao rastreamento e diagnóstico de Transtorno do Espectro Autista (TEA) e outros transtornos neurotípicos</t>
+  </si>
+  <si>
+    <t>0036.077824/2022-84</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual Aquisição de Materiais de Costura, visando atender as necessidades do Hospital Regional São Francisco do Guaporé - HRSF, Centro de Diálise de Ariquemes - CDA, Hospital e Pronto Socorro João Paulo II - JP II, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON, Policlínica Oswaldo Cruz - POC, Hospital Regional de Buritis - HRB e Hospital Infantil Cosme e Damião - HICD, pertencentes a Secretaria de Estado da Saúde - SESAU, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.022401/2024-99</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de permanentes para atender as necessidades do Núcleo de Farmácia Hospitalar e Setores Assistenciais chaves, do Hospital Regional de Cacoal - HRC, vinculado a Secretária de Estado da Saúde - SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0036.078020/2022-01</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos Médico-Hospitalares, visando atender as necessidades das Hospital Regional de São Francisco do Guaporé (HRSF), serviço de Atendimento Multidisciplinar Domiciliar (SAMD), Policlínica Oswaldo Cruz (POC), Hospital Regional de Extrema (HRE), Hospital Infantil São Cosme e Damião (HICD), Hospital e Pronto Socorro João Paulo II (JPII).</t>
+  </si>
+  <si>
+    <t>0036.019875/2023-72</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de materiais permanentes (médicos-hospitalares), visando atender as unidades da Secretária do Estado da Saúde, por um período de 12 (doze) meses</t>
+  </si>
+  <si>
+    <t>0036.059771/2024-81</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos técnológocos e equiapementos médico-hospitalar para atender as necessidades do Hospital Regional de Extrema</t>
+  </si>
+  <si>
+    <t>0036.052994/2024-18</t>
+  </si>
+  <si>
+    <t>Registro de Preço para a futura e eventual aquisição de EQUIPAMENTOS MÉDICO-HOSPITALARES ELETROPORTÁTEIS a fim de atender as unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia</t>
+  </si>
+  <si>
+    <t>0036.024010/2024-17</t>
+  </si>
+  <si>
+    <t>Aquisição de bomba de infusão, incubadora, ventilador mecânico e bolsa EMS para atender a Central de Apoio Aéreo - CAA</t>
+  </si>
+  <si>
+    <t>0050.014595/2024-71</t>
+  </si>
+  <si>
+    <t>Aquisição de Equipamentos de Proteção Individual (EPIs) destinados à equipe de manutenção do Hospital Estadual e Pronto-Socorro João Paulo II, com o objetivo de assegurar a segurança e a saúde dos trabalhadores no exercício de suas funções por um período de 12 meses.</t>
+  </si>
+  <si>
+    <t>0060.114123/2021-55</t>
+  </si>
+  <si>
+    <t>Registro de preço para futura e eventual Aquisição de Equipamentos de Proteção Individual – EPI’S e Equipamentos de Proteção Coletiva - EPC</t>
+  </si>
+  <si>
+    <t>0036.088787/2022-30</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de Radiografia Computadorizada - CR e CASSETE,​ visando atender as Unidades da SESAU, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>0036.044720/2024-55</t>
+  </si>
+  <si>
+    <t>Aquisição de EQUIPAMENTOS E ACESSÓRIOS DE DIAGNÓSTICO POR IMAGEM</t>
+  </si>
+  <si>
+    <t>0036.100610/2022-19</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos medico-hospitalar para atender as necessidades do Hospital Regional de Cacoal</t>
+  </si>
+  <si>
+    <t>0036.030869/2024-57</t>
+  </si>
+  <si>
+    <t>Aquisição de bens de consumo: UNIFORMES/FARDAMENTO E ACESSÓRIOS DESTINADOS À IDENTIFICAÇÃO E PADRONIZAÇÃO DOS SERVIDORES DOS SETORES DOS ALMOXARIFADOS E DISPENSAÇÃO da Secretaria de Estado da Saúde - SESAU.</t>
+  </si>
+  <si>
+    <t>0036.018964/2024-82</t>
+  </si>
+  <si>
+    <t>Registro de preço para futura e eventual aquisição de equipamentos e materiais permanentes de Fisioterapia, visando atender as unidades de saúde vinculadas à SESAU/RO</t>
+  </si>
+  <si>
+    <t>0036.053382/2024-42</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual Aquisição de Equipamento/Máquina de Hemodiálise visando atender as unidades assistenciais (Hospital Infantil Cosme e Damião, CEMETRON, Hospital e Pronto Socorro João Paulo II - HPSJPII e Hospital de Base Dr. Ary Pinheiro).</t>
+  </si>
+  <si>
+    <t>0036.032668/2024-94</t>
+  </si>
+  <si>
+    <t>Aquisição de uma Máquina de Hemodiálise, para atender ao Serviço de Hemodiálise do Hospital de Urgência e Emergência Regional de Cacoal - HEURO</t>
+  </si>
+  <si>
+    <t>0049.003774/2024-11</t>
+  </si>
+  <si>
+    <t>Aquisição de máquinas para hemodiálise a fim de suprir as necessidades do Centro de Diálise Madeira Mamoré - CDMM.</t>
+  </si>
+  <si>
+    <t>0036.008843/2024-22</t>
+  </si>
+  <si>
+    <t>Aquisição de material de informática</t>
+  </si>
+  <si>
+    <t>0049.002717/2024-15</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE ESTABILIZADOR DE TENSÃO, 2500 VA, 220 V, MONOFÁSICO, PARA SUPORTE À ULTRAFREEZER -80°C DO NÚCLEO DE TRANSPLANTE ÓSSEO DO HOSPITAL DE BASE DOUTOR ARY PINHEIRO - HBAP.</t>
+  </si>
+  <si>
+    <t>0066.163526/2019-53</t>
+  </si>
+  <si>
+    <t>Aquisição de Equipamentos Eletrônicos e Mobiliários para Reestruturar a Comissão de Residência Multiprofissional (COREMU) e Comissão de Residência Médica (COREME), conforme versa o plano de Trabalho COHREC - COREME</t>
+  </si>
+  <si>
+    <t>0036.036470/2024-80</t>
+  </si>
+  <si>
+    <t>Registro de Preço (SRP) do tipo menor preço por lote, visando à futura, eventual aquisição de Insumos para Lavanderia Hospitalar (detergente concentrado, alvejante e outros), para atender às necessidades dos núcleos de lavanderia hospitalar Estaduais gerenciadas pela Secretaria de Estado da Saúde - SESAU/RO</t>
+  </si>
+  <si>
+    <t>0049.015211/2023-95</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual aquisição de equipamentos laboratoriais, sendo ( agitador kline, banho maria e outros), visando atender as unidades de saúde vinculadas à SESAU/RO, por um período de 1 (um) ano.</t>
+  </si>
+  <si>
+    <t>0045.000109/2023-25</t>
+  </si>
+  <si>
+    <t>Aquisição de reagentes laboratoriais (KIT DE EXTRAÇÃO DE DNA, ÁCIDO BÓRICO, CLORETO DE SÓDIO, EDTA SAL DISSÓDICO (2H20) P.A, TRIS (HIDROXIMETRIL) AMINOMETANO, ÁLCOOL ETÍLICO, CORANTE AZUL METILENO 1% SOLUÇÃO AQUOSA E CORANTE GIEMSA) para atender o Centro de Pesquisa de Medicina Tropical de Rondônia-CEPEM/SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0049.002988/2024-71</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais permanentes a fim de suprir as necessidades do Centro de Diálise Madeira Mamoré - CDMM</t>
+  </si>
+  <si>
+    <t>0036.053793/2024-38</t>
+  </si>
+  <si>
+    <t>Aquisição de manequins e simuladores humanos para atividades de educação em saúde oferecidas pelo laboratório de simulação realística do Instituto Estadual de Educação em Saúde Pública de Rondônia- IESPRO/CETAS/SESAU/RO, por dispensa em razão do valor, conforme especificações e quantidades informadas no Item 3.1 deste Termo de Referência, via Dispensa de Licitação com fulcro no artigo 75, inciso II, da Lei n.º 14.133, de 01 de abril de 2021.</t>
+  </si>
+  <si>
+    <t>0059.000090/2024-49</t>
+  </si>
+  <si>
+    <t>Aquisição de MÁQUINA UNITARIZADORA DE MEDICAMENTOS COM CORTADOR DE BLISTER E ALIMENTADORES AUTOMÁTICO DE AMPOLAS E BLÍSTER.</t>
+  </si>
+  <si>
+    <t>0054.000923/2023-31</t>
+  </si>
+  <si>
+    <t>Aquisição de formulários de aplicação testes e protocolos diagnósticos especializados, destinados ao rastreamento e diagnóstico de Transtorno do Espectro Autista (TEA) e outros transtornos neurotípicos.</t>
+  </si>
+  <si>
+    <t>0053.002625/2024-76</t>
+  </si>
+  <si>
+    <t>Aquisição de MATERIAIS ACESSÓRIOS PARA ESTRUTURAÇÃO DA NOVA UTI DE INFECTOLOGIA E CME - CENTRAL DE MATERIAL E ESTERILIZAÇÃO DO CEMETRON, com equipamentos médico hospitalares e materiais permanentes diversos, do Centro de Medicina Tropical do Estado de Rondônia - CEMETRON, no âmbito da Secretaria de Estado da Saúde de Rondônia (SESAU/RO), conforme Documento de Oficialização de Demanda nº 15/2024/CEMETRON-DG (0052488655)</t>
+  </si>
+  <si>
+    <t>0036.053999/2024-68</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE MATERIAIS GRÁFICOS, ITENS FRACASSADOS NA DISPENSA ELETRÔNICA 90459/2024, A FIM DE ATENDER O CONSELHO ESTADUAL DE SAÚDE - CES NA 356ª REUNIÃO ORDINÁRIA ITINERANTE QUE OCORRERÁ DIA 26 A 29 DE NOVEMBRO DE 2024, COM O ENCONTRO DA MESA DIRETORA DOS CONSELHOS MUNICIPAIS DE SAÚDE DE RONDÔNIA E ENCONTRO DAS SECRETÁRIAS EXECUTIVAS.</t>
+  </si>
+  <si>
+    <t>0063.001623/2024-41</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada para prestação de serviços de materiais gráficos, especialmente para a confecção de Receituários de SUBSTÂNCIAS TIPO (C) e Receituários de SUBSTÂNCIAS TIPO (B). Estes receituários devem ser confeccionados mediante autorização dos órgãos vinculados à AGEVISA, e necessitam ser impressos em gráficas devidamente autorizadas, seguindo parâmetros rigorosos e específicos conforme a legislação vigente, PORTARIA Nº 344, DE 12 DE MAIO DE 1998 do Ministério da Saúde.</t>
+  </si>
+  <si>
+    <t>0036.017264/2024-71</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual aquisição centralizada de MATERIAIS GRÁFICOS, visando atender as unidades de saúde vinculadas à SESAU/RO, pelo período de 1 (um) ano, prorrogável por igual período, das unidades vinculadas à SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0049.072425/2022-88</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais permanente GARROTE / TORNIQUETE PNEUMÁTICO com pressão ajustável de 0 a 600 mmHg, cronômetro integrado, bateria de suporte e bivolt automático, a fim de suprir as necessidades do setor de Seção de Órtese e Prótese OPME e Departamento de Ortopedia do Hospital de Base Dr. Ary Pinheiro, visando atender as necessidades do Hospital Regional de Extrema HRE, de forma contínua, por um período de 5 (cinco) anos.</t>
+  </si>
+  <si>
+    <t>0036.057439/2024-82</t>
+  </si>
+  <si>
+    <t>Aquisição de material permanente - AUTOCLAVE HORIZONTAL DE MESA, a fim de atender a unidade de saúde Centro de Diálise Vale do Jamari em Ariquemes</t>
+  </si>
+  <si>
+    <t>0036.059744/2024-17</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais permanentes para para o Hospital de Base Dr. Ary Pinheiro - HBAP</t>
+  </si>
+  <si>
+    <t>0036.286056/2021-77</t>
+  </si>
+  <si>
+    <t>Aquisição de Equipamentos Permanentes visando atender as necessidades Hospital de Base de Porto Velho - HBAP.</t>
+  </si>
+  <si>
+    <t>0036.019282/2024-97</t>
+  </si>
+  <si>
+    <t>Aquisição de Equipamentos e Material Permanente, sendo (monitor multiparâmetros neonatal, incubadora de transporte neonatal, banqueta para parto vertical e cama PPP (Pré-parto, Parto e Pós-parto), visando atender o Hospital de Base Dr. Ary Pinheiro - Estruturação da Rede Cegonha.</t>
+  </si>
+  <si>
+    <t>0049.003281/2023-09</t>
+  </si>
+  <si>
+    <t>Registro de preço para futura e eventual aquisição de equipamentos médico-hospitalares (Aparelhos de Holmium Laser, Unidades Eletrocirúrgicas, Sistemas de Videolaroscopia, e Mesas Cirúrgicas Urológicas) para cirurgias minimamente invasivas em pacientes urológicos do Estado de Rondônia através do Hospital de Base Dr. Ary Pinheiro – HBAP pelo período de 12 meses.</t>
+  </si>
+  <si>
+    <t>0053.002301/2024-38</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de EQUIPAMENTOS E MATERIAIS PERMANENTES MÉDICO-HOSPITALARES PARA UNIDADE DE TERAPIA INTENSIVA - UTI, para atendimento das unidades vinculadas à da Secretaria de Estado da Saúde - SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0036.103747/2022-25</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos e materiais hospitalares para fins de subsídio ao projeto definitivo de abertura da UTI neonatal do Hospital Regional de Cacoal - HRC</t>
+  </si>
+  <si>
+    <t>0036.025041/2024-87</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de permanentes para atender as necessidades do Núcleo de Clínica Materno Infantil e Centro Obstétrico do Hospital de Base Dr. Ary Pinheiro - HBAP vinculado a Secretária de Estado da Saúde - SESAU/RO.</t>
+  </si>
+  <si>
+    <t>0036.019918/2023-10</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de materiais permanentes (mobiliário), visando atender as unidades da Secretária do Estado da Saúde, por um período de 12 (doze) meses</t>
+  </si>
+  <si>
+    <t>0036.057440/2024-15</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais permanentes para atender as necessidades do Centro de Diálise de Ariquemes - CDA</t>
+  </si>
+  <si>
+    <t>0036.057437/2024-93</t>
+  </si>
+  <si>
+    <t>Aquisição de material permanente - REPROCESSADORAS DE CAPILARES, a fim de atender a unidade de saúde Centro de Diálise Vale do Jamari em Ariquemes</t>
+  </si>
+  <si>
+    <t>0063.001707/2024-84</t>
+  </si>
+  <si>
+    <t>Aquisição de papel fotográfico para uso contínuo do setor de oftalmologia para o aparelho de tomografia de coerência óptica - OCT</t>
+  </si>
+  <si>
+    <t>0036.048286/2023-00</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de produtos de refrigeração, sendo (condicionadores de ar, com instalação), bebedouros, frigobar, geladeiras e freezers, destinados ao atendimento das Unidades de Saúde e à Sede da Secretaria de Estado da Saúde de Rondônia, por um período de um ano.</t>
+  </si>
+  <si>
+    <t>0036.008280/2024-72</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE SELADORAS via intenção de Registro de Preços conforme Programação Anual de Saúde - PAS/2024 e Plano Anual de Contratação - PAC/2024 das unidades vinculadas à SESAU/RO</t>
+  </si>
+  <si>
+    <t>0036.045201/2024-12</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual aquisições de EQUIPAMENTOS MÉDICOS DE TECNOLOGIA ÓPTICA PARA CAPTAÇÃO E TRANSMISSÃO DE IMAGENS E ASSESSÓRIOS, a fim de atender as unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia.</t>
+  </si>
+  <si>
+    <t>0036.004910/2025-11</t>
+  </si>
+  <si>
+    <t>Aquisição de transdutor linear a transdutor convexo compatíveis com os aparelhos de Ultrassom Mindray M7 e Ultrassom FT422 Saevo para atender as necessidades do Hospital Regional de Cacoal - HRC</t>
+  </si>
+  <si>
+    <t>0049.003356/2024-24</t>
+  </si>
+  <si>
+    <t>Aquisição de TUBOS ENDOSCÓPICOS FLEXIVÉIS E EQUIPAMENTOS PERMANENTES por um período de 01 (um) Ano, que tem como finalidade atender a demanda do Hospital de Base Dr. Ary Pinheiro de Porto Velho - HBAP</t>
+  </si>
+  <si>
+    <t>0036.008667/2025-18</t>
+  </si>
+  <si>
+    <t>O presente documento informa a necessidade para a Contratação de Empresa para prestação do Serviço de Intérprete de Libras, Hospedagem, Locação de Auditório, Salas, Treliça, Transporte Urbano (Traslado), ambulância, fornecimento de Material Gráfico, Arranjos de Flores, Camisetas, Refeição, Coffee Break, Água Mineral e Café, com objetivo de atender os participantes da 3ª Conferência Estadual de Saúde do Trabalhador e da Trabalhadora de Rondônia, programada para acontecer no período de 28 e 30 de maio de 2025, em Porto Velho/RO, conforme Resolução N. 139/2024/SESAU-CES.</t>
+  </si>
+  <si>
+    <t>0036.008656/2025-20</t>
+  </si>
+  <si>
+    <t>0036.033171/2024-93</t>
+  </si>
+  <si>
+    <t>Aquisição de 10 (dez) caixas personalizadas com suporte interno contendo furos com diâmetro compatível e devidamente identificados para armazenar frascos-ampola e ampolas de medicamentos sujeitos a controle especial (anestésicos e sedativos) utilizados durante os procedimentos cirúrgicos.</t>
+  </si>
+  <si>
+    <t>0036.012973/2024-60</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de consumo destinados a suprir as necessidades da Farmácia Especializada do Estado de Rondônia e as Farmácias das Gerências Regionais de Saúde do Estado de Rondônia, com o objetivo de garantir a prestação plena de ações e serviços operacionais da rede pública estadual de saúde de Rondônia.</t>
+  </si>
+  <si>
+    <t>0036.028937/2024-18</t>
+  </si>
+  <si>
+    <t>Aquisição de Materiais Gráficos por dispensa de licitação em razão do valor, visando atender a Comissão Intergestora Bipartite - CIB, o Conselho Estadual de Saúde - CES na promoção 2ª Conferência Estadual de Gestão do Trabalho e Educação em Saúde, e, a Gerência de Coordenação Estadual de Transplantes - GCET/SESAU em sua campanha de doação de órgãos 2024.</t>
+  </si>
+  <si>
+    <t>0046.000210/2025-38</t>
+  </si>
+  <si>
+    <t>Aquisição de baterias para nobreak, com objetivo de atender ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO</t>
+  </si>
+  <si>
+    <t>0036.006806/2025-61</t>
+  </si>
+  <si>
+    <t>Aquisição de Material Gráfico para atender a solenidade de premiação do prêmio: Equipe Rosa 2024</t>
+  </si>
+  <si>
+    <t>0036.027261/2024-45</t>
+  </si>
+  <si>
+    <t>Registro de preços para aquisição centralizada de placas de identificação e sinalização hospitalar e outros, conforme normas e regulamentos de segurança, com objetivo de atender as demandas da SESAU-SESMT</t>
+  </si>
+  <si>
+    <t>0063.000305/2025-43</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE EQUIPAMENTO E MATERIAL PERMANENTE PARA ATENÇÃO BÁSICA EM SAÚDE BUCAL, em prol de atender as necessidades do Centro de Especialidades Odontológicas - CEO/POC</t>
+  </si>
+  <si>
+    <t>0036.009923/2025-86</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA FORNECER MATERIAL GRÁFICO E DE CONSUMO, com objetivo de atender as Comissões Intersetoriais de Educação Permanente, Saúde Mental e Saúde da Mulher, na execução de suas atividades através das oficinas e cursos de capacitação aos conselheiros estaduais e municipais de saúde e demais participantes, cujas as ações estão programadas para ocorrer ao longo de todo o ano de 2025</t>
+  </si>
+  <si>
+    <t>0036.009331/2025-64</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA NO FORNECIMENTO DE MATERIAL GRÁFICO, com objetivo de atender aos participantes do 1º ENCONTRO ESTADUAL DE SAÚDE E MEIO AMBIENTE, programado para os dias 25 e 26 de setembro de 2025, em Porto Velho/RO, conforme Resolução N. 169/2025/SESAU-CES (ID 0057648405).</t>
+  </si>
+  <si>
+    <t>0036.011890/2025-34</t>
+  </si>
+  <si>
+    <t>Aquisição de material de consumo distribuição gratuita (folder, agenda, lanterna e camisetas) abertura de processo administrativo para aquisição de material de consumo, com objetivo de distribuição para as CIHDOTT'S de Porto Velho, Organização de Procura de Órgãos (OPO), e público em geral, no sentido de promover campanha alusiva ao Dia Nacional do Doador de Órgãos e Tecidos, bem como a conscientização sobre a importância de ser doador de órgãos nas campanhas diárias realizadas por esta Gerência de Coordenação Estadual de Transplantes - GCET/SESAU</t>
+  </si>
+  <si>
+    <t>0036.039896/2024-95</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada no fornecimento e instalação de placa luminosa de identificação no Prédio, com objetivo de atender as necessidades desta Gerência da Coordenação Estadual de Transplantes/SESAU-GCET.</t>
+  </si>
+  <si>
+    <t>0036.095236/2022-22</t>
+  </si>
+  <si>
+    <t>Registro de preços para aquisição de ventiladores pulmonar</t>
+  </si>
+  <si>
+    <t>0036.015170/2025-48</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais (acabamento, básico, cabeamento estruturado, elétricos, ferramentas, hidráulicos e esgoto) necessários para realização de Manutenção Predial das Unidades Hospitalares/SESAU-RO.</t>
+  </si>
+  <si>
+    <t>0049.011596/2023-11</t>
+  </si>
+  <si>
+    <t>Aquisição de kits de acessórios pediátricos para os monitores multiparâmetros instalados na UTI NEO do HBAP, em caráter emergencial, para atender a UTI NEO do Hospital de Base Dr. Ary Pinheiro (HBAP) face a DM nº 02406/22/TCE-RO de 09/08/2023.</t>
+  </si>
+  <si>
+    <t>0036.016410/2025-21</t>
+  </si>
+  <si>
+    <t>Aquisição de Camisetas, vinculado ao processo 0036.011890/2025-34</t>
+  </si>
+  <si>
+    <t>0036.016413/2025-65</t>
+  </si>
+  <si>
+    <t>Aquisição de lanternas, vinculado ao processo 0036.011890/2025-34</t>
+  </si>
+  <si>
+    <t>0036.059400/2024-08</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos de uso laboratorial necessários à realização de procedimentos Analíticos (exames laboratoriais), para atendimento ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO, cujo recurso é proveniente e específico do Programa: NOVO PAC - ESTRUTURAÇÃO DA VIGILÂNCIA LABORATORIAL EM SAÚDE E AMBIENTES E RESPOSTA AS EMERGÊNCIAS EM SAÚDE</t>
+  </si>
+  <si>
+    <t>0036.013084/2025-09</t>
+  </si>
+  <si>
+    <t>Aquisição de Cabo oxímetro infantil compatível com o Oxímetro de pulso da marca NONIN - 7500FO em prol de atender as necessidades do Hospital Regional de Cacoal - HRC</t>
+  </si>
+  <si>
+    <t>0036.017426/2025-51</t>
+  </si>
+  <si>
+    <t>Aquisição de Material de consumo CARGA DE GÁS GLP - P13: Gás Liquefeito de Petróleo - GLP acondicionado em botija de 13 Kg, para atender as demandas das unidades de Saúde Estaduais da Secretaria de Estado da Saúde - SESAU por um período de 06 (seis) meses</t>
+  </si>
+  <si>
+    <t>0036.016136/2025-91</t>
+  </si>
+  <si>
+    <t>Aquisição PASTA COM BOLSO - Impressão offset, 4 x 0 cores, papel tríplex fosco 350g, formato 23 x 32 cm (fechado) e 46x32cm (aberta). Acabamento em laminação bopp fosca, verniz uv na parte externa, com bolso interno sem impressão. Com logomarca do evento, do Governo do Estado de Rondônia, Secretaria de Estado da Saúde - SESAU e Conselho Estadual de Saúde. (arte a ser fornecida pela contratante).</t>
+  </si>
+  <si>
+    <t>0063.000527/2025-66</t>
+  </si>
+  <si>
+    <t>Aquisição de aparelho(s) de Monitoramento Ambulatorial da Pressão Arterial (MAPA) para atender a Policlínica Oswaldo Cruz-POC</t>
+  </si>
+  <si>
+    <t>0036.018495/2025-82</t>
+  </si>
+  <si>
+    <t>Aquisição de gêneros alimentícios (açúcar e café) para suprir as necessidades das unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia (SESAU-RO)</t>
+  </si>
+  <si>
+    <t>0063.000444/2025-77</t>
+  </si>
+  <si>
+    <t>Aquisição de Centrais de AR para atender ao CAPS II MADEIRA MAMORÉ</t>
+  </si>
+  <si>
+    <t>0036.049005/2024-17</t>
+  </si>
+  <si>
+    <t>Aquisição de carrinho de sedação compatível com ressonância magnética composto por Ventilador Pulmonar de Transporte RM, Bomba de Contraste para Ambiente de Ressonância Magnética, Aparelho de Anestesia para ambiente de Ressonância Magnética de 1.5T e 3T indicado para pacientes neonato, pediatrico e adultos e Monitor Multiparâmetro para ambiente de Ressonância Magnética de 1.5T e 3T em prol de atender as necessidades do setor de Diagnóstico do Hospital Regional de Cacoal (HRC)</t>
+  </si>
+  <si>
+    <t>0036.040954/2024-23</t>
+  </si>
+  <si>
+    <t>Aquisição com instalação de aparelho de RX – Panorâmico Digital, de alta resolução e baixa dose, cujo recurso é proveniente e específico do Repasse FNS, parcela única em 2024, OB008590, bloco - Estruturação da Rede de Serviços Públicos de Saúde (INVESTIMENTO) - ESTRUTURAÇÃO DA ATENÇÃO À SAÚDE BUCAL (ATENÇÃO PRIMÁRIA). Proposta nº 00733062000123004. Portaria nº 2418. Preconizados pelo ministério da Saúde.</t>
+  </si>
+  <si>
+    <t>0036.051327/2024-18</t>
+  </si>
+  <si>
+    <t>CEAF 1B / 2025</t>
+  </si>
+  <si>
+    <t>0036.016942/2024-88</t>
+  </si>
+  <si>
+    <t>Construção de um Espaço de convivência - POC</t>
+  </si>
+  <si>
+    <t>0046.000425/2025-59</t>
+  </si>
+  <si>
+    <t>Aquisição de condicionadores de ar (Central de Ar Condicionado), destinados ao atendimento das unidades de saúde (LABORATÓRIO CENTRAL DE SAÚDE PÚBLICA - LACEN/RO)</t>
+  </si>
+  <si>
+    <t>0050.007939/2025-76</t>
+  </si>
+  <si>
+    <t>JPII- Aquisição de Vídeo Laringoscópio Portátil.</t>
+  </si>
+  <si>
+    <t>0036.032294/2025-98</t>
+  </si>
+  <si>
+    <t>Aquisição de Materiais de Expediente - CLAP</t>
+  </si>
+  <si>
+    <t>0036.031800/2025-21</t>
+  </si>
+  <si>
+    <t>Aquisição do equipamento de raios-x fixo</t>
+  </si>
+  <si>
+    <t>0036.046139/2024-78</t>
+  </si>
+  <si>
+    <t>Prestação do serviço de confecção de chaves, carimbos e demais serviços tais como: conserto de fechaduras, extração de chave quebrada, troca de segredo de fechadura - POC</t>
+  </si>
+  <si>
+    <t>0050.006958/2025-85</t>
+  </si>
+  <si>
+    <t>manutenção preventiva e corretiva continuada de um aparelho de tomografia computadorizada da marca CANON, modelo AQUILON LIGHTNING, para atender as demandas do Hospital e Pronto Socorro João Paulo II. (MÃO DE OBRA + PEÇAS + TUBO DE RAIOS-X + DETECTOR)</t>
+  </si>
+  <si>
+    <t>0036.048955/2024-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Considerando que aportou nesta Gerência de Compras-GECOMP solicitação quanto a viabilidade da contratação da Empresa Especializada Águas de Ariquemes para o serviço de fornecimento de água e de coleta e tratamento de esgotamento sanitário - CDA</t>
+  </si>
+  <si>
+    <t>0036.002455/2025-19</t>
+  </si>
+  <si>
+    <t>prestação de serviços de manutenção preventiva, corretiva, preditiva e calibração, com reposição integral de peças e accessórios, de equipamentos de tratamento hemodialítico,  unidades de saúde HBAP, HPSJPII, CEMETRON,  AMI, HRC, HEURO, CDA.</t>
+  </si>
+  <si>
+    <t>0036.037694/2025-90</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de gerenciamento, operacionalização e execução das ações assistenciais para o pleno funcionamento do Hospital Regional Adamastor Teixeira de Oliveira. +</t>
+  </si>
+  <si>
+    <t>0049.004912/2025-61</t>
+  </si>
+  <si>
+    <t>Otorrinolaringologia no Hospital de Base Dr. Ary PinheiroHB</t>
+  </si>
+  <si>
+    <t>0036.037472/2025-77</t>
+  </si>
+  <si>
+    <t>Locação de Imóvel (galpão/prédio) no município de Ji-Paraná para atender as necessidades da I Gerência Regional</t>
+  </si>
+  <si>
+    <t>0049.009611/2025-23</t>
+  </si>
+  <si>
+    <t>prestação de Serviços de manutenção preventiva e corretiva dos equipamentos médico-hospitalares da marca Dornier com fornecimento de peças e serviços para atender Hospital de Base</t>
+  </si>
+  <si>
+    <t>0036.029331/2025-81</t>
+  </si>
+  <si>
+    <t>prestação coleta interna e externa, transporte, tratamento (incineração ou autoclavagem e incineração e destinação final dos resíduos de serviços de saúde RSS (grupos A,B,E e eventualmente C), de forma contínua, para atender o HBAP, HICD, CEMETRON, POC e HRB</t>
+  </si>
+  <si>
+    <t>0036.036313/2025-55</t>
+  </si>
+  <si>
+    <t>serviços contínuos de manutenção preventiva (incluindo rotinas de inspeção, aferição e calibração rastreada) e corretiva, com fornecimento de peças e materiais, para os equipamentos laboratoriais do (LACEN/LAFRON)</t>
+  </si>
+  <si>
+    <t>0036.016266/2025-23</t>
+  </si>
+  <si>
+    <t>Prestação de Serviços de Manutenção Preventiva e Corretiva em Sistema de Mamografia, para atendimento a Unidade Assistência de Alta Complexidade em Oncologia - UNACON - HBAP</t>
+  </si>
+  <si>
+    <t>0036.033091/2025-19</t>
+  </si>
+  <si>
+    <t>Manutenção Preventiva e Corretiva com Reposição de Peças em Estação de Tratamento de Esgoto - ETE, bem como Limpeza, Desobstrução do sistema de Esgotos (tubulação, caixa de inspeção e Caixas de Gordura), visando atender ao Hospital e Pronto Socorro João Paulo II - HEPSJP/II</t>
+  </si>
+  <si>
+    <t>0036.033994/2025-08</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de saúde com equipe multiprofissional e médica para atuação em UTI Neonatal nas áreas de Enfermagem, Fisioterapia, Psicologia, Assistência Social, Nutrição, Administrativo, Medicina Pediátrica e Neonatologia, para atendimento das necessidades do Hospital Regional de Cacoal e inicialização dos serviços de Neonatologia</t>
+  </si>
+  <si>
+    <t>0036.032961/2025-32</t>
+  </si>
+  <si>
+    <t>prestação de serviços funerários, serviços administrativos e serviços de translado de esquife com assistência 24 horas. Esses serviços são destinados ao atendimento de usuários do Sistema Único de Saúde (SUS) em Tratamento Fora de Domicílio (TFD)</t>
+  </si>
+  <si>
+    <t>0036.042874/2025-93</t>
+  </si>
+  <si>
+    <t>0036.034433/2025-18</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de coleta externa, transporte e destinação final dos resíduos sólidos (grupo D) - HRRO; JPII; AMI; CEMETRON; CEPEM; CERO; CAGF; CGPMNADM; HRE; HBAP;LACEN; LEPAC; POC; HICD.</t>
+  </si>
+  <si>
+    <t>0046.000254/2025-68</t>
+  </si>
+  <si>
+    <t>fornecimento continuado de insumos laboratoriais específicos para exames de microbiologia clínica automatizada, incluindo garrafas de hemocultura para automação, identificação de bactérias e fungos, testes de sensibilidade a antibióticos e antifugigrama todos automatizados, com fornecimento em regime de "COMODATO", de todo sistema/solução de automação laboratorial, incluindo todos os insumos laboratoriais, como: equipamentos e acessórios, reagentes, materiais de consumo, meios de cultura, controles/padrões ou similares, quando couber; necessários a todas as etapas da realização dos exames/testes propostos no certame, para atender ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO, LAFRON/RO e Laboratório de Microbiologia do Hospital de Base Ary Pinheiro, com possibilidade de expansão à Macroregião II, pertencente ao quadro da Secretaria de Estado da Saúde – SESAU/RO</t>
+  </si>
+  <si>
+    <t>0036.015381/2025-81</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Prestadora de Serviços de Refeição, Coffe Break, e fornecimento de Água e Café, com objetivo de atender aos participantes do 368ª (trecentésima sexagésima oitava) Reunião Ordinária (itinerante) e XV Plenária de Conselhos de Saúde do Estado de Rondônia, programadas para acontecer entre os dias 03 e 05 de dezembro de 2025, no município de Cacoal/RO</t>
+  </si>
+  <si>
+    <t>0036.059859/2024-01</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços médicos complementares especializados na área de cardiologia e neurologia com especialização em hemodinâmica, de forma contínua, para atender as demandas dos usuários da saúde pública nas dependências do Hospital de Base Dr. Ary Pinheiro - HBAP</t>
+  </si>
+  <si>
+    <t>0050.001971/2025-48</t>
+  </si>
+  <si>
+    <t>Aquisição Emergencial do Disjuntor de Média Tensão 630 A P.V.O. para suprir a necessidade de manutenção do Grupo Gerador no âmbito do Hospital Estadual e Pronto Socorro João Paulo II - HEPSJPII</t>
+  </si>
+  <si>
+    <t>0036.031964/2025-59</t>
+  </si>
+  <si>
+    <t>Registro de Preços para aquisição eventual de berços aquecidos neonatais para o Hospital de Base Dr. Ary Pinheiro.</t>
+  </si>
+  <si>
+    <t>0036.029885/2025-88</t>
+  </si>
+  <si>
+    <t>Fornecimento de SOLUÇÃO DE IMPRESSÃO CORPORATIVA, DE CARÁTER LOCAL E VIA REDE TCP/IP, compreendendo a cessão de direito de uso de equipamentos (copiadora/impressora/digitalizadora) com tecnologia digital e instalação, incluindo manutenção preventiva e corretiva com fornecimento e/ou substituição de peças, componentes, software de gerenciamento e todos os materiais e insumos utilizados na operação, incluindo papel gramatura 75g/m² (A4)</t>
+  </si>
+  <si>
+    <t>0036.041163/2025-00</t>
+  </si>
+  <si>
+    <t>HB - Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Básico Tipo B e de Suporte Avançado Tipo D (UTI Móvel) e Mão-de-obra especializada (Motorista/Socorrista e Técnico de Enfermagem)</t>
+  </si>
+  <si>
+    <t>0036.033084/2025-17</t>
+  </si>
+  <si>
+    <t>Manutenção preventiva e corretiva com reposição de peças da estação de tratamento de esgoto (por lodos ativados) HICD, HB, e POC</t>
+  </si>
+  <si>
+    <t>0046.000640/2024-79</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais e insumos para atender ao laboratório de cultura, identificação e teste de sensibilidade específicos de tuberculose(M. tuberculosis), objetivando garantir que a unidade tenha os recursos necessários para realizar a complementação diagnóstica de forma mais precisa e rápida da doença, aprimorar a capacidade de detecção precoce, e apoiar o tratamento eficaz dos paciente, promovendo o monitoramento de casos, e controle da transmissão da tuberculose - LACEN</t>
+  </si>
+  <si>
+    <t>0036.039729/2025-25</t>
+  </si>
+  <si>
+    <t>Aquisição de uma placa de identificação, conforme modelo do anexo 0063480293, para ser colocada em frente ao prédio em que esta se encontra, visando o melhor reconhecimento ao público quanto a localização desta VGRS, facilitando com que os pacientes e público geral encontrem o prédio com maior facilidade. - GRS5</t>
+  </si>
+  <si>
+    <t>0036.041455/2025-34</t>
+  </si>
+  <si>
+    <t>prestação Serviços de vigilância/segurança patrimonial, de forma contínua, para atender as unidades hospitalares Hospital Regional de Extrema e Hospital Regional de Buritis</t>
+  </si>
+  <si>
+    <t>0050.006512/2024-70</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em fabricação, fornecimento e instalação de toldos com fornecimento de peças e materiais necessários, JPII</t>
+  </si>
+  <si>
+    <t>0045.000097/2025-09</t>
+  </si>
+  <si>
+    <t>Aquisição de produtos de refrigeração (Condicionadores de ar - com instalação, bebedouros e geladeiras) - CEPEM</t>
+  </si>
+  <si>
+    <t>0036.031011/2025-91</t>
+  </si>
+  <si>
+    <t>prestação de serviços médicos complementares para a realização de Cirurgia Geral, Ginecológica e Obstétrica e pediatria de forma contínua, para atender as demandas dos usuários do SUS nas dependências do - HRSFG</t>
+  </si>
+  <si>
+    <t>0036.031476/2025-41</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de vigilância/segurança patrimonial, para atender as unidades administrativas vinculadas à Secretaria de Estado da Saúde, referente aos Lotes I, II, III e VI,</t>
+  </si>
+  <si>
+    <t>0036.044045/2025-45</t>
+  </si>
+  <si>
+    <t>serviços de análises clínicas inseridos nos subgrupos de diagnóstico em TRIAGEM NEONATAL, inseridos na tabela de procedimentos do Sistema Único de Saúde (SIGTAP)</t>
+  </si>
+  <si>
+    <t>0049.011732/2025-35</t>
+  </si>
+  <si>
+    <t>aquisição de equipamento médico hospitalar - HB</t>
+  </si>
+  <si>
+    <t>0036.039982/2025-89</t>
+  </si>
+  <si>
+    <t>contratação de empresa especializada em serviços de Operação Logística de Armazenamento e Distribuição, incluindo implantação e operação de Centro de Distribuição Logística Centralizado,</t>
+  </si>
+  <si>
+    <t>0046.000590/2025-19</t>
+  </si>
+  <si>
+    <t>Aquisição de material laboratorial (Vidraria de uso laboratorial exemplo: Becker, Proveta, Bureta, Tubos de ensaio, Funil de vidro de Wildman, dentre outros) para realização de exames de média e alta complexidade no intuito de atender as necessidades de setor específico do Laboratório Central de Saúde Pública - LACEN/RO</t>
+  </si>
+  <si>
+    <t>0053.003074/2025-49</t>
+  </si>
+  <si>
+    <t>Provimento de equipamentos médico-hospitalares para estruturação da nova UTI com 10 leitos de infectologia - Cemetron</t>
+  </si>
+  <si>
+    <t>0053.003086/2025-73</t>
+  </si>
+  <si>
+    <t>equipamentos médico-hospitalares - cemetron</t>
+  </si>
+  <si>
+    <t>0036.026538/2025-01</t>
+  </si>
+  <si>
+    <t>prestação de serviços médicos na área de Hematologia Pediátrica, para atender pacientes internados no HICD</t>
+  </si>
+  <si>
+    <t>0046.000141/2025-62</t>
+  </si>
+  <si>
+    <t>Serviço contínuo de manutenção preventiva, corretiva, calibração, testes de segurança elétrica, de equipamentos laboratoriais de alta complexidade - LACEN</t>
+  </si>
+  <si>
+    <t>0046.000203/2025-36</t>
+  </si>
+  <si>
+    <t>Serviço contínuo de manutenção preventiva, corretiva, calibração, testes de segurança elétrica, de equipamentos laboratoriais de alta complexidade, já existentes e de uso exclusivo do- LACEN/RO e LAFRON, os quais se encontram no setor de Biologia Molecular que são de alta tecnologia (Equipamento: Extrator automático de RNA/DNA - Modelo Extracta 32 – Fabricante: LOCCUS)</t>
+  </si>
+  <si>
+    <t>0036.039613/2025-96</t>
+  </si>
+  <si>
+    <t>aquisição de dietas enterais, suplementos e módulos para uso adulto</t>
+  </si>
+  <si>
+    <t>0036.039948/2025-12</t>
+  </si>
+  <si>
+    <t>Aquisição de formulários de aplicação e protocolos diagnósticos especializados destinados ao rastreamento e diagnóstico de tratamento do espectro autista(TEA) e outros transtornos neurotípicos - CERO</t>
+  </si>
+  <si>
+    <t>0036.032794/2025-20</t>
+  </si>
+  <si>
+    <t>Serviços de saúde na área de Oncologia, com apoio ambulatorial (terapêutico) e hospitalar no grupo de procedimentos clínicos, sub-grupo tratamento em oncologia e nas formas de organizações de Radioterapia, Quimioterapia paliativa adulto</t>
+  </si>
+  <si>
+    <t>0036.028648/2025-08</t>
+  </si>
+  <si>
+    <t>GCEREST - Material gráfico</t>
+  </si>
+  <si>
+    <t>0035.001566/2025-18</t>
+  </si>
+  <si>
+    <t>Aquisição de Material Permanente-(kit odontológico adaptado para atendimento de pacientes com Transtorno do Espectro Autista - TEA)I, destinados ao funcionamento do Centro de Especialidades Odontológicas – CEO</t>
+  </si>
+  <si>
+    <t>0036.042822/2025-17</t>
+  </si>
+  <si>
+    <t>Aquisição de formulários padronizados de receituários especiais. Estes receituários devem ser confeccionados mediante autorização dos órgãos vinculados à AGEVISA , e necessitam ser impressos em gráficas devidamente autorizadas, seguindo parâmetros rigorosos e específicos conforme a legislação vigente, PORTARIA Nº 344, DE 12 DE MAIO DE 1998 do Ministério da Saúde.</t>
+  </si>
+  <si>
+    <t>0036.037524/2025-13</t>
+  </si>
+  <si>
+    <t>fornecimento de materiais gráficos e demais itens de comunicação visual, destinados a atender às demandas das ações e campanhas alusivas ao Outubro Rosa 2025</t>
+  </si>
+  <si>
+    <t>0050.009804/2025-45</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de locação de equipamentos hospitalares, incluindo fornecimento de insumos, reagentes, acessórios, software e suporte técnico, pelo período de 1 (um) ano, podendo ser prorrogando conforme previsto no Art. 107 da Lei 14.133/21 João Paulo II.</t>
+  </si>
+  <si>
+    <t>0036.045300/2025-77</t>
+  </si>
+  <si>
+    <t>alimentação hospitalar pronta, destinados ao Hospital Regional São Francisco do Guaporé HRSFG</t>
+  </si>
+  <si>
+    <t>0036.027550/2025-25</t>
+  </si>
+  <si>
+    <t>Alimentação Hospitalar HRE, HRB, HRSF</t>
+  </si>
+  <si>
+    <t>0036.036824/2025-77</t>
+  </si>
+  <si>
+    <t>prestação de serviços médicos complementares especializados na área de Cirurgia Geral, Ginecologia e Obstetrícia e Pediatria, - HRSF</t>
+  </si>
+  <si>
+    <t>materiais gráficos e demais itens de comunicação visual, destinados a atender às demandas das ações e campanhas alusivas ao Outubro Rosa 2025</t>
+  </si>
+  <si>
+    <t>0036.034801/2025-28</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de manutenção por chamado, com fornecimento de peças, de forma contínua, aos equipamentos de carrinho de carga horizontal, carrinho de carga vertical, geladeiras e bebedouros</t>
+  </si>
+  <si>
+    <t>0036.036934/2025-39</t>
+  </si>
+  <si>
+    <t>prestação de serviços de agenciamento de transporte terrestre, abrangendo reserva, emissão e entrega de bilhetes interestaduais, em linhas regulares, para pacientes e acompanhantes autorizados pela CTFD</t>
   </si>
 </sst>
 </file>
@@ -389,8 +2038,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,6 +2058,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -725,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -745,197 +2401,197 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -943,50 +2599,65 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>143</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>147</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>149</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
@@ -994,48 +2665,54 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>155</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
@@ -1043,78 +2720,87 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>165</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>173</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
@@ -1122,10 +2808,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
@@ -1133,29 +2819,32 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>183</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -1163,81 +2852,3144 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>191</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>193</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>197</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>200</v>
+      </c>
+      <c r="B50" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>202</v>
+      </c>
+      <c r="B51" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" t="s">
+        <v>211</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>212</v>
+      </c>
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>216</v>
+      </c>
+      <c r="B58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>218</v>
+      </c>
+      <c r="B59" t="s">
+        <v>219</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>220</v>
+      </c>
+      <c r="B60" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>222</v>
+      </c>
+      <c r="B61" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" t="s">
+        <v>225</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>226</v>
+      </c>
+      <c r="B63" t="s">
+        <v>227</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>228</v>
+      </c>
+      <c r="B64" t="s">
+        <v>229</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>232</v>
+      </c>
+      <c r="B66" t="s">
+        <v>233</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>235</v>
+      </c>
+      <c r="B68" t="s">
+        <v>236</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>237</v>
+      </c>
+      <c r="B69" t="s">
+        <v>238</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>239</v>
+      </c>
+      <c r="B70" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" t="s">
+        <v>243</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" t="s">
+        <v>249</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>250</v>
+      </c>
+      <c r="B76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>254</v>
+      </c>
+      <c r="B78" t="s">
+        <v>255</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" t="s">
+        <v>257</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>258</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>260</v>
+      </c>
+      <c r="B81" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>262</v>
+      </c>
+      <c r="B82" t="s">
+        <v>263</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>264</v>
+      </c>
+      <c r="B83" t="s">
+        <v>265</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+      <c r="B84" t="s">
+        <v>267</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>268</v>
+      </c>
+      <c r="B85" t="s">
+        <v>269</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>270</v>
+      </c>
+      <c r="B86" t="s">
+        <v>271</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>274</v>
+      </c>
+      <c r="B88" t="s">
+        <v>275</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>277</v>
+      </c>
+      <c r="B90" t="s">
+        <v>278</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>279</v>
+      </c>
+      <c r="B91" t="s">
+        <v>280</v>
+      </c>
+      <c r="C91" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>281</v>
+      </c>
+      <c r="B92" t="s">
+        <v>282</v>
+      </c>
+      <c r="C92" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>283</v>
+      </c>
+      <c r="B93" t="s">
+        <v>284</v>
+      </c>
+      <c r="C93" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>285</v>
+      </c>
+      <c r="B94" t="s">
+        <v>286</v>
+      </c>
+      <c r="C94" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>287</v>
+      </c>
+      <c r="B95" t="s">
+        <v>288</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>289</v>
+      </c>
+      <c r="B96" t="s">
+        <v>290</v>
+      </c>
+      <c r="C96" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>291</v>
+      </c>
+      <c r="B97" t="s">
+        <v>292</v>
+      </c>
+      <c r="C97" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>293</v>
+      </c>
+      <c r="B98" t="s">
+        <v>294</v>
+      </c>
+      <c r="C98" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>295</v>
+      </c>
+      <c r="B99" t="s">
+        <v>296</v>
+      </c>
+      <c r="C99" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" t="s">
+        <v>298</v>
+      </c>
+      <c r="C100" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>299</v>
+      </c>
+      <c r="B101" t="s">
+        <v>300</v>
+      </c>
+      <c r="C101" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>303</v>
+      </c>
+      <c r="B103" t="s">
+        <v>304</v>
+      </c>
+      <c r="C103" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>305</v>
+      </c>
+      <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>307</v>
+      </c>
+      <c r="B105" t="s">
+        <v>308</v>
+      </c>
+      <c r="C105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>309</v>
+      </c>
+      <c r="B106" t="s">
+        <v>310</v>
+      </c>
+      <c r="C106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>311</v>
+      </c>
+      <c r="B107" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>313</v>
+      </c>
+      <c r="B108" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>146</v>
+      </c>
+      <c r="B110" t="s">
+        <v>147</v>
+      </c>
+      <c r="C110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>148</v>
+      </c>
+      <c r="B111" t="s">
+        <v>149</v>
+      </c>
+      <c r="C111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>170</v>
+      </c>
+      <c r="B112" t="s">
+        <v>171</v>
+      </c>
+      <c r="C112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>180</v>
+      </c>
+      <c r="B113" t="s">
+        <v>181</v>
+      </c>
+      <c r="C113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>192</v>
+      </c>
+      <c r="B114" t="s">
+        <v>193</v>
+      </c>
+      <c r="C114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>220</v>
+      </c>
+      <c r="B115" t="s">
+        <v>221</v>
+      </c>
+      <c r="C115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>226</v>
+      </c>
+      <c r="B116" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>228</v>
+      </c>
+      <c r="B117" t="s">
+        <v>229</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>158</v>
+      </c>
+      <c r="B118" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" t="s">
+        <v>247</v>
+      </c>
+      <c r="C119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>299</v>
+      </c>
+      <c r="B120" t="s">
+        <v>315</v>
+      </c>
+      <c r="C120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>168</v>
+      </c>
+      <c r="B121" t="s">
+        <v>169</v>
+      </c>
+      <c r="C121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>316</v>
+      </c>
+      <c r="B122" t="s">
+        <v>317</v>
+      </c>
+      <c r="C122" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>318</v>
+      </c>
+      <c r="B123" t="s">
+        <v>319</v>
+      </c>
+      <c r="C123" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>320</v>
+      </c>
+      <c r="B124" t="s">
+        <v>321</v>
+      </c>
+      <c r="C124" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>322</v>
+      </c>
+      <c r="B125" t="s">
+        <v>323</v>
+      </c>
+      <c r="C125" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>324</v>
+      </c>
+      <c r="B126" t="s">
+        <v>325</v>
+      </c>
+      <c r="C126" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>326</v>
+      </c>
+      <c r="B127" t="s">
+        <v>327</v>
+      </c>
+      <c r="C127" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>328</v>
+      </c>
+      <c r="B128" t="s">
+        <v>329</v>
+      </c>
+      <c r="C128" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>330</v>
+      </c>
+      <c r="B129" t="s">
+        <v>331</v>
+      </c>
+      <c r="C129" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>332</v>
+      </c>
+      <c r="B130" t="s">
+        <v>333</v>
+      </c>
+      <c r="C130" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>334</v>
+      </c>
+      <c r="B131" t="s">
+        <v>335</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>336</v>
+      </c>
+      <c r="B132" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>338</v>
+      </c>
+      <c r="B133" t="s">
+        <v>339</v>
+      </c>
+      <c r="C133" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>340</v>
+      </c>
+      <c r="B134" t="s">
+        <v>341</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>342</v>
+      </c>
+      <c r="B135" t="s">
+        <v>343</v>
+      </c>
+      <c r="C135" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>344</v>
+      </c>
+      <c r="B136" t="s">
+        <v>345</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>346</v>
+      </c>
+      <c r="B137" t="s">
+        <v>347</v>
+      </c>
+      <c r="C137" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>348</v>
+      </c>
+      <c r="B138" t="s">
+        <v>349</v>
+      </c>
+      <c r="C138" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" t="s">
+        <v>350</v>
+      </c>
+      <c r="C139" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>351</v>
+      </c>
+      <c r="B140" t="s">
+        <v>352</v>
+      </c>
+      <c r="C140" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>353</v>
+      </c>
+      <c r="B141" t="s">
+        <v>331</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>354</v>
+      </c>
+      <c r="B142" t="s">
+        <v>355</v>
+      </c>
+      <c r="C142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>356</v>
+      </c>
+      <c r="B143" t="s">
+        <v>357</v>
+      </c>
+      <c r="C143" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>359</v>
+      </c>
+      <c r="B144" t="s">
+        <v>360</v>
+      </c>
+      <c r="C144" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>361</v>
+      </c>
+      <c r="B145" t="s">
+        <v>362</v>
+      </c>
+      <c r="C145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>363</v>
+      </c>
+      <c r="B146" t="s">
+        <v>364</v>
+      </c>
+      <c r="C146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>365</v>
+      </c>
+      <c r="B147" t="s">
+        <v>366</v>
+      </c>
+      <c r="C147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>367</v>
+      </c>
+      <c r="B148" t="s">
+        <v>368</v>
+      </c>
+      <c r="C148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>369</v>
+      </c>
+      <c r="B149" t="s">
+        <v>370</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>371</v>
+      </c>
+      <c r="B150" t="s">
+        <v>372</v>
+      </c>
+      <c r="C150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>373</v>
+      </c>
+      <c r="B151" t="s">
+        <v>374</v>
+      </c>
+      <c r="C151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>375</v>
+      </c>
+      <c r="B152" t="s">
+        <v>376</v>
+      </c>
+      <c r="C152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>377</v>
+      </c>
+      <c r="B153" t="s">
+        <v>378</v>
+      </c>
+      <c r="C153" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>379</v>
+      </c>
+      <c r="B154" t="s">
+        <v>380</v>
+      </c>
+      <c r="C154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>381</v>
+      </c>
+      <c r="B155" t="s">
+        <v>382</v>
+      </c>
+      <c r="C155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>383</v>
+      </c>
+      <c r="B156" t="s">
+        <v>384</v>
+      </c>
+      <c r="C156" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>385</v>
+      </c>
+      <c r="B157" t="s">
+        <v>386</v>
+      </c>
+      <c r="C157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>387</v>
+      </c>
+      <c r="B158" t="s">
+        <v>388</v>
+      </c>
+      <c r="C158" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>389</v>
+      </c>
+      <c r="B159" t="s">
+        <v>390</v>
+      </c>
+      <c r="C159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>391</v>
+      </c>
+      <c r="B160" t="s">
+        <v>392</v>
+      </c>
+      <c r="C160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>393</v>
+      </c>
+      <c r="B161" t="s">
+        <v>394</v>
+      </c>
+      <c r="C161" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>395</v>
+      </c>
+      <c r="B162" t="s">
+        <v>396</v>
+      </c>
+      <c r="C162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>397</v>
+      </c>
+      <c r="B163" t="s">
+        <v>398</v>
+      </c>
+      <c r="C163" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>399</v>
+      </c>
+      <c r="B164" t="s">
+        <v>400</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>401</v>
+      </c>
+      <c r="B165" t="s">
+        <v>402</v>
+      </c>
+      <c r="C165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>403</v>
+      </c>
+      <c r="B166" t="s">
+        <v>404</v>
+      </c>
+      <c r="C166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>405</v>
+      </c>
+      <c r="B167" t="s">
+        <v>406</v>
+      </c>
+      <c r="C167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>407</v>
+      </c>
+      <c r="B168" t="s">
+        <v>408</v>
+      </c>
+      <c r="C168" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>409</v>
+      </c>
+      <c r="B169" t="s">
+        <v>410</v>
+      </c>
+      <c r="C169" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>411</v>
+      </c>
+      <c r="B170" t="s">
+        <v>412</v>
+      </c>
+      <c r="C170" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>413</v>
+      </c>
+      <c r="B171" t="s">
+        <v>414</v>
+      </c>
+      <c r="C171" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>415</v>
+      </c>
+      <c r="B172" t="s">
+        <v>416</v>
+      </c>
+      <c r="C172" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>417</v>
+      </c>
+      <c r="B173" t="s">
+        <v>418</v>
+      </c>
+      <c r="C173" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>419</v>
+      </c>
+      <c r="B174" t="s">
+        <v>420</v>
+      </c>
+      <c r="C174" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>421</v>
+      </c>
+      <c r="B175" t="s">
+        <v>422</v>
+      </c>
+      <c r="C175" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>423</v>
+      </c>
+      <c r="B176" t="s">
+        <v>424</v>
+      </c>
+      <c r="C176" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>425</v>
+      </c>
+      <c r="B177" t="s">
+        <v>426</v>
+      </c>
+      <c r="C177" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>427</v>
+      </c>
+      <c r="B178" t="s">
+        <v>428</v>
+      </c>
+      <c r="C178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>429</v>
+      </c>
+      <c r="B179" t="s">
+        <v>430</v>
+      </c>
+      <c r="C179" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>431</v>
+      </c>
+      <c r="B180" t="s">
+        <v>432</v>
+      </c>
+      <c r="C180" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>433</v>
+      </c>
+      <c r="B181" t="s">
+        <v>434</v>
+      </c>
+      <c r="C181" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>435</v>
+      </c>
+      <c r="B182" t="s">
+        <v>436</v>
+      </c>
+      <c r="C182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>437</v>
+      </c>
+      <c r="B183" t="s">
+        <v>438</v>
+      </c>
+      <c r="C183" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>439</v>
+      </c>
+      <c r="B184" t="s">
+        <v>440</v>
+      </c>
+      <c r="C184" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>441</v>
+      </c>
+      <c r="B185" t="s">
+        <v>442</v>
+      </c>
+      <c r="C185" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>443</v>
+      </c>
+      <c r="B186" t="s">
+        <v>444</v>
+      </c>
+      <c r="C186" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>445</v>
+      </c>
+      <c r="B187" t="s">
+        <v>446</v>
+      </c>
+      <c r="C187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>447</v>
+      </c>
+      <c r="B188" t="s">
+        <v>448</v>
+      </c>
+      <c r="C188" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>449</v>
+      </c>
+      <c r="B189" t="s">
+        <v>450</v>
+      </c>
+      <c r="C189" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>451</v>
+      </c>
+      <c r="B190" t="s">
+        <v>452</v>
+      </c>
+      <c r="C190" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>453</v>
+      </c>
+      <c r="B191" t="s">
+        <v>454</v>
+      </c>
+      <c r="C191" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>455</v>
+      </c>
+      <c r="B192" t="s">
+        <v>456</v>
+      </c>
+      <c r="C192" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>457</v>
+      </c>
+      <c r="B193" t="s">
+        <v>458</v>
+      </c>
+      <c r="C193" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>459</v>
+      </c>
+      <c r="B194" t="s">
+        <v>460</v>
+      </c>
+      <c r="C194" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>461</v>
+      </c>
+      <c r="B195" t="s">
+        <v>462</v>
+      </c>
+      <c r="C195" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>463</v>
+      </c>
+      <c r="B196" t="s">
+        <v>464</v>
+      </c>
+      <c r="C196" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>465</v>
+      </c>
+      <c r="B197" t="s">
+        <v>466</v>
+      </c>
+      <c r="C197" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>467</v>
+      </c>
+      <c r="B198" t="s">
+        <v>468</v>
+      </c>
+      <c r="C198" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>469</v>
+      </c>
+      <c r="B199" t="s">
+        <v>470</v>
+      </c>
+      <c r="C199" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>471</v>
+      </c>
+      <c r="B200" t="s">
+        <v>472</v>
+      </c>
+      <c r="C200" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>473</v>
+      </c>
+      <c r="B201" t="s">
+        <v>474</v>
+      </c>
+      <c r="C201" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>475</v>
+      </c>
+      <c r="B202" t="s">
+        <v>476</v>
+      </c>
+      <c r="C202" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>477</v>
+      </c>
+      <c r="B203" t="s">
+        <v>478</v>
+      </c>
+      <c r="C203" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>479</v>
+      </c>
+      <c r="B204" t="s">
+        <v>480</v>
+      </c>
+      <c r="C204" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>481</v>
+      </c>
+      <c r="B205" t="s">
+        <v>482</v>
+      </c>
+      <c r="C205" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>483</v>
+      </c>
+      <c r="B206" t="s">
+        <v>484</v>
+      </c>
+      <c r="C206" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>485</v>
+      </c>
+      <c r="B207" t="s">
+        <v>484</v>
+      </c>
+      <c r="C207" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>486</v>
+      </c>
+      <c r="B208" t="s">
+        <v>487</v>
+      </c>
+      <c r="C208" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>488</v>
+      </c>
+      <c r="B209" t="s">
+        <v>489</v>
+      </c>
+      <c r="C209" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>490</v>
+      </c>
+      <c r="B210" t="s">
+        <v>491</v>
+      </c>
+      <c r="C210" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>492</v>
+      </c>
+      <c r="B211" t="s">
+        <v>493</v>
+      </c>
+      <c r="C211" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>494</v>
+      </c>
+      <c r="B212" t="s">
+        <v>495</v>
+      </c>
+      <c r="C212" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>496</v>
+      </c>
+      <c r="B213" t="s">
+        <v>497</v>
+      </c>
+      <c r="C213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>498</v>
+      </c>
+      <c r="B214" t="s">
+        <v>499</v>
+      </c>
+      <c r="C214" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>500</v>
+      </c>
+      <c r="B215" t="s">
+        <v>501</v>
+      </c>
+      <c r="C215" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>502</v>
+      </c>
+      <c r="B216" t="s">
+        <v>503</v>
+      </c>
+      <c r="C216" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>504</v>
+      </c>
+      <c r="B217" t="s">
+        <v>505</v>
+      </c>
+      <c r="C217" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>506</v>
+      </c>
+      <c r="B218" t="s">
+        <v>507</v>
+      </c>
+      <c r="C218" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>508</v>
+      </c>
+      <c r="B219" t="s">
+        <v>509</v>
+      </c>
+      <c r="C219" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>510</v>
+      </c>
+      <c r="B220" t="s">
+        <v>511</v>
+      </c>
+      <c r="C220" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>512</v>
+      </c>
+      <c r="B221" t="s">
+        <v>513</v>
+      </c>
+      <c r="C221" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>514</v>
+      </c>
+      <c r="B222" t="s">
+        <v>515</v>
+      </c>
+      <c r="C222" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>516</v>
+      </c>
+      <c r="B223" t="s">
+        <v>517</v>
+      </c>
+      <c r="C223" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>518</v>
+      </c>
+      <c r="B224" t="s">
+        <v>519</v>
+      </c>
+      <c r="C224" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>520</v>
+      </c>
+      <c r="B225" t="s">
+        <v>521</v>
+      </c>
+      <c r="C225" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>522</v>
+      </c>
+      <c r="B226" t="s">
+        <v>523</v>
+      </c>
+      <c r="C226" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>524</v>
+      </c>
+      <c r="B227" t="s">
+        <v>525</v>
+      </c>
+      <c r="C227" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>526</v>
+      </c>
+      <c r="B228" t="s">
+        <v>527</v>
+      </c>
+      <c r="C228" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>528</v>
+      </c>
+      <c r="B229" t="s">
+        <v>529</v>
+      </c>
+      <c r="C229" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>530</v>
+      </c>
+      <c r="B230" t="s">
+        <v>531</v>
+      </c>
+      <c r="C230" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>532</v>
+      </c>
+      <c r="B231" t="s">
+        <v>533</v>
+      </c>
+      <c r="C231" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>534</v>
+      </c>
+      <c r="B232" t="s">
+        <v>535</v>
+      </c>
+      <c r="C232" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>10</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>12</v>
+      </c>
+      <c r="B234" t="s">
+        <v>13</v>
+      </c>
+      <c r="C234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>536</v>
+      </c>
+      <c r="B236" t="s">
+        <v>537</v>
+      </c>
+      <c r="C236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>16</v>
+      </c>
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>18</v>
+      </c>
+      <c r="B238" t="s">
+        <v>19</v>
+      </c>
+      <c r="C238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>20</v>
+      </c>
+      <c r="B239" t="s">
+        <v>21</v>
+      </c>
+      <c r="C239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>22</v>
+      </c>
+      <c r="B240" t="s">
+        <v>23</v>
+      </c>
+      <c r="C240" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>24</v>
+      </c>
+      <c r="B241" t="s">
+        <v>25</v>
+      </c>
+      <c r="C241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>26</v>
+      </c>
+      <c r="B242" t="s">
+        <v>27</v>
+      </c>
+      <c r="C242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>28</v>
+      </c>
+      <c r="B243" t="s">
+        <v>29</v>
+      </c>
+      <c r="C243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>30</v>
+      </c>
+      <c r="B244" t="s">
+        <v>31</v>
+      </c>
+      <c r="C244" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>32</v>
+      </c>
+      <c r="B245" t="s">
+        <v>33</v>
+      </c>
+      <c r="C245" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>34</v>
+      </c>
+      <c r="B246" t="s">
+        <v>35</v>
+      </c>
+      <c r="C246" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>36</v>
+      </c>
+      <c r="B247" t="s">
+        <v>37</v>
+      </c>
+      <c r="C247" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>38</v>
+      </c>
+      <c r="B248" t="s">
+        <v>39</v>
+      </c>
+      <c r="C248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>40</v>
+      </c>
+      <c r="B249" t="s">
+        <v>41</v>
+      </c>
+      <c r="C249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>7</v>
+      </c>
+      <c r="B250" t="s">
+        <v>42</v>
+      </c>
+      <c r="C250" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B251" t="s">
+        <v>43</v>
+      </c>
+      <c r="C251" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>44</v>
+      </c>
+      <c r="B252" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>46</v>
+      </c>
+      <c r="B253" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>48</v>
+      </c>
+      <c r="B254" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>50</v>
+      </c>
+      <c r="B255" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>52</v>
+      </c>
+      <c r="B256" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>54</v>
+      </c>
+      <c r="B257" t="s">
+        <v>55</v>
+      </c>
+      <c r="C257" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>56</v>
+      </c>
+      <c r="B258" t="s">
+        <v>57</v>
+      </c>
+      <c r="C258" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>58</v>
+      </c>
+      <c r="B259" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>60</v>
+      </c>
+      <c r="B260" t="s">
+        <v>61</v>
+      </c>
+      <c r="C260" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>62</v>
+      </c>
+      <c r="B261" t="s">
+        <v>63</v>
+      </c>
+      <c r="C261" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>65</v>
+      </c>
+      <c r="B262" t="s">
+        <v>66</v>
+      </c>
+      <c r="C262" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>67</v>
+      </c>
+      <c r="B263" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>69</v>
+      </c>
+      <c r="B264" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>71</v>
+      </c>
+      <c r="B265" t="s">
+        <v>72</v>
+      </c>
+      <c r="C265" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>73</v>
+      </c>
+      <c r="B266" t="s">
+        <v>74</v>
+      </c>
+      <c r="C266" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>75</v>
+      </c>
+      <c r="B267" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>77</v>
+      </c>
+      <c r="B268" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>79</v>
+      </c>
+      <c r="B269" t="s">
+        <v>80</v>
+      </c>
+      <c r="C269" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>81</v>
+      </c>
+      <c r="B270" t="s">
+        <v>82</v>
+      </c>
+      <c r="C270" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>83</v>
+      </c>
+      <c r="B271" t="s">
+        <v>84</v>
+      </c>
+      <c r="C271" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>85</v>
+      </c>
+      <c r="B272" t="s">
+        <v>82</v>
+      </c>
+      <c r="C272" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>86</v>
+      </c>
+      <c r="B273" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>88</v>
+      </c>
+      <c r="B274" t="s">
+        <v>89</v>
+      </c>
+      <c r="C274" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>90</v>
+      </c>
+      <c r="B275" t="s">
+        <v>91</v>
+      </c>
+      <c r="C275" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>92</v>
+      </c>
+      <c r="B276" t="s">
+        <v>93</v>
+      </c>
+      <c r="C276" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>538</v>
+      </c>
+      <c r="B277" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>94</v>
+      </c>
+      <c r="B278" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>94</v>
+      </c>
+      <c r="B279" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>97</v>
+      </c>
+      <c r="B280" t="s">
+        <v>98</v>
+      </c>
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>99</v>
+      </c>
+      <c r="B281" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>101</v>
+      </c>
+      <c r="B282" t="s">
+        <v>102</v>
+      </c>
+      <c r="C282" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
         <v>103</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B283" t="s">
         <v>104</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C283" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>540</v>
+      </c>
+      <c r="B284" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>542</v>
+      </c>
+      <c r="B285" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>544</v>
+      </c>
+      <c r="B286" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>546</v>
+      </c>
+      <c r="B287" t="s">
+        <v>547</v>
+      </c>
+      <c r="C287" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>548</v>
+      </c>
+      <c r="B288" t="s">
+        <v>549</v>
+      </c>
+      <c r="C288" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>550</v>
+      </c>
+      <c r="B289" t="s">
+        <v>551</v>
+      </c>
+      <c r="C289" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>552</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>554</v>
+      </c>
+      <c r="B291" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>556</v>
+      </c>
+      <c r="B292" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>558</v>
+      </c>
+      <c r="B293" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>560</v>
+      </c>
+      <c r="B294" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>562</v>
+      </c>
+      <c r="B295" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>564</v>
+      </c>
+      <c r="B296" t="s">
+        <v>565</v>
+      </c>
+      <c r="C296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>566</v>
+      </c>
+      <c r="B297" t="s">
+        <v>567</v>
+      </c>
+      <c r="C297" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>568</v>
+      </c>
+      <c r="B298" t="s">
+        <v>569</v>
+      </c>
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>570</v>
+      </c>
+      <c r="B299" t="s">
+        <v>571</v>
+      </c>
+      <c r="C299" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>572</v>
+      </c>
+      <c r="B300" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>574</v>
+      </c>
+      <c r="B301" t="s">
+        <v>575</v>
+      </c>
+      <c r="C301" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>576</v>
+      </c>
+      <c r="B302" t="s">
+        <v>575</v>
+      </c>
+      <c r="C302" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>577</v>
+      </c>
+      <c r="B303" t="s">
+        <v>578</v>
+      </c>
+      <c r="C303" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>579</v>
+      </c>
+      <c r="B304" t="s">
+        <v>580</v>
+      </c>
+      <c r="C304" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>581</v>
+      </c>
+      <c r="B305" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>583</v>
+      </c>
+      <c r="B306" t="s">
+        <v>584</v>
+      </c>
+      <c r="C306" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>585</v>
+      </c>
+      <c r="B307" t="s">
+        <v>586</v>
+      </c>
+      <c r="C307" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>587</v>
+      </c>
+      <c r="B308" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>589</v>
+      </c>
+      <c r="B309" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>591</v>
+      </c>
+      <c r="B310" t="s">
+        <v>592</v>
+      </c>
+      <c r="C310" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>593</v>
+      </c>
+      <c r="B311" t="s">
+        <v>594</v>
+      </c>
+      <c r="C311" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>595</v>
+      </c>
+      <c r="B312" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>597</v>
+      </c>
+      <c r="B313" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>599</v>
+      </c>
+      <c r="B314" t="s">
+        <v>600</v>
+      </c>
+      <c r="C314" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>601</v>
+      </c>
+      <c r="B315" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>603</v>
+      </c>
+      <c r="B316" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>605</v>
+      </c>
+      <c r="B317" t="s">
+        <v>606</v>
+      </c>
+      <c r="C317" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>607</v>
+      </c>
+      <c r="B318" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>609</v>
+      </c>
+      <c r="B319" t="s">
+        <v>610</v>
+      </c>
+      <c r="C319" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>611</v>
+      </c>
+      <c r="B320" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>613</v>
+      </c>
+      <c r="B321" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>615</v>
+      </c>
+      <c r="B322" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>617</v>
+      </c>
+      <c r="B323" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>619</v>
+      </c>
+      <c r="B324" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>621</v>
+      </c>
+      <c r="B325" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>623</v>
+      </c>
+      <c r="B326" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>625</v>
+      </c>
+      <c r="B327" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>627</v>
+      </c>
+      <c r="B328" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>629</v>
+      </c>
+      <c r="B329" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>631</v>
+      </c>
+      <c r="B330" t="s">
+        <v>632</v>
+      </c>
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>633</v>
+      </c>
+      <c r="B331" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>635</v>
+      </c>
+      <c r="B332" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>637</v>
+      </c>
+      <c r="B333" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>639</v>
+      </c>
+      <c r="B334" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>641</v>
+      </c>
+      <c r="B335" t="s">
+        <v>642</v>
+      </c>
+      <c r="C335" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>643</v>
+      </c>
+      <c r="B336" t="s">
+        <v>644</v>
+      </c>
+      <c r="C336" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>645</v>
+      </c>
+      <c r="B337" t="s">
+        <v>646</v>
+      </c>
+      <c r="C337" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>647</v>
+      </c>
+      <c r="B338" t="s">
+        <v>648</v>
+      </c>
+      <c r="C338" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>639</v>
+      </c>
+      <c r="B339" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>650</v>
+      </c>
+      <c r="B340" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>652</v>
+      </c>
+      <c r="B341" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8988FFDD-F942-433D-B52B-E2DD2E3AB786}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76AD4B22-0A48-43DD-B589-5D29D7CD100E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="objetos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">objetos!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">objetos!$A$1:$C$642</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3996,7 +3996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>101</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>103</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>105</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>108</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>110</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>112</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>116</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>118</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>120</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>122</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>124</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>112</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>127</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>129</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>131</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>133</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>135</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>137</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>141</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>143</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>145</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>147</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>149</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>151</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>153</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>155</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>157</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>158</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>160</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>162</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>164</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>166</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>168</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>169</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>171</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>173</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>177</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>179</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>181</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>185</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>187</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>189</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>191</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>193</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>195</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>197</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>199</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>201</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>203</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>205</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>207</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>209</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>211</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>213</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>215</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>217</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>219</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>221</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>223</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>225</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>153</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>228</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>230</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>232</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>234</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>133</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>237</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>239</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>241</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>243</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>245</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>247</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>249</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>251</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>253</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>255</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>257</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>259</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>261</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>263</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>265</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>267</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>270</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>272</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>273</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>275</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>276</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>278</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>280</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>282</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>284</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>286</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>288</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>290</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>292</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>294</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>296</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>298</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>300</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>302</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>304</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>106</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>141</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>143</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>164</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>173</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>185</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>213</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>219</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>221</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>153</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>239</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>290</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>162</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>307</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>309</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>311</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>313</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>315</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>317</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>319</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>320</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>322</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>324</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>326</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>328</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>330</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>332</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>334</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>336</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>338</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>7</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>341</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>343</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>344</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>346</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>349</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>351</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>353</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>355</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>356</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>358</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>360</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>362</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>364</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>368</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>370</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>372</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>374</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>375</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>376</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>378</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>380</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>382</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>384</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>386</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>388</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>390</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>391</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>395</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>397</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>399</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>401</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>403</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>407</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>409</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>411</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>413</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>414</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>416</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>418</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>420</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>422</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>424</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>426</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>428</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>430</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>431</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>433</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>435</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>437</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>439</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>441</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>443</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>445</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>447</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>449</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>453</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>457</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>459</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>461</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>463</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>465</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>467</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>469</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>470</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>472</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>474</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>476</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>480</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>482</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>484</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>486</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>488</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>490</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>492</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>494</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>496</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>502</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>503</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>505</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>506</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>508</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>509</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>513</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>515</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>8</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>10</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>12</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>517</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>14</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>16</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>18</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>20</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>22</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>24</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>26</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>28</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>30</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>32</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>34</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>36</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>38</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="7" t="s">
         <v>6</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>7</v>
       </c>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>52</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>54</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>56</v>
       </c>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>58</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>59</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>62</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>64</v>
       </c>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>68</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>70</v>
       </c>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>76</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>77</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>79</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>81</v>
       </c>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>84</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>86</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>88</v>
       </c>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>90</v>
       </c>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>93</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>95</v>
       </c>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>97</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>521</v>
       </c>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>527</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>529</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>531</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>533</v>
       </c>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C290" s="1"/>
     </row>
-    <row r="291" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>534</v>
       </c>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C291" s="1"/>
     </row>
-    <row r="292" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>536</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C294" s="1"/>
     </row>
-    <row r="295" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>542</v>
       </c>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C295" s="1"/>
     </row>
-    <row r="296" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>544</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>546</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>547</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>549</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>551</v>
       </c>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C300" s="1"/>
     </row>
-    <row r="301" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>553</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>555</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>556</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>558</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>560</v>
       </c>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="C305" s="1"/>
     </row>
-    <row r="306" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>562</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>564</v>
       </c>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="C308" s="1"/>
     </row>
-    <row r="309" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>568</v>
       </c>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="C309" s="1"/>
     </row>
-    <row r="310" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>570</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>572</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>574</v>
       </c>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C312" s="1"/>
     </row>
-    <row r="313" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>576</v>
       </c>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C313" s="1"/>
     </row>
-    <row r="314" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>578</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>580</v>
       </c>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C316" s="1"/>
     </row>
-    <row r="317" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>583</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>585</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="C318" s="1"/>
     </row>
-    <row r="319" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>586</v>
       </c>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C320" s="1"/>
     </row>
-    <row r="321" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>588</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C321" s="1"/>
     </row>
-    <row r="322" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>590</v>
       </c>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C325" s="1"/>
     </row>
-    <row r="326" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>597</v>
       </c>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C326" s="1"/>
     </row>
-    <row r="327" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>599</v>
       </c>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C328" s="1"/>
     </row>
-    <row r="329" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>602</v>
       </c>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C329" s="1"/>
     </row>
-    <row r="330" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>604</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C331" s="1"/>
     </row>
-    <row r="332" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>607</v>
       </c>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="C332" s="1"/>
     </row>
-    <row r="333" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>609</v>
       </c>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C333" s="1"/>
     </row>
-    <row r="334" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>610</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="C334" s="1"/>
     </row>
-    <row r="335" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>612</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>613</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>615</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>617</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>610</v>
       </c>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C339" s="1"/>
     </row>
-    <row r="340" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>619</v>
       </c>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C340" s="1"/>
     </row>
-    <row r="341" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>620</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>624</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>626</v>
       </c>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C344" s="1"/>
     </row>
-    <row r="345" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>630</v>
       </c>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="C346" s="1"/>
     </row>
-    <row r="347" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>633</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>635</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>638</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>640</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>640</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>643</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>643</v>
       </c>
@@ -7766,7 +7766,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>646</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>646</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>646</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>646</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>651</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>653</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>653</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>653</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>653</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>635</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>635</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>635</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>635</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>658</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>660</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>662</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>663</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>124</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>665</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>366</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>668</v>
       </c>
@@ -7997,7 +7997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>670</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>672</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>270</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>674</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>676</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>10</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>8</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>680</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>682</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>684</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>686</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>688</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>120</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>691</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>693</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>197</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>696</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>463</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>699</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>701</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>703</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>705</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>160</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>145</v>
       </c>
@@ -8261,7 +8261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>344</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>662</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>709</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>478</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>12</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>195</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>714</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>716</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>718</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>720</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>469</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>723</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>725</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>467</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>728</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>730</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>732</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>734</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>736</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>484</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>739</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>259</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>343</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>300</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>743</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>745</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>207</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>748</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>750</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>752</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>754</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>201</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>488</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>757</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>758</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>759</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>168</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>761</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>503</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>205</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>765</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>767</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>769</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>106</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>772</v>
       </c>
@@ -8756,7 +8756,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>774</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>209</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>777</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>494</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>780</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>781</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>783</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>785</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>498</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>500</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>788</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>6</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>505</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>791</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>280</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>267</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>638</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>509</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>797</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>276</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="465" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>800</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>802</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>804</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>806</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="469" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>808</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>810</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>812</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>82</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>815</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>817</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>640</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>273</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="478" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>822</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="479" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>824</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>826</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>141</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>829</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="483" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>831</v>
       </c>
@@ -9196,7 +9196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>833</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>835</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>643</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>447</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="488" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>838</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="489" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>840</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="490" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>842</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>59</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="492" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>845</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>847</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>282</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>850</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="496" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>852</v>
       </c>
@@ -9339,7 +9339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="497" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>854</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>856</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>251</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="500" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>859</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="501" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>861</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="502" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>864</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="503" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>42</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="504" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>866</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="505" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>868</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="506" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>870</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>872</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>874</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="509" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>875</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" ht="180" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>877</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="511" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>878</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="512" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>880</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>882</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>883</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="515" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>885</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>93</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>888</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>32</v>
       </c>
@@ -9581,7 +9581,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="519" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>890</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>892</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="521" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>894</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="522" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>896</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>898</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="524" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>900</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="525" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>902</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>904</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>906</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="528" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>908</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="529" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>213</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="531" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>411</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="532" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>646</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="533" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>914</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="534" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>915</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>181</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>294</v>
       </c>
@@ -9779,7 +9779,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="537" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:3" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>211</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="538" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>920</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>183</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="540" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>923</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>651</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="542" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>925</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="543" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>927</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>929</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>931</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="546" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>933</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="547" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>935</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="548" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>937</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="549" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>939</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="550" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>941</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>943</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="552" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>945</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="553" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>947</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>949</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="555" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>951</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="556" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>368</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="557" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>954</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="558" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>278</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="560" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>959</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="561" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>961</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="562" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>963</v>
       </c>
@@ -10065,7 +10065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="563" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>965</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="564" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>967</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="565" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>969</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="566" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>971</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="567" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>973</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="568" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>975</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>977</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="570" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:3" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>979</v>
       </c>
@@ -10153,7 +10153,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="571" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>980</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="572" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>982</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="573" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>14</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="574" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>984</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="575" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>16</v>
       </c>
@@ -10208,7 +10208,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="576" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>986</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="577" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>988</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="578" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>22</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="579" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>991</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="580" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>20</v>
       </c>
@@ -10263,7 +10263,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="581" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>994</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="582" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>38</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="583" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>997</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="584" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>999</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="585" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>1001</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="586" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>1002</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="587" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>1004</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="588" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>1006</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="589" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>1008</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="590" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>26</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="591" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>265</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="594" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>1016</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="595" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>1017</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="596" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>326</v>
       </c>
@@ -10439,7 +10439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="597" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>261</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="598" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>1021</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="599" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>562</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="600" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>1024</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="601" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>298</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="602" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>653</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="603" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>1027</v>
       </c>
@@ -10516,7 +10516,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="604" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>1029</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="605" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>234</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="606" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>317</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="607" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>131</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="608" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>155</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="609" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>635</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="610" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>215</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="611" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>296</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="612" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>476</v>
       </c>
@@ -10615,7 +10615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="613" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>1037</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="614" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>521</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="615" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>1040</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="616" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>1042</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="617" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>332</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="618" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>241</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>330</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>1047</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="621" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>255</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="622" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>1050</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="623" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>1052</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="624" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>307</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="625" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>1055</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="626" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>129</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="627" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>1058</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="628" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>311</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="629" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>1061</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="630" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>68</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="631" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>1064</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="632" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>1066</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="633" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>1068</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="634" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>1070</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="635" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>658</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="636" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>422</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="637" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>1072</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="638" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>1074</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="639" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>1076</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="640" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>660</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="641" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>482</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="642" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>508</v>
       </c>
@@ -10946,7 +10946,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
+  <autoFilter ref="A1:C642" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76AD4B22-0A48-43DD-B589-5D29D7CD100E}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CF723FA-DD93-4C0A-A74B-4C4FA09385C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
@@ -3288,192 +3288,192 @@
     <t>AQUISIÇÃO DE APARELHO(S) DE MONITORAMENTO AMBULATORIAL DA PRESSÃO ARTERIAL (MAPA), EM ATENDIMENTO A DEMANDA APRESENTADA PELA POLICLÍNICA OSWALDO CRUZ - POC/SESAU-RO.</t>
   </si>
   <si>
-    <t>Contratação de empresa especializada na prestação de serviços de locação de sistema de Fornecimento e tratamento de água para hemodiálise com osmose reversa fixa duplo passo, visando atender a 26 pontos, incluíndo a rede de distribuição e os pontos de consumo, de forma contínua,? visando atender ao Hospital Regional de Cacoal (HRC), por um período de 12 (doze) meses.</t>
-  </si>
-  <si>
-    <t>Contratação de  serviços dos Correios para a Operação de Logística de Suprimentos In House conforme disponibiliza a NLLC (Inciso IX, art. 75 da Lei 14.133/21) para o Setor de Controle de Estoque, Armazenamento e Distribuição de Suprimentos desta Setorial de Produtos Médicos da SESAU, por um período mínimo de 12 (doze) meses.</t>
-  </si>
-  <si>
-    <t>Contratação Emergencial de Empresa Especializada na Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Avançado TIPO ”D” (UTI Móvel) e Suporte Básico TIPO "B", com mão de obra especializada, para atender as necessidades do Hospital Regional São Francisco do Guaporé-HRSF, Policlínica Oswaldo Cruz-POC, Hospital Regional de Buritis-HRB, Hospital de Urgência e Emergência Regional de Cacoal-HEURO, Hospital Regional de Cacoal-HRC, Centro de Medicina Tropical-CEMETRON, Hospital e Pronto Socorro João Paulo II-JPII, Hospital de Retaguarda de Rondônia-HRRO; Centro de Medicina Intensiva? - AMI; Hospital Regional de Extrema - HRE e Serviço Assistencial Multidisciplinar e Domiciliar-SAMD, pelo período de 12 (doze) meses.</t>
-  </si>
-  <si>
-    <t>Manutenção preventiva e corretiva com fornecimento de peças, executada de forma contínua em equipamentos médico hospitalares da marca Drager, visando atender às necessidades do Hospital de Base Dr. Ary Pinheiro - HBAP, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON e Hospital de Retaguarda de Rondônia-HRRO, desta Secretaria de Estado da Saúde de Rondônia – SESAU-RO, por um período de 12 (doze) meses?.</t>
-  </si>
-  <si>
-    <t>Contratação de empresa especializada na prestação de serviços de Construção da base do reservatório em concreto armado (sobre o solo); fornecimento e instalação de cisterna pré-fabricada com capacidade de 10.000 litros, tipo Tanque, sobre a base (não aterrado), com extravasor, tubos, conexões, entrada e saída de água; conjunto motobomba para recalque tipo centrífuga de 1 CV para comprimento máximo de 25 metros; instalações de quadro elétrico com comprimento máximo de 15 metros, cabos elétricos, disjuntor e automação,  conforme Decreto nº 29.252 de 04 de julho de 2024, pelo período de até 1 (um) ano.</t>
-  </si>
-  <si>
-    <t>Contratação de profissionais médicos para atendimento em Cirurgia Geral, bem como subespecilidades cirúrgicas, quando não disponível no Complexo de Cacoal, nas demandas dos usuários da saúde pública, nas dependências do Hospital de Urgência e Emergência Regional de Cacoal - HEURO, pertencente a Secretaria de Estado da Saúde - SESAU, pelo período de até 12 meses, a partir da primeira assinatura contratual, em conformidade com o disposto no  Art. 107, da Lei 14.133 de 1º de abril de 2021.</t>
-  </si>
-  <si>
-    <t>Registro de Preço para a futura e eventual aquisição de CABOS E ACESSÓRIOS PARA EQUIPAMENTOS MÉDICO-HOSPITALARES,  a fim de atender as unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia"</t>
-  </si>
-  <si>
-    <t>Registro de Preços para futura e eventual Aquisição de Materiais de Costura, visando atender as necessidades do Hospital Regional São Francisco do Guaporé - HRSF,  Centro de Diálise de Ariquemes - CDA, Hospital e Pronto Socorro João Paulo II - JP II, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON, Policlínica Oswaldo Cruz - POC, Hospital Regional de Buritis - HRB e Hospital Infantil Cosme e Damião - HICD, pertencentes a Secretaria de Estado da Saúde - SESAU, por um período de 12 (doze) meses.</t>
-  </si>
-  <si>
-    <t>Aquisição de materiais de permanentes para atender as necessidades do  Núcleo de Farmácia Hospitalar e Setores Assistenciais chaves, do Hospital Regional de Cacoal - HRC,  vinculado a Secretária de Estado da Saúde - SESAU/RO.</t>
-  </si>
-  <si>
-    <t>Registro de Preços para futura e eventual aquisição de Radiografia Computadorizada - CR e CASSETE,? visando atender as Unidades da SESAU, por um período de 12 (doze) meses.</t>
-  </si>
-  <si>
-    <t>Registro de Preço para futura e eventual aquisição de equipamentos laboratoriais, sendo ( agitador kline, banho maria e outros),  visando atender as unidades de saúde vinculadas à SESAU/RO,  por um período de 1 (um) ano.</t>
-  </si>
-  <si>
-    <t>Registro de Preço para futura e eventual aquisição centralizada de MATERIAIS GRÁFICOS, visando atender as unidades de saúde vinculadas à SESAU/RO, pelo período de 1 (um) ano, prorrogável por igual período,  das unidades vinculadas à SESAU/RO.</t>
-  </si>
-  <si>
-    <t>Aquisição de equipamentos de uso laboratorial  necessários à realização de procedimentos Analíticos (exames laboratoriais), para atendimento ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO, cujo recurso é proveniente e específico do Programa: NOVO PAC - ESTRUTURAÇÃO DA VIGILÂNCIA LABORATORIAL EM SAÚDE E AMBIENTES E RESPOSTA AS EMERGÊNCIAS EM SAÚDE</t>
-  </si>
-  <si>
-    <t>Aquisição de Material de consumo CARGA DE GÁS GLP - P13: Gás Liquefeito de Petróleo - GLP acondicionado em botija de 13 Kg, para atender as demandas  das unidades de Saúde Estaduais da Secretaria de Estado da Saúde - SESAU por um período de 06 (seis) meses</t>
-  </si>
-  <si>
-    <t>Aquisição de aparelho(s) de Monitoramento Ambulatorial da Pressão Arterial (MAPA)  para atender a Policlínica Oswaldo Cruz-POC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ÁGUA MINERAL GARRAFÃO RETORNÁVEL DE 20 LITROS, ÁGUA MINERAL SEM GÁS DE 500ML E ÁGUA MINERAL COM GÁS DE 500ML, para atender as demandas das unidades do interior </t>
-  </si>
-  <si>
-    <t>Alimentação Hospitalar - HBAP, HICD,  CEMETRON, CRUE, CEREL.</t>
-  </si>
-  <si>
-    <t>_x000D_
+    <t>Contratação de empresa especializada na prestação de serviços de locação de sistema de Fornecimento e tratamento de água para hemodiálise com osmose reversa fixa duplo passo, visando atender a 26 pontos, incluíndo a rede de distribuição e os pontos de consumo, de forma contínua,​ visando atender ao Hospital Regional de Cacoal (HRC), por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Contratação de serviços dos Correios para a Operação de Logística de Suprimentos In House conforme disponibiliza a NLLC (Inciso IX, art. 75 da Lei 14.133/21) para o Setor de Controle de Estoque, Armazenamento e Distribuição de Suprimentos desta Setorial de Produtos Médicos da SESAU, por um período mínimo de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Contratação Emergencial de Empresa Especializada na Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Avançado TIPO ”D” (UTI Móvel) e Suporte Básico TIPO "B", com mão de obra especializada, para atender as necessidades do Hospital Regional São Francisco do Guaporé-HRSF, Policlínica Oswaldo Cruz-POC, Hospital Regional de Buritis-HRB, Hospital de Urgência e Emergência Regional de Cacoal-HEURO, Hospital Regional de Cacoal-HRC, Centro de Medicina Tropical-CEMETRON, Hospital e Pronto Socorro João Paulo II-JPII, Hospital de Retaguarda de Rondônia-HRRO; Centro de Medicina Intensiva​ - AMI; Hospital Regional de Extrema - HRE e Serviço Assistencial Multidisciplinar e Domiciliar-SAMD, pelo período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Manutenção preventiva e corretiva com fornecimento de peças, executada de forma contínua em equipamentos médico hospitalares da marca Drager, visando atender às necessidades do Hospital de Base Dr. Ary Pinheiro - HBAP, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON e Hospital de Retaguarda de Rondônia-HRRO, desta Secretaria de Estado da Saúde de Rondônia – SESAU-RO, por um período de 12 (doze) meses​.</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Construção da base do reservatório em concreto armado (sobre o solo); fornecimento e instalação de cisterna pré-fabricada com capacidade de 10.000 litros, tipo Tanque, sobre a base (não aterrado), com extravasor, tubos, conexões, entrada e saída de água; conjunto motobomba para recalque tipo centrífuga de 1 CV para comprimento máximo de 25 metros; instalações de quadro elétrico com comprimento máximo de 15 metros, cabos elétricos, disjuntor e automação, conforme Decreto nº 29.252 de 04 de julho de 2024, pelo período de até 1 (um) ano.</t>
+  </si>
+  <si>
+    <t>Contratação de profissionais médicos para atendimento em Cirurgia Geral, bem como subespecilidades cirúrgicas, quando não disponível no Complexo de Cacoal, nas demandas dos usuários da saúde pública, nas dependências do Hospital de Urgência e Emergência Regional de Cacoal - HEURO, pertencente a Secretaria de Estado da Saúde - SESAU, pelo período de até 12 meses, a partir da primeira assinatura contratual, em conformidade com o disposto no Art. 107, da Lei 14.133 de 1º de abril de 2021.</t>
+  </si>
+  <si>
+    <t>Registro de Preço para a futura e eventual aquisição de CABOS E ACESSÓRIOS PARA EQUIPAMENTOS MÉDICO-HOSPITALARES, a fim de atender as unidades de saúde vinculadas à Secretaria de Estado da Saúde de Rondônia"</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual Aquisição de Materiais de Costura, visando atender as necessidades do Hospital Regional São Francisco do Guaporé - HRSF, Centro de Diálise de Ariquemes - CDA, Hospital e Pronto Socorro João Paulo II - JP II, Centro de Medicina Tropical do Estado de Rondônia - CEMETRON, Policlínica Oswaldo Cruz - POC, Hospital Regional de Buritis - HRB e Hospital Infantil Cosme e Damião - HICD, pertencentes a Secretaria de Estado da Saúde - SESAU, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de permanentes para atender as necessidades do Núcleo de Farmácia Hospitalar e Setores Assistenciais chaves, do Hospital Regional de Cacoal - HRC, vinculado a Secretária de Estado da Saúde - SESAU/RO.</t>
+  </si>
+  <si>
+    <t>Registro de Preços para futura e eventual aquisição de Radiografia Computadorizada - CR e CASSETE,​ visando atender as Unidades da SESAU, por um período de 12 (doze) meses.</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual aquisição de equipamentos laboratoriais, sendo ( agitador kline, banho maria e outros), visando atender as unidades de saúde vinculadas à SESAU/RO, por um período de 1 (um) ano.</t>
+  </si>
+  <si>
+    <t>Registro de Preço para futura e eventual aquisição centralizada de MATERIAIS GRÁFICOS, visando atender as unidades de saúde vinculadas à SESAU/RO, pelo período de 1 (um) ano, prorrogável por igual período, das unidades vinculadas à SESAU/RO.</t>
+  </si>
+  <si>
+    <t>Aquisição de equipamentos de uso laboratorial necessários à realização de procedimentos Analíticos (exames laboratoriais), para atendimento ao Laboratório Central de Saúde Pública do Estado de Rondônia - LACEN/RO, cujo recurso é proveniente e específico do Programa: NOVO PAC - ESTRUTURAÇÃO DA VIGILÂNCIA LABORATORIAL EM SAÚDE E AMBIENTES E RESPOSTA AS EMERGÊNCIAS EM SAÚDE</t>
+  </si>
+  <si>
+    <t>Aquisição de Material de consumo CARGA DE GÁS GLP - P13: Gás Liquefeito de Petróleo - GLP acondicionado em botija de 13 Kg, para atender as demandas das unidades de Saúde Estaduais da Secretaria de Estado da Saúde - SESAU por um período de 06 (seis) meses</t>
+  </si>
+  <si>
+    <t>Aquisição de aparelho(s) de Monitoramento Ambulatorial da Pressão Arterial (MAPA) para atender a Policlínica Oswaldo Cruz-POC</t>
+  </si>
+  <si>
+    <t>ÁGUA MINERAL GARRAFÃO RETORNÁVEL DE 20 LITROS, ÁGUA MINERAL SEM GÁS DE 500ML E ÁGUA MINERAL COM GÁS DE 500ML, para atender as demandas das unidades do interior</t>
+  </si>
+  <si>
+    <t>Alimentação Hospitalar - HBAP, HICD, CEMETRON, CRUE, CEREL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 Considerando que aportou nesta Gerência de Compras-GECOMP solicitação quanto a viabilidade da contratação da Empresa Especializada Águas de Ariquemes para o serviço de fornecimento de água e de coleta e tratamento de esgotamento sanitário - CDA</t>
   </si>
   <si>
-    <t xml:space="preserve"> serviços contínuos de manutenção preventiva (incluindo rotinas de inspeção, aferição e calibração rastreada) e corretiva, com fornecimento de peças e materiais, para os equipamentos laboratoriais do (LACEN/LAFRON)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Contratação de empresa especializada em fabricação, fornecimento e instalação de toldos com fornecimento de peças e materiais necessários, JPII</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prestação de serviços de vigilância/segurança patrimonial, para atender as unidades administrativas vinculadas à Secretaria de Estado da Saúde, referente aos Lotes I, II, III e VI,</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> serviços de análises clínicas inseridos nos subgrupos de diagnóstico em TRIAGEM NEONATAL, inseridos na tabela de procedimentos do Sistema Único de Saúde (SIGTAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> aquisição de equipamento médico hospitalar - HB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prestação de serviços médicos na área de Hematologia Pediátrica, para atender pacientes internados no HICD </t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquisição de dietas enterais, suplementos e módulos para uso adulto </t>
-  </si>
-  <si>
-    <t>Serviços de saúde na área de Oncologia, com apoio ambulatorial (terapêutico) e hospitalar no grupo de procedimentos clínicos, sub-grupo tratamento em oncologia e nas formas de organizações de Radioterapia, Quimioterapia paliativa  adulto</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aquisição de formulários padronizados de receituários especiais. Estes receituários devem ser confeccionados mediante autorização dos órgãos vinculados à AGEVISA , e necessitam ser impressos em gráficas devidamente autorizadas, seguindo parâmetros rigorosos e específicos conforme a legislação vigente, PORTARIA Nº 344, DE 12 DE MAIO DE 1998 do Ministério da Saúde. </t>
-  </si>
-  <si>
-    <t>Contratação de empresa especializada na prestação de serviços de locação de equipamentos hospitalares, incluindo fornecimento de insumos, reagentes, acessórios, software e suporte técnico, pelo período de 1 (um) ano, podendo ser prorrogando conforme previsto no Art. 107 da Lei 14.133/21  João Paulo II.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> materiais gráficos e demais itens de comunicação visual, destinados a atender às demandas das ações e campanhas alusivas ao Outubro Rosa 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratação de empresa especializada em serviços de manutenção por chamado, com fornecimento de peças, de forma contínua, aos equipamentos de carrinho de carga horizontal, carrinho de carga vertical, geladeiras e bebedouros </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> decisões judiciais -  equipamento BiPAP (Bilevel Positive Pressure Airwy), em favor do menor, representada por sua genitora. </t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS,  FORMALIZADA PELO PROCESSO ELETRÔNICO n.º 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO</t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS,  FORMALIZADA PELO PROCESSO ELETRÔNICO Nº. 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO</t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS,  FORMALIZADA PELO PROCESSO ELETRÔNICO Nº. 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO,</t>
-  </si>
-  <si>
-    <t>REGISTRO DE PREÇOS (SRP),  DO TIPO MENOR PREÇO POR ITEM , PARA AQUISIÇÃO DE BENS E SERVIÇOS COMUNS. VISANDO À FUTURA, EVENTUAL E PARCELADA AQUISIÇÃO DE MATERIAIS DE CONSUMO DO GRUPO DE APRESENTAÇÃO "CÂNULAS".- (MATERIAIS MÉDICO-HOSPITALARES/PENSO - CÂNULA OROFARÍNGEA DE GUEDEL ESTÉRIL, Nº 00, CÂNULA DE TRAQUEOSTOMIA DE METAL CROMADO, CÂNULA TRAQUEOSTOMIA ESTÉRIL COM BALÃO Nº 3.0, FIXADOR PARA CÂNULA DE TRAQUEOSTOMIA ADULTO E OUTROS) - EXERCÍCIO 2025/2026.</t>
+    <t>serviços contínuos de manutenção preventiva (incluindo rotinas de inspeção, aferição e calibração rastreada) e corretiva, com fornecimento de peças e materiais, para os equipamentos laboratoriais do (LACEN/LAFRON)</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em fabricação, fornecimento e instalação de toldos com fornecimento de peças e materiais necessários, JPII</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de vigilância/segurança patrimonial, para atender as unidades administrativas vinculadas à Secretaria de Estado da Saúde, referente aos Lotes I, II, III e VI,</t>
+  </si>
+  <si>
+    <t>serviços de análises clínicas inseridos nos subgrupos de diagnóstico em TRIAGEM NEONATAL, inseridos na tabela de procedimentos do Sistema Único de Saúde (SIGTAP)</t>
+  </si>
+  <si>
+    <t>aquisição de equipamento médico hospitalar - HB</t>
+  </si>
+  <si>
+    <t>prestação de serviços médicos na área de Hematologia Pediátrica, para atender pacientes internados no HICD</t>
+  </si>
+  <si>
+    <t>aquisição de dietas enterais, suplementos e módulos para uso adulto</t>
+  </si>
+  <si>
+    <t>Serviços de saúde na área de Oncologia, com apoio ambulatorial (terapêutico) e hospitalar no grupo de procedimentos clínicos, sub-grupo tratamento em oncologia e nas formas de organizações de Radioterapia, Quimioterapia paliativa adulto</t>
+  </si>
+  <si>
+    <t>Aquisição de formulários padronizados de receituários especiais. Estes receituários devem ser confeccionados mediante autorização dos órgãos vinculados à AGEVISA , e necessitam ser impressos em gráficas devidamente autorizadas, seguindo parâmetros rigorosos e específicos conforme a legislação vigente, PORTARIA Nº 344, DE 12 DE MAIO DE 1998 do Ministério da Saúde.</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de locação de equipamentos hospitalares, incluindo fornecimento de insumos, reagentes, acessórios, software e suporte técnico, pelo período de 1 (um) ano, podendo ser prorrogando conforme previsto no Art. 107 da Lei 14.133/21 João Paulo II.</t>
+  </si>
+  <si>
+    <t>materiais gráficos e demais itens de comunicação visual, destinados a atender às demandas das ações e campanhas alusivas ao Outubro Rosa 2025</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de manutenção por chamado, com fornecimento de peças, de forma contínua, aos equipamentos de carrinho de carga horizontal, carrinho de carga vertical, geladeiras e bebedouros</t>
+  </si>
+  <si>
+    <t>decisões judiciais - equipamento BiPAP (Bilevel Positive Pressure Airwy), em favor do menor, representada por sua genitora.</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS, FORMALIZADA PELO PROCESSO ELETRÔNICO n.º 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS, FORMALIZADA PELO PROCESSO ELETRÔNICO Nº. 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE CREDENCIADOS QUE ATUEM NA PRESTAÇÃO DE SERVIÇOS PARA REALIZAÇÃO DE EXAMES E PROCEDIMENTOS NA ÁREA DE DIAGNOSE POR IMAGEM NOS SUBGRUPOS DE DIAGNÓSTICOS POR TOMOGRAFIA COMPUTADORIZADA COM SEUS RESPECTIVOS LAUDOS, DE FORMA COMPLEMENTAR, PARA ATENDER AS NECESSIDADES DOS USUÁRIOS DA REGIÃO DE SAÚDE MADEIRA MAMORÉ, DE MODO A FACILITAR O ACESSO E GARANTIR O ATENDIMENTO AOS USUÁRIOS DO SUS, FORMALIZADA PELO PROCESSO ELETRÔNICO Nº. 0036.347190/2020-71, TENDO COMO INTERESSADA A SECRETARIA DE ESTADO DA SAÚDE – RO,</t>
+  </si>
+  <si>
+    <t>REGISTRO DE PREÇOS (SRP), DO TIPO MENOR PREÇO POR ITEM , PARA AQUISIÇÃO DE BENS E SERVIÇOS COMUNS. VISANDO À FUTURA, EVENTUAL E PARCELADA AQUISIÇÃO DE MATERIAIS DE CONSUMO DO GRUPO DE APRESENTAÇÃO "CÂNULAS".- (MATERIAIS MÉDICO-HOSPITALARES/PENSO - CÂNULA OROFARÍNGEA DE GUEDEL ESTÉRIL, Nº 00, CÂNULA DE TRAQUEOSTOMIA DE METAL CROMADO, CÂNULA TRAQUEOSTOMIA ESTÉRIL COM BALÃO Nº 3.0, FIXADOR PARA CÂNULA DE TRAQUEOSTOMIA ADULTO E OUTROS) - EXERCÍCIO 2025/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">AQUISIÇÃO DE POLTRONAS E ARMÁRIOS PARA ESTRUTURAÇÃO DO NOVO AUDITÓRIO DO CENTRO DE MEDICINA TROPICAL DE RONDÔNIA - CEMETRON.
- </t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA OBJETIVANDO A PARTICIPAÇÃO DE 04 (QUATRO) SERVIDORES DESTA SECRETARIA ESTADUAL DE SAÚDE DE RONDÔNIA NO CURSO DE COMO ELABORAR CONCURSO PÚBLICO E PROCESSO SELETIVO SIMPLIFICADO, DOS DIAS  28 A 30 DE ABRIL DE 2025 EM BRASÍLIA/DF</t>
+</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA OBJETIVANDO A PARTICIPAÇÃO DE 04 (QUATRO) SERVIDORES DESTA SECRETARIA ESTADUAL DE SAÚDE DE RONDÔNIA NO CURSO DE COMO ELABORAR CONCURSO PÚBLICO E PROCESSO SELETIVO SIMPLIFICADO, DOS DIAS 28 A 30 DE ABRIL DE 2025 EM BRASÍLIA/DF</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO/PROCEDIMENTOS INSERIDOS SUBGRUPOS DE DIAGNÓSTICO EM LABORATÓRIO CLÍNICO, DE FORMA EMERGENCIAL, PELO PERÍODO DE UM (01) ANO, OU ATÉ A CONCLUSÃO DO PROCESSO LICITATÓRIO.
- </t>
+</t>
   </si>
   <si>
     <t xml:space="preserve">AQUISIÇÃO DE APARELHO CPAP COM MÁSCARA FACIAL PARA CUMPRIMENTO DA DETERMINAÇÃO CONTIDA NOS PROCESSOS JUDICIAIS.
- </t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA REALIZAÇÃO DE ESTUDO ELETROFISIOLÓGICO TERAPÊUTICO - ABLAÇÃO POR RADIOFREQUÊNCIA SEM FLUOROSCOPIA PARA O ATENDIMENTO DE PACIENTE GESTANTE INTERNADA  NO HOSPITAL DE BASE DOUTOR ARY PINHEIRO - HB, COM DIAGNÓSTICO DE TAQUICARDIA SUPRAVENTRICULAR/TAQUICARDIA ATRIAL.</t>
+</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA REALIZAÇÃO DE ESTUDO ELETROFISIOLÓGICO TERAPÊUTICO - ABLAÇÃO POR RADIOFREQUÊNCIA SEM FLUOROSCOPIA PARA O ATENDIMENTO DE PACIENTE GESTANTE INTERNADA NO HOSPITAL DE BASE DOUTOR ARY PINHEIRO - HB, COM DIAGNÓSTICO DE TAQUICARDIA SUPRAVENTRICULAR/TAQUICARDIA ATRIAL.</t>
   </si>
   <si>
     <t xml:space="preserve">AQUISIÇÃO DE MÉDICOS HOSPITALARES/PENSO DOS SEGUINTES GRUPOS DE APRESENTAÇÃO: "EQUIPOS E LINHAS ARTERIAIS", "CATETERES", "TÊXTEIS", "MATERIAIS DIVERSOS II", "CME", "MATERIAIS PARA AFERIÇÃO", "SISTEMA URINÁRIO", "MATERIAIS DIVERSOS I", "SONDAS II" E "TRATO RESPIRATÓRIO"
- </t>
-  </si>
-  <si>
-    <t>AQUISIÇÃO DE MATERIAIS DE CONSUMO- "COBERTURA PARA CURATIVOS" - (MATERIAIS MÉDICO-HOSPITALARES/PENSO - COBERTURA DE HIDROFIBRA, CURATIVO FILME TRANSPARENTE ROLO DE POLIURETANO COM ADESIVO DE POLIACRILATO, CURATIVO EM MULTICAMADAS, CURATIVO PARA FIXAÇÃO E PROTEÇÃO NO LOCAL DE INSERÇÃO DE CATETERES CENTRAIS E PERIFÉRICOS? E OUTROS).</t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE TRANSPORTE INTER-HOSPITALAR DE PACIENTES, COM DISPONIBILIZAÇÃO DE VEÍCULO/AMBULÂNCIA DE SUPORTE AVANÇADO TIPO ”D” (UTI MÓVEL) E SUPORTE BÁSICO TIPO "B", COM MÃO DE OBRA ESPECIALIZADA, PARA ATENDER AS NECESSIDADES DO HOSPITAL REGIONAL SÃO FRANCISCO DO GUAPORÉ-HRSF, POLICLÍNICA OSWALDO CRUZ-POC, HOSPITAL REGIONAL DE BURITIS-HRB, HOSPITAL DE URGÊNCIA E EMERGÊNCIA REGIONAL DE CACOAL-HEURO, HOSPITAL REGIONAL DE CACOAL-HRC, CENTRO DE MEDICINA TROPICAL-CEMETRON, HOSPITAL E PRONTO SOCORRO JOÃO PAULO II-JPII, HOSPITAL DE RETAGUARDA DE RONDÔNIA-HRRO; CENTRO DE MEDICINA INTENSIVA? - AMI; HOSPITAL REGIONAL DE EXTREMA - HRE E SERVIÇO ASSISTENCIAL MULTIDISCIPLINAR E DOMICILIAR-SAMD, POR UM PERÍODO DE 1 (UM) ANO, OU ATÉ QUE SE CONCLUA O PROCESSO LICITATÓRIO  0036.109115/2022-75.</t>
-  </si>
-  <si>
-    <t>AQUISIÇÃO DE MATERIAIS DE CONSUMO DO GRUPO DE APRESENTAÇÃO "BOLSAS DE COLOSTOMIA" - (MATERIAIS MÉDICO-HOSPITALARES/PENSO - BOLSAS PARA ESTOMA INTESTINAL E INTESTINAL PÓS-OPERATÓRIO, URINÁRIO, UMA E DUAS PEÇAS, ADULTO E INFANTIL, CONVEXAS E NÃO CONVEXAS, ADJUVANTES????, ENTRE OUTROS...</t>
-  </si>
-  <si>
-    <t>AQUISIÇÃO DOS MEDICAMENTOS, DIOSMINA + HESPERIDINA 900 + 100 MG, EZETIMIBA 10 MG E RIVAROXABANA 20 MG, CONFORME SOLICITAÇÃO MÉDICA  ANEXADA NOS AUTOS, VISANDO O CUMPRIMENTO DA ORDEM JUDICIAL.</t>
-  </si>
-  <si>
-    <t>AQUISIÇÃO DE GÊNERO ALIMENTÍCIOS (CAFÉ) PARA ATENDER AS DEMANDAS  DAS UNIDADES DE SAÚDE ESTADUAIS DA SECRETARIA DE ESTADO DA SAÚDE - SESAU POR UM PERÍODO DE 06 (SEIS) MESES.</t>
+</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE MATERIAIS DE CONSUMO- "COBERTURA PARA CURATIVOS" - (MATERIAIS MÉDICO-HOSPITALARES/PENSO - COBERTURA DE HIDROFIBRA, CURATIVO FILME TRANSPARENTE ROLO DE POLIURETANO COM ADESIVO DE POLIACRILATO, CURATIVO EM MULTICAMADAS, CURATIVO PARA FIXAÇÃO E PROTEÇÃO NO LOCAL DE INSERÇÃO DE CATETERES CENTRAIS E PERIFÉRICOS​ E OUTROS).</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE TRANSPORTE INTER-HOSPITALAR DE PACIENTES, COM DISPONIBILIZAÇÃO DE VEÍCULO/AMBULÂNCIA DE SUPORTE AVANÇADO TIPO ”D” (UTI MÓVEL) E SUPORTE BÁSICO TIPO "B", COM MÃO DE OBRA ESPECIALIZADA, PARA ATENDER AS NECESSIDADES DO HOSPITAL REGIONAL SÃO FRANCISCO DO GUAPORÉ-HRSF, POLICLÍNICA OSWALDO CRUZ-POC, HOSPITAL REGIONAL DE BURITIS-HRB, HOSPITAL DE URGÊNCIA E EMERGÊNCIA REGIONAL DE CACOAL-HEURO, HOSPITAL REGIONAL DE CACOAL-HRC, CENTRO DE MEDICINA TROPICAL-CEMETRON, HOSPITAL E PRONTO SOCORRO JOÃO PAULO II-JPII, HOSPITAL DE RETAGUARDA DE RONDÔNIA-HRRO; CENTRO DE MEDICINA INTENSIVA​ - AMI; HOSPITAL REGIONAL DE EXTREMA - HRE E SERVIÇO ASSISTENCIAL MULTIDISCIPLINAR E DOMICILIAR-SAMD, POR UM PERÍODO DE 1 (UM) ANO, OU ATÉ QUE SE CONCLUA O PROCESSO LICITATÓRIO 0036.109115/2022-75.</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE MATERIAIS DE CONSUMO DO GRUPO DE APRESENTAÇÃO "BOLSAS DE COLOSTOMIA" - (MATERIAIS MÉDICO-HOSPITALARES/PENSO - BOLSAS PARA ESTOMA INTESTINAL E INTESTINAL PÓS-OPERATÓRIO, URINÁRIO, UMA E DUAS PEÇAS, ADULTO E INFANTIL, CONVEXAS E NÃO CONVEXAS, ADJUVANTES​​​​, ENTRE OUTROS...</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DOS MEDICAMENTOS, DIOSMINA + HESPERIDINA 900 + 100 MG, EZETIMIBA 10 MG E RIVAROXABANA 20 MG, CONFORME SOLICITAÇÃO MÉDICA ANEXADA NOS AUTOS, VISANDO O CUMPRIMENTO DA ORDEM JUDICIAL.</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE GÊNERO ALIMENTÍCIOS (CAFÉ) PARA ATENDER AS DEMANDAS DAS UNIDADES DE SAÚDE ESTADUAIS DA SECRETARIA DE ESTADO DA SAÚDE - SESAU POR UM PERÍODO DE 06 (SEIS) MESES.</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS E FORNECIMENTO DE COFFEE BREAK PARA O IV SIMPÓSIO DE SAÚDE E SEGURANÇA DO TRABALHO DA SECRETARIA DE ESTADO DA SAÚDE DE RONDÔNIA NOS DIAS 13 E 14 DE AGOSTO DE 2025.
- </t>
+</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM REALIZAÇÃO DE PROCEDIMENTO DE RECONSTRUÇÃO ÓSSEA, SEGUIDA DE IMPLANTE E PRÓTESE FIXAS.
- </t>
-  </si>
-  <si>
-    <t>AQUISIÇÃO DOS MEDICAMENTOS RISPERIDONA 1 MG/ML 30 ML, BISOPROLOL 5 MG COMPRIMIDO, DIMESILATO DE LISDEXANFETAMINA 30 MG COMPRIMIDO, RIVAROXABANA 15 MG COMPRIMIDO, PREGABALINA 150 MG COMPRIMIDO?????, CLORIDRATO DE TRAZODONA 150 MG COMPRIMIDO, CLORIDRATO DE CICLOBENZAPRINA 10 MG COMPRIMIDO, DAPAGLIFLOZINA 10 MG COMPRIMIDO, CITIDINA 1 MG + URIDINA 2,5 MG + HIDROXOCOBALAMINA 1,5 MG CÁPSULAS, GELATINOSAS, CUMARINA 15 MG + TROXERRUTINA 90 MG COMPRIMIDO, DOBESILATO DE CÁLCIO 500 MG CÁPSULAS GELATINOSAS DURAS, EMPAGLIFLOZINA 25 MG + LINAGLIPTINA 5 MG COMPRIMIDO, DESVENLAFAXINA 50 MG COMPRIMIDO, VIMPOCETINA 5 MG COMPRIMIDO, BISOPROLOL 10 MG COMPRIMIDO, NITRENDIPINO 20 MG COMPRIMIDO, METFORMINA XR 1 G COMPRIMIDO, ALOPURINOL 100 MG COMPRIMIDO, ÁCIDO ACETILSALICÍLICO 81 MG COMPRIMIDO, DUTASTERIDA + TANSULOSINA 0,5 MG + 0,4 MG CÁPSULAS, LACTOBACILLUS ACIDOPHILUS + LACTOBACILLUS PARACASEI + BIFIDOBACTERIUM LACTIS + BIFIDOBACTERIUM BIFIDUM CÁPSULAS, ATORVASTATINA CÁLCICA 20 MG COMPRIMIDO, EMPAGLIFLOZINA 25 MG COMPRIMIDO, ALOGLIPTINA 25 MG + CLORIDRATO DE PIOGLITAZONA 15 MG COMPRIMIDO REVESTIDO, CONFORME SOLICITAÇÕES MÉDICAS ANEXADAS NOS AUTOS, ATRAVÉS DE DISPENSA DE LICITAÇÃO, COM FULCRO NO ARTIGO 75, INCISO VIII, DA LEI Nº 14.133, DE 01 DE ABRIL DE 2021.</t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM REALIZAÇÃO DE PROCEDIMENTO CIRÚRGICO DE TRATAMENTO PERCUTANEO DE ANEURISMA OU DISSECÇÃO DA AORTA COM ENDOPROTESE + EMBOLIZAÇÃO DE ARTÉRIA ILÍACA INTERNA PARA PACIENTE INTERNADO UNIDADE DE TERAPIA INTENSIVA -UTI  DO HOSPITAL DE BASE DR. ARY PINHEIRO.</t>
+</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DOS MEDICAMENTOS RISPERIDONA 1 MG/ML 30 ML, BISOPROLOL 5 MG COMPRIMIDO, DIMESILATO DE LISDEXANFETAMINA 30 MG COMPRIMIDO, RIVAROXABANA 15 MG COMPRIMIDO, PREGABALINA 150 MG COMPRIMIDO​​​​​, CLORIDRATO DE TRAZODONA 150 MG COMPRIMIDO, CLORIDRATO DE CICLOBENZAPRINA 10 MG COMPRIMIDO, DAPAGLIFLOZINA 10 MG COMPRIMIDO, CITIDINA 1 MG + URIDINA 2,5 MG + HIDROXOCOBALAMINA 1,5 MG CÁPSULAS, GELATINOSAS, CUMARINA 15 MG + TROXERRUTINA 90 MG COMPRIMIDO, DOBESILATO DE CÁLCIO 500 MG CÁPSULAS GELATINOSAS DURAS, EMPAGLIFLOZINA 25 MG + LINAGLIPTINA 5 MG COMPRIMIDO, DESVENLAFAXINA 50 MG COMPRIMIDO, VIMPOCETINA 5 MG COMPRIMIDO, BISOPROLOL 10 MG COMPRIMIDO, NITRENDIPINO 20 MG COMPRIMIDO, METFORMINA XR 1 G COMPRIMIDO, ALOPURINOL 100 MG COMPRIMIDO, ÁCIDO ACETILSALICÍLICO 81 MG COMPRIMIDO, DUTASTERIDA + TANSULOSINA 0,5 MG + 0,4 MG CÁPSULAS, LACTOBACILLUS ACIDOPHILUS + LACTOBACILLUS PARACASEI + BIFIDOBACTERIUM LACTIS + BIFIDOBACTERIUM BIFIDUM CÁPSULAS, ATORVASTATINA CÁLCICA 20 MG COMPRIMIDO, EMPAGLIFLOZINA 25 MG COMPRIMIDO, ALOGLIPTINA 25 MG + CLORIDRATO DE PIOGLITAZONA 15 MG COMPRIMIDO REVESTIDO, CONFORME SOLICITAÇÕES MÉDICAS ANEXADAS NOS AUTOS, ATRAVÉS DE DISPENSA DE LICITAÇÃO, COM FULCRO NO ARTIGO 75, INCISO VIII, DA LEI Nº 14.133, DE 01 DE ABRIL DE 2021.</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM REALIZAÇÃO DE PROCEDIMENTO CIRÚRGICO DE TRATAMENTO PERCUTANEO DE ANEURISMA OU DISSECÇÃO DA AORTA COM ENDOPROTESE + EMBOLIZAÇÃO DE ARTÉRIA ILÍACA INTERNA PARA PACIENTE INTERNADO UNIDADE DE TERAPIA INTENSIVA -UTI DO HOSPITAL DE BASE DR. ARY PINHEIRO.</t>
   </si>
   <si>
     <t xml:space="preserve">REGISTRO DE PREÇOS PARA A FUTURA E EVENTUAL AQUISIÇÃO DE MEDICAMENTOS DE USO CONTÍNUO, DESTINADOS AO ATENDIMENTO DE DEMANDAS JUDICIALIZADAS, EM CUMPRIMENTO ÀS DETERMINAÇÕES JUDICIAIS ENCAMINHADAS À COORDENADORIA DE CONCILIAÇÃO E MANDADOS JUDICIAIS (CCMJ), VISANDO ASSEGURAR O CUMPRIMENTO DAS OBRIGAÇÕES LEGAIS E À GARANTIA DO DIREITO CONSTITUCIONAL À SAÚDE, COM FORNECIMENTO PROGRAMADO PELO PERÍODO DE 1 (UM) ANO.
- </t>
-  </si>
-  <si>
-    <t>À FUTURA, EVENTUAL E PARCELADA AQUISIÇÃO DE MATERIAIS DE CONSUMO "MATERIAIS DE FIOS II - NÃO ABSORVÍVEIS PARA SUTURA" (MATERIAIS MÉDICO-HOSPITALARES/PENSO - FIOS DE NYLON?, FIOS DE AÇO INOXIDÁVEL, FIOS DE POLIPROPILENO, FIOS DE POLIÉSTER COM ALGODÃO, FIOS DE POLIÉSTER TRANÇADO, FIOS DE SEDA E OUTROS) - EXERCÍCIO 2025.</t>
-  </si>
-  <si>
-    <t>IMPLANTAÇÃO DE PREGÃO ELETRÔNICO COM VISTAS AO SISTEMA DE REGISTRO DE PREÇOS (SRP), DO TIPO MENOR PREÇO POR ITEM, PARA AQUISIÇÃO FUTURA, EVENTUAL E PARCELADA DE MATERIAIS DE CONSUMO "FÓRMULAS, DIETAS ENTERAIS E SUPLEMENTOS PEDIATRICOS", PARA ATENDER AS DEMANDAS DAS UNIDADES DE SAÚDE DO ESTADO DE RONDÔNIA (HOSPITAL REGIONAL DE CACOAL/HOSPITAL DE URGÊNCIA E EMERGÊNCIA DE CACOAL - HRC/HEURO; HOSPITAL DE BASE ARY PINHEIRO - HBAP; HOSPITAL INFANTIL COSME DAMIÃO - HICD; HOSPITAL REGIONAL DE EXTREMA - HRE; PROGRAMA DE TERAPIA NUTRICIONAL ENTERAL DOMICILIAR - PTNED  E NÚCLEO DE APOIO E CONCILIAÇÃO - NAC E DO NÚCLEO DE MANDADOS JUDICIAIS - NMJ; HOSPITAL REGIONAL DE BURITIS - HRB;  HOSPITAL DE BASE ARY PINHEIRO - NÚCLEO DE FISSURADOS - HBAP/NUFIS E HOSPITAL REGIONAL DE SÃO FRANCISCO DO GUAPORÉ - HRSFG), PARA O EXERCÍCIO DE 2025.</t>
+</t>
+  </si>
+  <si>
+    <t>À FUTURA, EVENTUAL E PARCELADA AQUISIÇÃO DE MATERIAIS DE CONSUMO "MATERIAIS DE FIOS II - NÃO ABSORVÍVEIS PARA SUTURA" (MATERIAIS MÉDICO-HOSPITALARES/PENSO - FIOS DE NYLON​, FIOS DE AÇO INOXIDÁVEL, FIOS DE POLIPROPILENO, FIOS DE POLIÉSTER COM ALGODÃO, FIOS DE POLIÉSTER TRANÇADO, FIOS DE SEDA E OUTROS) - EXERCÍCIO 2025.</t>
+  </si>
+  <si>
+    <t>IMPLANTAÇÃO DE PREGÃO ELETRÔNICO COM VISTAS AO SISTEMA DE REGISTRO DE PREÇOS (SRP), DO TIPO MENOR PREÇO POR ITEM, PARA AQUISIÇÃO FUTURA, EVENTUAL E PARCELADA DE MATERIAIS DE CONSUMO "FÓRMULAS, DIETAS ENTERAIS E SUPLEMENTOS PEDIATRICOS", PARA ATENDER AS DEMANDAS DAS UNIDADES DE SAÚDE DO ESTADO DE RONDÔNIA (HOSPITAL REGIONAL DE CACOAL/HOSPITAL DE URGÊNCIA E EMERGÊNCIA DE CACOAL - HRC/HEURO; HOSPITAL DE BASE ARY PINHEIRO - HBAP; HOSPITAL INFANTIL COSME DAMIÃO - HICD; HOSPITAL REGIONAL DE EXTREMA - HRE; PROGRAMA DE TERAPIA NUTRICIONAL ENTERAL DOMICILIAR - PTNED E NÚCLEO DE APOIO E CONCILIAÇÃO - NAC E DO NÚCLEO DE MANDADOS JUDICIAIS - NMJ; HOSPITAL REGIONAL DE BURITIS - HRB; HOSPITAL DE BASE ARY PINHEIRO - NÚCLEO DE FISSURADOS - HBAP/NUFIS E HOSPITAL REGIONAL DE SÃO FRANCISCO DO GUAPORÉ - HRSFG), PARA O EXERCÍCIO DE 2025.</t>
   </si>
   <si>
     <t xml:space="preserve">FUTURA E EVENTUAL AQUISIÇÃO DE MATERIAL DE CONSUMO (INJETÁVEIS III - DESERTOS/FRACASSADOS), COM O OBJETIVO DE ATENDER AS NECESSIDADES E DEMANDAS DAS UNIDADES DE SAÚDE HOSPITALARES E AMBULATORIAIS, GERENCIADAS PELA SECRETARIA DE ESTADO DA SAÚDE – SESAU/RO.
- </t>
+</t>
   </si>
   <si>
     <t xml:space="preserve">REGISTRO DE PREÇOS DESTINADO À FUTURA E EVENTUAL AQUISIÇÃO DE MATERIAL DE CONSUMO (INJETÁVEIS IV - DESERTOS/FRACASSADOS), CONFORME RELATÓRIO FINAL DOS FRACASSOS (0053909095) EM ANEXO E DOCUMENTO DE OFICIALIZAÇÃO DE DEMANDA (0053908484)
- </t>
-  </si>
-  <si>
-    <t>Pregão Eletrônico com vistas ao Sistema de Registro de Preços (SRP), do tipo menor preço por item, para AQUISIÇÃO MATERIAL DE CONSUMO VISANDO ATENDER AS NECESSIDADES E DEMANDAS DAS UNIDADES DE SAÚDE HOSPITALARES E AMBULATORIAIS, UNIDADES GERENCIADAS  PELA SECRETARIA DE ESTADO DA SAÚDE - SESAU/RO; MEDICAMENTOS DO GRUPO INJETÁVEIS IV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AQUISIÇÃO DE MEDICAMENTO, APIXAPANA 2,5 MG, PARA CUMPRIMENTO DE DETERMINAÇÃO JUDICIAL.
- </t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA REALIZAÇÃO DE CONTROLE E MONITORAMENTO DE ÁGUA POTÁVEL, COM ANÁLISE PERIÓDICA DAS ÁGUAS, LIMPEZA E LIMPEZA E DESINFECÇÃO DOS RESERVATÓRIOS, DE FORMA CONTÍNUA, VISANDO ATENDER AS UNIDADES HOSPITALARES POR LOTES,  POR UM PERÍODO DE 5 (CINCO) ANOS.</t>
-  </si>
-  <si>
-    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HIGIENIZAÇÃO E LIMPEZA HOSPITALAR, LABORATORIAL E AMBULATORIAL - HIGIENIZAÇÃO, CONSERVAÇÃO, DESINFECÇÃO DE SUPERFÍCIES E MOBILIÁRIOS E RECOLHIMENTO INTERNO DOS RESÍDUOS GRUPO “D”, DE FORMA CONTÍNUA PARA ATENDER A ASSISTÊNCIA MÉDICA INTENSIVA - AMI PELO PERÍODO DE 12 MESES.??????</t>
+</t>
+  </si>
+  <si>
+    <t>Pregão Eletrônico com vistas ao Sistema de Registro de Preços (SRP), do tipo menor preço por item, para AQUISIÇÃO MATERIAL DE CONSUMO VISANDO ATENDER AS NECESSIDADES E DEMANDAS DAS UNIDADES DE SAÚDE HOSPITALARES E AMBULATORIAIS, UNIDADES GERENCIADAS PELA SECRETARIA DE ESTADO DA SAÚDE - SESAU/RO; MEDICAMENTOS DO GRUPO INJETÁVEIS IV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQUISIÇÃO DE MEDICAMENTO, APIXAPANA 2,5 MG, PARA CUMPRIMENTO DE DETERMINAÇÃO JUDICIAL.
+</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA REALIZAÇÃO DE CONTROLE E MONITORAMENTO DE ÁGUA POTÁVEL, COM ANÁLISE PERIÓDICA DAS ÁGUAS, LIMPEZA E LIMPEZA E DESINFECÇÃO DOS RESERVATÓRIOS, DE FORMA CONTÍNUA, VISANDO ATENDER AS UNIDADES HOSPITALARES POR LOTES, POR UM PERÍODO DE 5 (CINCO) ANOS.</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HIGIENIZAÇÃO E LIMPEZA HOSPITALAR, LABORATORIAL E AMBULATORIAL - HIGIENIZAÇÃO, CONSERVAÇÃO, DESINFECÇÃO DE SUPERFÍCIES E MOBILIÁRIOS E RECOLHIMENTO INTERNO DOS RESÍDUOS GRUPO “D”, DE FORMA CONTÍNUA PARA ATENDER A ASSISTÊNCIA MÉDICA INTENSIVA - AMI PELO PERÍODO DE 12 MESES.​​​​​​</t>
   </si>
 </sst>
 </file>
@@ -3655,10 +3655,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6482,7 +6478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>508</v>
       </c>
@@ -9482,7 +9478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:3" ht="180" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" ht="167.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>877</v>
       </c>
@@ -9515,7 +9511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>882</v>
       </c>
@@ -10947,6 +10943,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C642" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
+  <hyperlinks>
+    <hyperlink ref="A250" r:id="rId1" display="http://sei.sistemas.ro.gov.br/sei/controlador.php?acao=protocolo_visualizar&amp;id_protocolo=61082654&amp;id_procedimento_atual=48692645&amp;infra_sistema=100000100&amp;infra_unidade_atual=110000787&amp;infra_hash=22d419bb074061e04034f860c5121b70baf0843cd71098642bd395e3ecdfdfeb1eb260ad24a95adb23ada03eb002b4f9de28ffb4d750133a6a5674d3de6272eff57fa78a382587008ff7141fbadcd92a508da18109598c301aa0405c1728d641" xr:uid="{9E4B052D-BC4B-41DD-8FD0-C2A08D4F7567}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CF723FA-DD93-4C0A-A74B-4C4FA09385C3}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CF1A792-6DE7-4153-B9B5-95130D35F783}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="objetos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="1149">
   <si>
     <t>objeto</t>
   </si>
@@ -3474,6 +3474,36 @@
   </si>
   <si>
     <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HIGIENIZAÇÃO E LIMPEZA HOSPITALAR, LABORATORIAL E AMBULATORIAL - HIGIENIZAÇÃO, CONSERVAÇÃO, DESINFECÇÃO DE SUPERFÍCIES E MOBILIÁRIOS E RECOLHIMENTO INTERNO DOS RESÍDUOS GRUPO “D”, DE FORMA CONTÍNUA PARA ATENDER A ASSISTÊNCIA MÉDICA INTENSIVA - AMI PELO PERÍODO DE 12 MESES.​​​​​​</t>
+  </si>
+  <si>
+    <t>0036.046175/2025-12</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO DE IMPLANTE VALVAR AÓRTICO POR VIA PERCUTÂNEA - TAVI - JUDICIAL</t>
+  </si>
+  <si>
+    <t>0036.047058/2025-76</t>
+  </si>
+  <si>
+    <t>exame Enema Opaco Via Retal, Capsula Endoscópica e Manometria Anorretal</t>
+  </si>
+  <si>
+    <t>0046.000739/2025-51</t>
+  </si>
+  <si>
+    <t>Aquisição de material de laboratorial de média e alta complexidade - LACEN</t>
+  </si>
+  <si>
+    <t>0036.050814/2025-44</t>
+  </si>
+  <si>
+    <t>Contratação de material de consumo de classe farmacológica Água Bidestilada para injeção de 500 ml</t>
+  </si>
+  <si>
+    <t>0050.010216/2025-54</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de manutenção corretiva e preventiva de camas hospitalares, manuais e mecânicas, com fornecimento e substituição de peças</t>
   </si>
 </sst>
 </file>
@@ -3655,6 +3685,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3974,7 +4008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}">
-  <dimension ref="A1:C642"/>
+  <dimension ref="A1:C647"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -10941,11 +10975,61 @@
         <v>3</v>
       </c>
     </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C643" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C645" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C646" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1148</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C642" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
   <hyperlinks>
     <hyperlink ref="A250" r:id="rId1" display="http://sei.sistemas.ro.gov.br/sei/controlador.php?acao=protocolo_visualizar&amp;id_protocolo=61082654&amp;id_procedimento_atual=48692645&amp;infra_sistema=100000100&amp;infra_unidade_atual=110000787&amp;infra_hash=22d419bb074061e04034f860c5121b70baf0843cd71098642bd395e3ecdfdfeb1eb260ad24a95adb23ada03eb002b4f9de28ffb4d750133a6a5674d3de6272eff57fa78a382587008ff7141fbadcd92a508da18109598c301aa0405c1728d641" xr:uid="{9E4B052D-BC4B-41DD-8FD0-C2A08D4F7567}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/objetos.xlsx
+++ b/backend/objetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leozed92-my.sharepoint.com/personal/leozed_leozed92_onmicrosoft_com/Documents/Aplicativos/App GAD SESAU/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB857DD-1F55-4A56-9287-8AEC1FCE1045}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{C24DD8E0-50BB-40E4-B648-E8FAFBB74FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E47FD4DF-3087-418D-B80E-0E7D8D2832C7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92D8D400-3915-4B7A-B5E9-ACA32B0E4BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="objetos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1548">
   <si>
     <t>objeto</t>
   </si>
@@ -3584,49 +3584,6 @@
     <t>0036.017462/2025-15</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">aquisição de material de consumo específico de forma emergencial em atenção ao processo </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0020.013898/2024-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Comunicação: Externa), que ver sobre a Decisão (5) (</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0051184796</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>) em que defere sobre a obrigação da execução do procedimento cirúrgico ARTRODESE DE MÉDIAS / GRANDES ARTICULAÇÕES DE MEMBRO INFERIOR, com o insumo de Haste para artrodese de Tibiotársica, utilizada principalmente em artrose do tornozelo é um desgaste progressivo da cartilagem que pode levar a dor e deformação do tornozelo. Cabe ressaltar que o procedimento será realizado no Hospital de Base Dr. Ary Pinheiro - SESAU;</t>
-    </r>
-  </si>
-  <si>
     <t>0036.049194/2025-09</t>
   </si>
   <si>
@@ -3715,13 +3672,1046 @@
   </si>
   <si>
     <t>prestação de serviços de higienização e limpeza hospitalar, laboratorial e ambulatorial. Isso inclui a higienização, conservação, desinfecção de superfícies e mobiliários, além do recolhimento dos resíduos do Grupo “D”. Esses serviços devem ser prestados ao Hospital e Pronto Socorro João Paulo II</t>
+  </si>
+  <si>
+    <t>aquisição de material de consumo específico de forma emergencial em atenção ao processo 0020.013898/2024-23 (Comunicação: Externa), que ver sobre a Decisão (5) (0051184796) em que defere sobre a obrigação da execução do procedimento cirúrgico ARTRODESE DE MÉDIAS / GRANDES ARTICULAÇÕES DE MEMBRO INFERIOR, com o insumo de Haste para artrodese de Tibiotársica, utilizada principalmente em artrose do tornozelo é um desgaste progressivo da cartilagem que pode levar a dor e deformação do tornozelo. Cabe ressaltar que o procedimento será realizado no Hospital de Base Dr. Ary Pinheiro - SESAU;</t>
+  </si>
+  <si>
+    <t>0036.051878/2025-62</t>
+  </si>
+  <si>
+    <t>Aquisição necessária compreende o Insumo Sensor Freestyle Libre 2 (medidor glicêmico) + Leitor de monitoramento de glicose fresttyle 2 plus sistema flash. Este Insumo possui uma tecnologia avançada, melhorando a qualidade de vida do paciente</t>
+  </si>
+  <si>
+    <t>0036.054099/2025-19</t>
+  </si>
+  <si>
+    <t>aquisição de materiais hospitalares do grupo de "SONDAS I" - EXERCÍCIO 2026</t>
+  </si>
+  <si>
+    <t>0036.053669/2025-53</t>
+  </si>
+  <si>
+    <t>aquisição de materiais de consumo médico-hospitalar/penso de diversos grupos de apresentação, incluindo, mas não se limitando a: "CÂNULAS", CATÉTERES", "CME", "CURATIVOS", "DIVERSOS I", "DIVERSOS II", "DRENOS", "EQUIPOS E LINHAS ARTERIAIS", "FIOS II (NÃO ABSORVÍVEIS", "NEFROLOGIA", "QUÍMICOS E SANEANTES" , "PERFURO CORTANTE", "TUBOS" e "MATERIAL LABORATORIAL"</t>
+  </si>
+  <si>
+    <t>0054.020941/2025-09</t>
+  </si>
+  <si>
+    <t>Fornecimento e instalação de centrais de ar-condicionado - CERO - Recurso Federal</t>
+  </si>
+  <si>
+    <t>0036.018037/2025-43</t>
+  </si>
+  <si>
+    <t>aquisição ordinária de MATERIAL DE CONSUMO NECESSÁRIO PARA A REALIZAÇÃO DE CIRURGIA GERAL E BARIÁTRICA.</t>
+  </si>
+  <si>
+    <t>0036.056900/2025-61</t>
+  </si>
+  <si>
+    <t>Prestação de serviços de objeto o fornecimento de Sistema de Automação Laboratorial (equipamentos) e todos os materiais, reagentes e acessórios necessários à realização de TESTES HEMATOLOGIA - LEPAC</t>
+  </si>
+  <si>
+    <t>0036.056916/2025-73</t>
+  </si>
+  <si>
+    <t>fornecimento de Sistemas de Automação Laboratorial (equipamentos) e todos os materiais, reagentes e acessórios necessários à realização de TESTES de HEMATOLOGIA, HEMOSTASIA, BIOQUIMICA, em atendimento ao programa e projetos prioritários do governo (SISTEMA SGPP) sistema mantido pelo setor de desenvolvimento da CASA CIVIL SOMAR (Comitê de Soluções para Melhoria e Alcance de Resultados) do Estado de Rondônia, quanto a Ampliação do acesso ao diagnóstico laboratorial das hepatites virais, e outros necessários à realização de exames laboratoriais de importância médica assim como aos de monitoramento das doenças/agravos entre outros programas preconizados pelo ministério da Saúde, tendo como unidade de referência o Laboratório de Fronteira de Rondônia - LAFRON/Guajará Mirim</t>
+  </si>
+  <si>
+    <t>0036.056923/2025-75</t>
+  </si>
+  <si>
+    <t>prestação de serviços de fornecimento de Sistemas de Automação Laboratorial (equipamentos) e todos os insumos e acessórios necessários à realização de exames de Bioquímica, Imunologia, Hematologia, Dosagens Hormonais, Urinálise, Hemostasia, Alérgenos, Auto Imunidades, Imuno-hematológicos, Toxicológicos e Medicamentosos, dentre outros, para atender às necessidades do Laboratório de Patologia e Análises Clínicas do Estado de Rondônia - LEPAC</t>
+  </si>
+  <si>
+    <t>0005.005466/2025-18</t>
+  </si>
+  <si>
+    <t>Emenda Berço Aquecido HB</t>
+  </si>
+  <si>
+    <t>0036.057137/2025-95</t>
+  </si>
+  <si>
+    <t>Prestação de serviço de esterilização (CME Classe II) e processamento de PPS para atender os Estabelecimentos Assistenciais de Saúde (EAS) gerenciadas pelo Secretaria de Estado de Saúde de Rondônia (SESAU-RO), com disponibilização de instrumental em comodato, visando atender unidades: HB, JPII, CDA, HRE, HRC, AMI/ JPII, HICD e HEURO, HRB, HRSF, CEMETRON, POC, HRR</t>
+  </si>
+  <si>
+    <t>0036.029755/2025-45</t>
+  </si>
+  <si>
+    <t>adesão da ATA DE REGISTRO DE PREÇOS (Compras: Licitação Adesão a Ata de RP-Participante) - CITI</t>
+  </si>
+  <si>
+    <t>0036.057216/2025-04</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada na Prestação de Serviço de Transporte Inter-Hospitalar de Pacientes, com disponibilização de Veículo/Ambulância de Suporte Avançado TIPO ”D” (UTI Móvel) e Suporte Básico TIPO "B", com mão de obra especializada, para atender as necessidades, pelo período de 12 (doze) meses. Questionou-se sobre a possibilidade de anulação do Lote 3 do certame. - SAMD, POC e HRE</t>
+  </si>
+  <si>
+    <t>0036.028065/2025-79</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de consumo materiais médico-hospitalares /penso "CURATIVOS"- Curativo de espuma 6 camadas e fibras 100% cmc, cobertura antimicrobiana estéril, cobertura de hidrofibra, curativo antimicrobiano, curativo de fibras de celulose e etilsulfonato de celulose e outros.</t>
+  </si>
+  <si>
+    <t>0036.052437/2025-88</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE MATERIAIS DE CONSUMO MATERIAIS MÉDICO-HOSPITALARES /penso "FIOS II - Não Absorvíveis "- Fio Nylon, fio de aço inoxidável, fio de marcapasso, fio polipropileno e outros - EXERCÍCIO 2026</t>
+  </si>
+  <si>
+    <t>0005.007618/2025-17</t>
+  </si>
+  <si>
+    <t>aquisição de Insumos Hospitalares - EMENDA PARLAMENTAR LUIS DO HOSPITAL (HICD)</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar</t>
+  </si>
+  <si>
+    <t>0036.009622/2025-52</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Manutenção Preventiva e Corretiva com Fornecimento de Peças, a ser executada de forma contínua no Equipamento Médico Hospitalar de Ressonância Magnética da Marca Philips - HRC</t>
+  </si>
+  <si>
+    <t>0046.000236/2025-86</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE MATERIAIS, INSUMOS KITs e REAGENTES DE EXTRAÇÃO MOLECULAR, LACEN</t>
+  </si>
+  <si>
+    <t>0005.008047/2025-38</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar Individual vinculada ao Deputado Estadual Jean Oliveira, no valor de R$ 836.800,00 destinada à aquisição de Insumos Hospitalares das Especialidades Médicas e Instrumentos Cirúrgicos.</t>
+  </si>
+  <si>
+    <t>0005.008049/2025-27</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar Individual vinculada ao Deputado Estadual Jean Oliveira, no valor de R$ 2.952.800,00 (dois milhões, novecentos e cinquenta e dois mil e oitocentos reais), destinada à aquisição de Insumos Hospitalares das Especialidades Médicas e Instrumentos Cirúrgicos</t>
+  </si>
+  <si>
+    <t>0005.007472/2025-18</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar - aquisição de Insumos Hospitalares das Especialidades médicas e instrumentos cirúrgicos</t>
+  </si>
+  <si>
+    <t>0005.008178/2025-15</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar - Destinada à contratação de exames de Ressonância Magnética - Carreta</t>
+  </si>
+  <si>
+    <t>0036.058631/2025-77</t>
+  </si>
+  <si>
+    <t>Aquisição na prestação de serviços de fornecimento de COFFEE BREAK - CIB</t>
+  </si>
+  <si>
+    <t>0036.017652/2024-51</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada em serviços de limpeza e higienização Hospitalar, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento dos Resíduos Grupo “D”, de forma contínua para atender a Hospital Estadual e Pronto Socorro João Paulo II, pelo período de 5 (cinco) anos podendo ser prorrogado até o limite do art. 107 da Lei 14.133/21.</t>
+  </si>
+  <si>
+    <t>0005.008268/2025-14</t>
+  </si>
+  <si>
+    <t>Emenda Parlamentar Dra. Taíssa - AMBULÂNCIA</t>
+  </si>
+  <si>
+    <t>0020.020375/2025-14</t>
+  </si>
+  <si>
+    <t>Contratação de empresa especializada na prestação de serviços de Alimentação e Nutrição Hospitalar, com disponibilização de equipamentos e demais utensílios, materiais de consumo, realização de manutenção preventiva e corretiva com reposição de peças para atender de forma continuada as necessidades do Hospital Regional de São Francisco do Guaporé - HRSFG, Hospital Regional de Extrema – HRE e do Hospital Regional de Buritis - HRB, de forma emergencial, por um período de 1 (um) ano ou até que se conclua o processo licitatório nº 0036.005911/2024-00.</t>
+  </si>
+  <si>
+    <t>0049.010688/2025-46</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais de consumo necessários para a realização da coleta externa, interna, acondicionamento, fracionamento e distribuição do leite humano cru e pasteurizado distribuído à Unidade neonatal, garantir maior segurança alimentar do leite captado e processado para consumo dos recém nascidos da UTI Neonatal</t>
+  </si>
+  <si>
+    <t>0036.056057/2025-12</t>
+  </si>
+  <si>
+    <t>aquisição de espaço físico (auditório) adequado para a realização das Reuniões Regimentais de Câmara Técnica, COSEMS e Ordinária de CIB no exercício de 2026.</t>
+  </si>
+  <si>
+    <t>Aquisição de Medicamentos</t>
+  </si>
+  <si>
+    <t>0036.004926/2025-23</t>
+  </si>
+  <si>
+    <t>0036.029420/2025-27</t>
+  </si>
+  <si>
+    <t>0036.055424/2025-61</t>
+  </si>
+  <si>
+    <t>0036.056681/2025-10</t>
+  </si>
+  <si>
+    <t>0036.058709/2025-53</t>
+  </si>
+  <si>
+    <t>0036.059239/2025-45</t>
+  </si>
+  <si>
+    <t>0036.009237/2025-13</t>
+  </si>
+  <si>
+    <t>0036.021027/2025-95</t>
+  </si>
+  <si>
+    <t>0036.028182/2025-32</t>
+  </si>
+  <si>
+    <t>0036.032542/2025-09</t>
+  </si>
+  <si>
+    <t>0036.030535/2025-64</t>
+  </si>
+  <si>
+    <t>0036.033282/2025-81</t>
+  </si>
+  <si>
+    <t>0036.038481/2025-85</t>
+  </si>
+  <si>
+    <t>0036.039484/2025-36</t>
+  </si>
+  <si>
+    <t>0036.040080/2025-95</t>
+  </si>
+  <si>
+    <t>0036.042572/2025-15</t>
+  </si>
+  <si>
+    <t>0036.041607/2025-07</t>
+  </si>
+  <si>
+    <t>0036.045056/2025-42</t>
+  </si>
+  <si>
+    <t>0036.045374/2025-11</t>
+  </si>
+  <si>
+    <t>0036.042712/2025-55</t>
+  </si>
+  <si>
+    <t>0036.048058/2025-93</t>
+  </si>
+  <si>
+    <t>0036.049643/2025-19</t>
+  </si>
+  <si>
+    <t>0036.049396/2025-42</t>
+  </si>
+  <si>
+    <t>0036.049514/2025-12</t>
+  </si>
+  <si>
+    <t>0036.055027/2025-99</t>
+  </si>
+  <si>
+    <t>0036.054577/2025-91</t>
+  </si>
+  <si>
+    <t>0036.024380/2025-27</t>
+  </si>
+  <si>
+    <t>EXAME DE ELETROENCEFALOGRAMA EM VIGILIA E SONO ESPONTANEO C/ OU S/ FOTOESTIMULO (EEG),</t>
+  </si>
+  <si>
+    <t>0036.024495/2025-11</t>
+  </si>
+  <si>
+    <t>MANOMETRIA ANORRETAL</t>
+  </si>
+  <si>
+    <t>0036.024502/2025-85</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE VNI DE ALTA PERFORMANCE - VENTILADOR DOMICILIAR (Trilogy, por exemplo), ASSIM COMO DISPOSITIVO DE ASSISTÊNCIA À TOSSE (Cough Assist, por exemplo)</t>
+  </si>
+  <si>
+    <t>0036.024701/2025-93</t>
+  </si>
+  <si>
+    <t>exame de angiotomografia de coração e vasos de base</t>
+  </si>
+  <si>
+    <t>0036.025250/2025-10</t>
+  </si>
+  <si>
+    <t>Consulta e Avaliação com Neuropsicólogo</t>
+  </si>
+  <si>
+    <t>0036.025306/2025-28</t>
+  </si>
+  <si>
+    <t>Consulta em Fisiatria</t>
+  </si>
+  <si>
+    <t>0036.025324/2025-18</t>
+  </si>
+  <si>
+    <t>CONSULTA EM FONOAUDIOLOGIA</t>
+  </si>
+  <si>
+    <t>0036.029536/2025-66</t>
+  </si>
+  <si>
+    <t>exame de imagem.</t>
+  </si>
+  <si>
+    <t>0036.030203/2025-80</t>
+  </si>
+  <si>
+    <t>EXAME NASOFIBROLARINGOSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.037169/2025-74</t>
+  </si>
+  <si>
+    <t>ELETROENCEFALOGRAMA</t>
+  </si>
+  <si>
+    <t>0036.037298/2025-62</t>
+  </si>
+  <si>
+    <t>Exame de DNA</t>
+  </si>
+  <si>
+    <t>0036.037519/2025-01</t>
+  </si>
+  <si>
+    <t>EXAME LABORATORIAL</t>
+  </si>
+  <si>
+    <t>0036.038207/2025-14</t>
+  </si>
+  <si>
+    <t>Oxigenoterapia em Câmara Hiperbárica</t>
+  </si>
+  <si>
+    <t>0036.039330/2025-44</t>
+  </si>
+  <si>
+    <t>Exame Urodinâmico Completo</t>
+  </si>
+  <si>
+    <t>0036.039821/2025-95</t>
+  </si>
+  <si>
+    <t>EXAME DE NASOFIBROSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.040193/2025-91</t>
+  </si>
+  <si>
+    <t>PET-SCAN</t>
+  </si>
+  <si>
+    <t>0036.040419/2025-53</t>
+  </si>
+  <si>
+    <t>ANGIOTOMOGRAFIA CORONARIANA</t>
+  </si>
+  <si>
+    <t>0036.041047/2025-82</t>
+  </si>
+  <si>
+    <t>sessões de oxigenoterapia,</t>
+  </si>
+  <si>
+    <t>0036.016309/2025-71</t>
+  </si>
+  <si>
+    <t>Contratação de Empresa Especializada para a Prestação de Serviços de Higienização e Limpeza Hospitalar e assemelhadas, Laboratorial e Ambulatorial - Higienização, Conservação, Desinfecção de Superfícies e Mobiliários e Recolhimento dos Resíduos do Grupo “D” para atender às necessidades do Hospital de Base Dr. Ary Pinheiro (HBAP) e Unidade Assistência de Alta Complexidade Oncológica (UNACON)</t>
+  </si>
+  <si>
+    <t>0036.042221/2025-12</t>
+  </si>
+  <si>
+    <t>URETROCISTOGRAFIA MICCIONAL</t>
+  </si>
+  <si>
+    <t>0036.046000/2025-13</t>
+  </si>
+  <si>
+    <t>0036.046061/2025-72</t>
+  </si>
+  <si>
+    <t>Exame de Angiotomografia</t>
+  </si>
+  <si>
+    <t>0036.046312/2025-19</t>
+  </si>
+  <si>
+    <t>equipamentos e dispositivos assistivos,</t>
+  </si>
+  <si>
+    <t>0036.049240/2025-61</t>
+  </si>
+  <si>
+    <t>BRONCOSCOPIA PARA RETIRADA DE CORPO ESTRANHO</t>
+  </si>
+  <si>
+    <t>0036.049308/2025-11</t>
+  </si>
+  <si>
+    <t>ANGIOGRAFIA CEREBRAL COM TESTE DE OCLUSÃO A ESQUERDA</t>
+  </si>
+  <si>
+    <t>0036.050046/2025-29</t>
+  </si>
+  <si>
+    <t>SESSÕES DE CÂMARA HIPERBÁRICA</t>
+  </si>
+  <si>
+    <t>0036.050880/2025-14</t>
+  </si>
+  <si>
+    <t>EXAME DE NASOFIBROLARINGOSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.052488/2025-18</t>
+  </si>
+  <si>
+    <t>Exame de Enema Opaco</t>
+  </si>
+  <si>
+    <t>0036.053181/2025-26</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE VNI DE ALTA PERFORMANCE - VENTILADOR DOMICILIAR (Trilogy, por exemplo), ASSIM COMO DISPOSITIVO DE ASSISTÊNCIA À TOSSE (</t>
+  </si>
+  <si>
+    <t>0036.056569/2025-89</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA PEDIATRICA DE CORREÇÃO CORONARIA ANÔMALA E MIOCARDIOPATIA GRAVE</t>
+  </si>
+  <si>
+    <t>0036.057728/2025-62</t>
+  </si>
+  <si>
+    <t>Tratamento Endovascular para Aneurisma do Segmento Oftálmico da Artéria Carótida Interna, com fundo voltado para o cavo carotídeo</t>
+  </si>
+  <si>
+    <t>0036.058227/2025-01</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE MEMBRO INFERIOR COM STENT REVESTIDO</t>
+  </si>
+  <si>
+    <t>0036.058748/2025-51</t>
+  </si>
+  <si>
+    <t>CORREÇÃO DE CARDIOPATIA CONGENITA OBSTRUTIVA CONGESTIVA TIPO COR TRIATRIATUM , DISPLASIA MITRAL E VENTRICULO ESQUERDO PEQUENO</t>
+  </si>
+  <si>
+    <t>0036.053975/2025-90</t>
+  </si>
+  <si>
+    <t>CONSULTA COM GENETICISTA</t>
+  </si>
+  <si>
+    <t>0036.039839/2025-97</t>
+  </si>
+  <si>
+    <t>TERAPIA FUNDAMENTADA NA CIÊNCIA ABA</t>
+  </si>
+  <si>
+    <t>0036.047840/2025-95</t>
+  </si>
+  <si>
+    <t>MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>0036.044164/2025-06</t>
+  </si>
+  <si>
+    <t>Instalação e Adaptação de Rede Elétrica</t>
+  </si>
+  <si>
+    <t>contratação de empresa para serviço de cirurgia cardíaca neonatal/pediátrica</t>
+  </si>
+  <si>
+    <t>0036.010284/2025-00</t>
+  </si>
+  <si>
+    <t>EXAMES DE NASOFIBROLARINGOSCOPIA</t>
+  </si>
+  <si>
+    <t>aquisição de aparelho CPAP com máscara facial,</t>
+  </si>
+  <si>
+    <t>0036.005827/2025-69</t>
+  </si>
+  <si>
+    <t>0036.060236/2024-73</t>
+  </si>
+  <si>
+    <t>CONSULTA COM PNEUMOLOGISTA - PEDIATRICO</t>
+  </si>
+  <si>
+    <t>0036.057915/2024-65</t>
+  </si>
+  <si>
+    <t>EXAME DE BRONCOSPOPIA</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA INFANTIL PARA CARDIOPATIA CONGENITA TIPO ESTENOSE MITRAL CONGENITA, COMUNICAÇÃO INTERVENTRICULAR PERIMEMBRANOSA PEQUENA, FORAME OVAL DE ALTO FLUXO</t>
+  </si>
+  <si>
+    <t>0036.024128/2025-18</t>
+  </si>
+  <si>
+    <t>contratação de empresa para serviço de Cirurgia Pediátrica Neonatal de correção de Cardiopaa Congênita cianóca de Hipofluxo Pulmonar po Atresia Tricuspide</t>
+  </si>
+  <si>
+    <t>0036.029091/2025-14</t>
+  </si>
+  <si>
+    <t>ESTIMULAÇÃO MAGNÉTICA TRANSCRANIANA REPETITIVA - EMTr</t>
+  </si>
+  <si>
+    <t>CORREÇÃO DE ANEURISMA DISSECANTE COM TUBO VALVADO</t>
+  </si>
+  <si>
+    <t>0036.030669/2025-85</t>
+  </si>
+  <si>
+    <t>0036.031093/2025-73</t>
+  </si>
+  <si>
+    <t>Óculos de grau confeccionado com lentes</t>
+  </si>
+  <si>
+    <t>Cardiopatias Congênitas Cianóticas</t>
+  </si>
+  <si>
+    <t>0036.040709/2025-05</t>
+  </si>
+  <si>
+    <t>Implante Transcateter de Válvula Aórtica (TAVI),</t>
+  </si>
+  <si>
+    <t>tratamento endovascular de artéria subclávia esquerda</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA DE BANDAGEM PULMONAR</t>
+  </si>
+  <si>
+    <t>0036.042225/2025-92</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA - FECHAMENTO DE FORAME OVAL PATENTE</t>
+  </si>
+  <si>
+    <t>0036.037158/2025-94</t>
+  </si>
+  <si>
+    <t>ACOMPANHAMENTOS EM TERAPIAS - MACRO II</t>
+  </si>
+  <si>
+    <t>Cirurgia para correção da atresia tricúspide, Anastomose sistêmico pulmonar</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO CIRÚRGICO de SAFENECTOMIA BILATERAL</t>
+  </si>
+  <si>
+    <t>Cirurgia neonatal/pediátrica para correção de cardiopatia congênita cianótica, tipo dupla via de saída do ventrículo direito</t>
+  </si>
+  <si>
+    <t>Neuromonitorização Intra-Operatória</t>
+  </si>
+  <si>
+    <t>0036.009325/2025-15</t>
+  </si>
+  <si>
+    <t>COLANGIORESSONÂNCIA COM SEDAÇÃO - RNM DE CRÂNIO COM CONTRASTE E SEDAÇÃO - RNM DE CRÂNIO COM SEDAÇÃO</t>
+  </si>
+  <si>
+    <t>0036.010165/2025-49</t>
+  </si>
+  <si>
+    <t>ARTRODESE DE COLUNA TORÁCICA - ARTROPLASTIA DE REVISÃO DE JOELHO COM PROTESE HINGE</t>
+  </si>
+  <si>
+    <t>Implante Percutâneo de Válvula Aórtica (TAVI)</t>
+  </si>
+  <si>
+    <t>ESTUDO ELETROFISIOLÓGICO TERAPÊUTICO- ABLAÇÃO POR RADIOFREQUÊNCIA SEM FLUOROSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.013132/2025-51</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO DE CIRURGIA DE REVISÃO DE ARTROPLASTIA COM ENXERTO ÓSSEO E COMPONENTES DE REVISÃO</t>
+  </si>
+  <si>
+    <t>0036.015001/2025-16</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE CARÓTIDA INTERNA ESQUERDA</t>
+  </si>
+  <si>
+    <t>0036.017516/2025-42</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE TRANSCATETER DE VÁLVULA AÓRTICA (TAVI)</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA INFANTIL DE VALVULOPLASTIA MITRAL E OU TROCA VALVAR MITRAL EM CENTRO COM EXPERTISE PARA ESTA PATOLOGIA REUMÁTICA GRAVE
+Cirurgia Pediátrica Neonatal de correção de Hipoplasia do Arco Aórtico e Coarctação de Aorta</t>
+  </si>
+  <si>
+    <t>0036.019721/2025-42</t>
+  </si>
+  <si>
+    <t>procedimento de facectomia c/ implante de lente intraocular</t>
+  </si>
+  <si>
+    <t>0036.021602/2025-50</t>
+  </si>
+  <si>
+    <t>SUPORTE VENTILATÓRIO PARA RESIDÊNCIA</t>
+  </si>
+  <si>
+    <t>0036.023039/2025-54</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE TERMOABLAÇÃO BILATERAL DA VEIA SAFENA MAGNA COM ENDOLASER E TERMOABLAÇÃO ASSISTIDAS DE COLATERAIS</t>
+  </si>
+  <si>
+    <t>0036.023083/2025-64</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO DE RECONSTITUIÇÃO DA CAVIDADE ORBITÁRIA</t>
+  </si>
+  <si>
+    <t>Procedimento de Tratamento Endovascular de Aneurisma Cerebral de Artéria Carótida Interna a Esquerda</t>
+  </si>
+  <si>
+    <t>0036.023869/2025-81</t>
+  </si>
+  <si>
+    <t>CIRÚRGIA ENDOVASCULAR PARA CORREÇÃO DE ENDOLEAK EM ANEURISMA DE AORTA ABDOMINAL
+CIRURGIA ENDOVASCULAR PARA DILATAÇÃO ANEURISMÁTICA NO SEGMENTO OFTÁLMICO DA ARTÉRIA CARÓTIDA INTERNA ESQUERDA E ANEURISMA CEREBRAL NA ARTÉRIA CARÓTIDA INTERNA DIREITA</t>
+  </si>
+  <si>
+    <t>0036.025475/2025-68</t>
+  </si>
+  <si>
+    <t>ANGIOGRAFIA DE CAROTIDAS e IMPLANTE DE STENT EM ACI ESQUERDA</t>
+  </si>
+  <si>
+    <t>Cirurgia Pediátrica Neonatal para correção de Cardiopatia Congênita tipo Tetralogia de Fallot</t>
+  </si>
+  <si>
+    <t>ESCOLIOSE TORÁCICA ESQUERDA GRAVE DE 54º GRAUS 
+PROCEDIMENTO CIRÚRGICO DE ESCOLIOSE</t>
+  </si>
+  <si>
+    <t>Angiografia Cerebral dos 4 vasos com teste de oclusão</t>
+  </si>
+  <si>
+    <t>Cirurgia Pediátrica Neonatal para correção de Cardiopatia Congênita tipo Coarctação da Aorta</t>
+  </si>
+  <si>
+    <t>0036.029223/2025-16</t>
+  </si>
+  <si>
+    <t>processador de som do Implante Coclear</t>
+  </si>
+  <si>
+    <t>0036.029262/2025-13</t>
+  </si>
+  <si>
+    <t>CIRURGIA ENDOVASCULAR COM COLOCAÇÃO DE STENT EM SEIO TRANSVERSO</t>
+  </si>
+  <si>
+    <t>0036.030594/2025-32</t>
+  </si>
+  <si>
+    <t>ENDOSCOPIA DIGESTIVA ALTA COM APLICAÇÃO DE CIANOACRILATO EM VARIZES DE GROSSO CALIBRE</t>
+  </si>
+  <si>
+    <t>Procedimento Cirúrgico endovascular de aneurisma cerebral com Implante de COILS, a ser definida de acordo com a avaliação das imagens. Anexo IMAGENS ANGIOGRAFIA CEREBRAL</t>
+  </si>
+  <si>
+    <t>Arteriografia da Arteria Renal Esquerda + Embolização Superseletiva de Seguimento de Artéria Renal Esquerda</t>
+  </si>
+  <si>
+    <t>TRATAMENTO PERCUTANEO DE ANEURISMA OU DISSECÇÃO DA AORTA COM ENDOPROTESE A SER DEFINIDA DE ACORDO COM A AVALIAÇÃO DAS IMAGENS PELO LINK INFORMADO NO (0061929917) + EMBOLIZAÇÃO DE ARTÉRIA ILÍACA INTERNA</t>
+  </si>
+  <si>
+    <t>Angioplastia de Carótidas</t>
+  </si>
+  <si>
+    <t>0036.033776/2025-65</t>
+  </si>
+  <si>
+    <t>Colonoscopia/ Colonoscopia com coleta de material para biopsia.</t>
+  </si>
+  <si>
+    <t>Artroplastia total de quadril direito com uso de enxerto ósseo</t>
+  </si>
+  <si>
+    <t>0036.034542/2025-35</t>
+  </si>
+  <si>
+    <t>NASOLARINGOSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.034759/2025-45</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE INTRALUNINAL DE ARTÉRIA CAROTIDA ESQUERA COM STENT RECOBERTO</t>
+  </si>
+  <si>
+    <t>0036.034785/2025-73</t>
+  </si>
+  <si>
+    <t>ANGIORRESSONANCIA ARTERIAL DOS VASOS CERVICAIS E SUPRA AORTICOS COM SEDAÇÃO SEM CONTRASTE</t>
+  </si>
+  <si>
+    <t>0036.034849/2025-36</t>
+  </si>
+  <si>
+    <t>ANGIOGRAFIA CEREBRAL COM EMBOLIZAÇÃO DE MAV</t>
+  </si>
+  <si>
+    <t>0036.035070/2025-38</t>
+  </si>
+  <si>
+    <t>Colonoscopia com biópsia</t>
+  </si>
+  <si>
+    <t>TRATAMENTO ENDOVASCULAR DE ANEURISMAR VISCERAL</t>
+  </si>
+  <si>
+    <t>CIRÚRGICO/REABILITADOR ODONTOLÓGICO SOB ANESTESIA GERAL REALIZANDO ADEQUAÇÃO DO MEIO BUCAL</t>
+  </si>
+  <si>
+    <t>0036.036916/2025-57</t>
+  </si>
+  <si>
+    <t>contratação de empresa especializada na realização de cirurgia cardíaca pediátrica/neonatal de alta complexidade, destinada ao tratamento de Cardiopatia Congênita de Hipofluxo Pulmonar( Tetralogia de Fallot de MA Anatomia, e portadora de T21)</t>
+  </si>
+  <si>
+    <t>Embolização de aneurismas de aorta torácica
+tratamento endovascular de aneurisma de aorta abdomin</t>
+  </si>
+  <si>
+    <t>0036.037109/2025-51</t>
+  </si>
+  <si>
+    <t>EXAMES DE COLONOSCOPIA</t>
+  </si>
+  <si>
+    <t>Angiografia Cerebral do 4 vasos para tratamento endovascular de aneurisma cerebral com stent e Angiografia Cerebral do 4 vasos para tratamento Endovascular de Pseudoaneurisma de artéria temporal profunda</t>
+  </si>
+  <si>
+    <t>0036.038504/2025-51</t>
+  </si>
+  <si>
+    <t>Broncoscopia com dilatação</t>
+  </si>
+  <si>
+    <t>0036.038679/2025-69</t>
+  </si>
+  <si>
+    <t>Safenectomia bilateral com exerese de colaterais</t>
+  </si>
+  <si>
+    <t>0036.039071/2025-51</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE ARTERIA MESENTERICA SUPERIOR COM STENT</t>
+  </si>
+  <si>
+    <t>0036.039239/2025-29</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE COLUNA (hérnia de disco extrusa lombar)</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE FAV+ TROMBECTOMIA de FAV de MSD</t>
+  </si>
+  <si>
+    <t>0036.040416/2025-10</t>
+  </si>
+  <si>
+    <t>ANGIOTOMOGRAFIA DE AORTA - PROTOCOLO TAVI</t>
+  </si>
+  <si>
+    <t>0036.040839/2025-30</t>
+  </si>
+  <si>
+    <t>CONSULTA EM ANGIOLOGIA/CIRURGIA VASCULAR, bem como da cirurgia a ser prescrita pelo especialista e eventuais exames necessários, dada a gravidade do quadro clínico</t>
+  </si>
+  <si>
+    <t>0036.044138/2025-70</t>
+  </si>
+  <si>
+    <t>Broncoscopia Pulmonar, Broncoscopia,Broncoscopia com Lavado Broncoalveolar</t>
+  </si>
+  <si>
+    <t>0036.044289/2025-28</t>
+  </si>
+  <si>
+    <t>procedimento cirúrgico de aneurisma em aorta abdominal e estenose de arterias renais</t>
+  </si>
+  <si>
+    <t>0036.044664/2025-30</t>
+  </si>
+  <si>
+    <t>NASOFIBROLARINGOSCOPIA</t>
+  </si>
+  <si>
+    <t>0036.045148/2025-22</t>
+  </si>
+  <si>
+    <t>SERIOGRAFIA ESOFAGO ESTOMAGO E DUODENO</t>
+  </si>
+  <si>
+    <t>0036.045745/2025-57</t>
+  </si>
+  <si>
+    <t>Timpanomastoidectomia</t>
+  </si>
+  <si>
+    <t>procedimento cirúrgico de Valvuloplastia Mitral Percutânea</t>
+  </si>
+  <si>
+    <t>0036.046682/2025-56</t>
+  </si>
+  <si>
+    <t>ÓRTESE (COLETE TIPO 3D) PARA CORREÇÃODA ESCOLIOSE</t>
+  </si>
+  <si>
+    <t>0036.047133/2025-07</t>
+  </si>
+  <si>
+    <t>POLISSONOGRAFIA TIPO 1 OU 2</t>
+  </si>
+  <si>
+    <t>0036.048471/2025-58</t>
+  </si>
+  <si>
+    <t>Angiotomografia Coronária (protocolo TAVI); Angiotomografia de Tórax (protocolo TAVI) e Angiotomografia de Abdome (protocolo TAVI).</t>
+  </si>
+  <si>
+    <t>0036.048568/2025-61</t>
+  </si>
+  <si>
+    <t>Acesso Transparieto Hepático para Hemodíalise</t>
+  </si>
+  <si>
+    <t>0036.049073/2025-59</t>
+  </si>
+  <si>
+    <t>IMPLANTE PERCUTÂNEO DE VÁLVULA AÓRTICA (TAVI)</t>
+  </si>
+  <si>
+    <t>0036.049126/2025-31</t>
+  </si>
+  <si>
+    <t>Procedimento cirúrgico de termoablação da veia safena magna bilateral e termoablação assistida de varizes tronculares bilateralmente (tratamento total a laser)</t>
+  </si>
+  <si>
+    <t>0036.049141/2025-80</t>
+  </si>
+  <si>
+    <t>ANGIOPLASTIA DE ARTÉRIA FEMORAL SUPERFICIAL E POPLÍTEA NO MEMBRO INFERIOR DIREITO</t>
+  </si>
+  <si>
+    <t>0036.049172/2025-31</t>
+  </si>
+  <si>
+    <t>Cateterismo Cardíaco e Exames Endovasculares , especificamente o Implante de Cateter de Swan-Ganz e avaliação para Implante de Válvula Aórtica Transcateter (TAVI)</t>
+  </si>
+  <si>
+    <t>0036.049299/2025-50</t>
+  </si>
+  <si>
+    <t>Angioçastia de Carótida</t>
+  </si>
+  <si>
+    <t>0036.049477/2025-42</t>
+  </si>
+  <si>
+    <t>0036.049532/2025-02</t>
+  </si>
+  <si>
+    <t>Endoscopia Digestiva Alta com Escleroterapia com Cianoacrilato de varizes de fundo gástrico</t>
+  </si>
+  <si>
+    <t>0036.049825/2025-81</t>
+  </si>
+  <si>
+    <t>ANGIOTOMOGRAFIA DE CORONÁRIAS</t>
+  </si>
+  <si>
+    <t>0036.050530/2025-58</t>
+  </si>
+  <si>
+    <t>0036.050696/2025-74</t>
+  </si>
+  <si>
+    <t>Tratamento endovascular para Embolização de MAV de Hemiface Esquerda</t>
+  </si>
+  <si>
+    <t>0036.050742/2025-35</t>
+  </si>
+  <si>
+    <t>Broncoscopia com dilatação traqueal</t>
+  </si>
+  <si>
+    <t>0036.051333/2025-56</t>
+  </si>
+  <si>
+    <t>ENEMA OPACO VIA RETAL, CAPSULA ENDOSCÓPICA E MANOMETRIA ANORRETAL</t>
+  </si>
+  <si>
+    <t>0036.051538/2025-31</t>
+  </si>
+  <si>
+    <t>Implante Transcate de Válvula Aórtica -TAVI</t>
+  </si>
+  <si>
+    <t>0036.051649/2025-48</t>
+  </si>
+  <si>
+    <t>Procedimento de Embolização de Hemangioma Hepático</t>
+  </si>
+  <si>
+    <t>0036.052303/2025-67</t>
+  </si>
+  <si>
+    <t>consulta com especialista em Pneumopediatria</t>
+  </si>
+  <si>
+    <t>0036.052358/2025-77</t>
+  </si>
+  <si>
+    <t>Broncoscopia rígida para dilatação e Broncoscopia rígida para correção de granuloma</t>
+  </si>
+  <si>
+    <t>0036.052492/2025-78</t>
+  </si>
+  <si>
+    <t>Angiografia Cerebral do 4 vasos para Embolização de MAV e ANGIOPLASTIA DE CAROTIDA COM STENT</t>
+  </si>
+  <si>
+    <t>0036.052693/2025-75</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO DE TROCA VALVAR AÓRTICA POR IMPLANTE TRANSCATETER -TAVI</t>
+  </si>
+  <si>
+    <t>0036.053382/2025-23</t>
+  </si>
+  <si>
+    <t>APARELHO CPAP AUTOMÁTICO COM MÁSCARA NASAL</t>
+  </si>
+  <si>
+    <t>0036.053785/2025-72</t>
+  </si>
+  <si>
+    <t>SESSÕES DE TERAPIA HIPERBÁRICA</t>
+  </si>
+  <si>
+    <t>0036.053804/2025-61</t>
+  </si>
+  <si>
+    <t>0036.053940/2025-51</t>
+  </si>
+  <si>
+    <t>procedimento cirúrgico de prótese de revisão de quadril</t>
+  </si>
+  <si>
+    <t>0036.054414/2025-16</t>
+  </si>
+  <si>
+    <t>Sessão de Oxigenoterapia em Câmara Hiperbárica</t>
+  </si>
+  <si>
+    <t>0036.054628/2025-84</t>
+  </si>
+  <si>
+    <t>Embolização de Malformação arterio-venosa intraparenquimatosa do sistema nervoso central</t>
+  </si>
+  <si>
+    <t>0036.054799/2025-11</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA DE CORREÇÃO DE DRENAGEM ANÔMALA DE VEIAS PULMONARES PARCIAL</t>
+  </si>
+  <si>
+    <t>0036.055471/2025-12</t>
+  </si>
+  <si>
+    <t>Seriografia de Esôfago, Estômago e Duodeno / URETROCISTOGRAFIA MICCIONAL</t>
+  </si>
+  <si>
+    <t>0036.055550/2025-15</t>
+  </si>
+  <si>
+    <t>BRONCOSCOPIA COM DILATAÇÃO</t>
+  </si>
+  <si>
+    <t>0036.055844/2025-47</t>
+  </si>
+  <si>
+    <t>CROMATOGRAFIA DE AMINOACIDOS ( SANGUE), CORMATOGRAFIA DE TANDEN (URINA), DOSAGEM DE ALCICARNITINAS PLASMÁTICAS E PESQUISA DE ÁCIDOS ORGANICOS NA URINA</t>
+  </si>
+  <si>
+    <t>ACOMPANHAMENTOS EM TERAPIAS - MACRO I</t>
+  </si>
+  <si>
+    <t>AVALIAÇÕES EM TERAPIAS - MACRO I</t>
+  </si>
+  <si>
+    <t>0036.000236/2025-03</t>
+  </si>
+  <si>
+    <t>irurgia cardíaca de correção de cardiopatia congenita cianótic</t>
+  </si>
+  <si>
+    <t>CIRURGIA CARDÍACA DE CORREÇÃO DE CARDIOPATIA CONGÊNITA CIANÓTICA</t>
+  </si>
+  <si>
+    <t>0036.002844/2025-44</t>
+  </si>
+  <si>
+    <t>0036.000741/2025-40</t>
+  </si>
+  <si>
+    <t>0036.004560/2025-92</t>
+  </si>
+  <si>
+    <t>0036.000491/2026-29</t>
+  </si>
+  <si>
+    <t>Contratação de serviço técnico especializado de consultoria para atualização de Projeto de Modelagem de Parceria Público Privada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3796,13 +4786,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF1155CC"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3846,7 +4829,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3885,6 +4868,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4226,7 +5212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}">
-  <dimension ref="A1:C676"/>
+  <dimension ref="A1:C887"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -11372,25 +12358,25 @@
         <v>1174</v>
       </c>
       <c r="B661" s="8" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="C661" s="1"/>
     </row>
     <row r="662" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B662" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="B662" s="1" t="s">
-        <v>1177</v>
       </c>
       <c r="C662" s="1"/>
     </row>
     <row r="663" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1178</v>
-      </c>
-      <c r="B663" s="1" t="s">
-        <v>1179</v>
       </c>
       <c r="C663" s="3" t="s">
         <v>26</v>
@@ -11398,129 +12384,2372 @@
     </row>
     <row r="664" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B664" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="B664" s="1" t="s">
-        <v>1181</v>
       </c>
       <c r="C664" s="1"/>
     </row>
     <row r="665" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1182</v>
-      </c>
-      <c r="B665" s="1" t="s">
-        <v>1183</v>
       </c>
       <c r="C665" s="1"/>
     </row>
     <row r="666" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B666" s="1" t="s">
         <v>1184</v>
-      </c>
-      <c r="B666" s="1" t="s">
-        <v>1185</v>
       </c>
       <c r="C666" s="1"/>
     </row>
     <row r="667" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B667" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="B667" s="1" t="s">
-        <v>1187</v>
       </c>
       <c r="C667" s="1"/>
     </row>
     <row r="668" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1188</v>
-      </c>
-      <c r="B668" s="1" t="s">
-        <v>1189</v>
       </c>
       <c r="C668" s="1"/>
     </row>
     <row r="669" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B669" s="1" t="s">
         <v>1190</v>
-      </c>
-      <c r="B669" s="1" t="s">
-        <v>1191</v>
       </c>
       <c r="C669" s="1"/>
     </row>
     <row r="670" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B670" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="B670" s="1" t="s">
-        <v>1193</v>
       </c>
       <c r="C670" s="1"/>
     </row>
     <row r="671" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B671" s="1" t="s">
         <v>1194</v>
-      </c>
-      <c r="B671" s="1" t="s">
-        <v>1195</v>
       </c>
       <c r="C671" s="1"/>
     </row>
     <row r="672" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B672" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="B672" s="1" t="s">
-        <v>1197</v>
       </c>
       <c r="C672" s="1"/>
     </row>
     <row r="673" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1198</v>
-      </c>
-      <c r="B673" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="C673" s="1"/>
     </row>
     <row r="674" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B674" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="B674" s="1" t="s">
-        <v>1201</v>
       </c>
       <c r="C674" s="1"/>
     </row>
     <row r="675" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B675" s="1" t="s">
         <v>1202</v>
-      </c>
-      <c r="B675" s="1" t="s">
-        <v>1203</v>
       </c>
       <c r="C675" s="1"/>
     </row>
     <row r="676" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B676" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="B676" s="1" t="s">
-        <v>1205</v>
-      </c>
       <c r="C676" s="5" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C682" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C683" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C690" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C692" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>704</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C704" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C705" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C706" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C707" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C708" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C709" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C710" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C711" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C712" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>850</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C713" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C714" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C715" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C716" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C717" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C718" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C719" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>985</v>
+      </c>
+      <c r="B720" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C720" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C721" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B722" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C722" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>995</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C723" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B724" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C724" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C725" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B726" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C726" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B727" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C727" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B728" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C728" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B729" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C729" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B730" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C730" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B731" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C731" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C732" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C733" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C734" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B735" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C735" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B736" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C736" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B737" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C737" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B738" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C738" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B739" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C739" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B740" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C740" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B741" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C741" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B742" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C742" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B743" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C743" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B744" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C744" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C745" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C746" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B747" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C747" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B748" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C748" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B749" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C749" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B750" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C750" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B751" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C751" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B752" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C752" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B753" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C753" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C754" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B755" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C755" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B756" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C756" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B757" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C757" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A758" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B758" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C758" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B759" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C759" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B760" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C760" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B761" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C761" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B762" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C762" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B763" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C763" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B764" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C764" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B765" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C765" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B766" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C766" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B767" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C767" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B768" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C768" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B769" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C769" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B770" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C770" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C771" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>917</v>
+      </c>
+      <c r="B772" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C772" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>706</v>
+      </c>
+      <c r="B773" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C773" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C774" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>777</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C775" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B776" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C776" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B777" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C777" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B778" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C778" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>872</v>
+      </c>
+      <c r="B779" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C779" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B780" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C780" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B781" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C781" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A782" t="s">
+        <v>913</v>
+      </c>
+      <c r="B782" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C782" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A783" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B783" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C783" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B784" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C784" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A785" t="s">
+        <v>981</v>
+      </c>
+      <c r="B785" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C785" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A786" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B786" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C786" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A787" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B787" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C787" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A788" t="s">
+        <v>997</v>
+      </c>
+      <c r="B788" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C788" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A789" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B789" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C789" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A790" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B790" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C790" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A791" t="s">
+        <v>717</v>
+      </c>
+      <c r="B791" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C791" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A792" t="s">
+        <v>728</v>
+      </c>
+      <c r="B792" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C792" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A793" t="s">
+        <v>736</v>
+      </c>
+      <c r="B793" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C793" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>754</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C794" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C795" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C796" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>787</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C797" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>793</v>
+      </c>
+      <c r="B798" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C798" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B799" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C799" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B800" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C800" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B801" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C801" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>836</v>
+      </c>
+      <c r="B802" s="14" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C802" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C803" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C804" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C805" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C806" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>875</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C807" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B808" s="14" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C808" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C809" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>888</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C810" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>896</v>
+      </c>
+      <c r="B811" s="14" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C811" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>900</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C812" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>910</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C813" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B814" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C814" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B815" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C815" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C816" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>927</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C817" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>929</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C818" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>931</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C819" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>933</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C820" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C821" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>949</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C822" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C823" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C824" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C825" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C826" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C827" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>951</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C828" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>957</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C829" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B830" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C830" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>967</v>
+      </c>
+      <c r="B831" s="14" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C831" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C832" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>979</v>
+      </c>
+      <c r="B833" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C833" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B834" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C834" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B835" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C835" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B836" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C836" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B837" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C837" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>991</v>
+      </c>
+      <c r="B838" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C838" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B839" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C839" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C840" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C841" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C842" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B843" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C843" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B844" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C844" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B845" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C845" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C846" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C847" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C848" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C849" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B850" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C850" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B851" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C851" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C852" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C853" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C854" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C855" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C856" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C857" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C858" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C859" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C860" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C861" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C862" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C863" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C864" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C865" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C866" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C867" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C868" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C869" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C870" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C871" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C872" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C873" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C874" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C875" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C876" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C877" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C878" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>740</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C879" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>738</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C880" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A881" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C881" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A882" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C882" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A883" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C883" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A884" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C884" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A885" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A886" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A887" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1547</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C642" xr:uid="{4A2FF0CA-3C4D-4BFF-9AA5-A0CFD76751B1}"/>
-  <hyperlinks>
-    <hyperlink ref="A250" r:id="rId1" display="http://sei.sistemas.ro.gov.br/sei/controlador.php?acao=protocolo_visualizar&amp;id_protocolo=61082654&amp;id_procedimento_atual=48692645&amp;infra_sistema=100000100&amp;infra_unidade_atual=110000787&amp;infra_hash=22d419bb074061e04034f860c5121b70baf0843cd71098642bd395e3ecdfdfeb1eb260ad24a95adb23ada03eb002b4f9de28ffb4d750133a6a5674d3de6272eff57fa78a382587008ff7141fbadcd92a508da18109598c301aa0405c1728d641" xr:uid="{ADD110A2-0E66-4D23-826D-F25B91CB33E6}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>